--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119966735</v>
+        <v>119966720</v>
       </c>
       <c r="B20" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503371</v>
+        <v>503241</v>
       </c>
       <c r="R20" t="n">
-        <v>7134532</v>
+        <v>7134650</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966720</v>
+        <v>119966735</v>
       </c>
       <c r="B21" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503241</v>
+        <v>503371</v>
       </c>
       <c r="R21" t="n">
-        <v>7134650</v>
+        <v>7134532</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119966748</v>
+        <v>119949136</v>
       </c>
       <c r="B34" t="n">
-        <v>79642</v>
+        <v>57463</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4133,38 +4133,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503392</v>
+        <v>503213</v>
       </c>
       <c r="R34" t="n">
-        <v>7134464</v>
+        <v>7134603</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4223,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119949136</v>
+        <v>119966748</v>
       </c>
       <c r="B35" t="n">
-        <v>57463</v>
+        <v>79642</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4235,43 +4240,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503213</v>
+        <v>503392</v>
       </c>
       <c r="R35" t="n">
-        <v>7134603</v>
+        <v>7134464</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119966732</v>
+        <v>119950975</v>
       </c>
       <c r="B50" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5770,41 +5770,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503285</v>
+        <v>503152</v>
       </c>
       <c r="R50" t="n">
-        <v>7135231</v>
+        <v>7134944</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119950975</v>
+        <v>119945198</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5872,25 +5872,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503152</v>
+        <v>503176</v>
       </c>
       <c r="R51" t="n">
-        <v>7134944</v>
+        <v>7134750</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5962,10 +5962,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119945198</v>
+        <v>119966732</v>
       </c>
       <c r="B52" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5978,37 +5978,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503176</v>
+        <v>503285</v>
       </c>
       <c r="R52" t="n">
-        <v>7134750</v>
+        <v>7135231</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119949016</v>
+        <v>119945075</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7101,25 +7101,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7129,10 +7129,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503196</v>
+        <v>503170</v>
       </c>
       <c r="R63" t="n">
-        <v>7134584</v>
+        <v>7134825</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7191,10 +7191,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119945075</v>
+        <v>119949016</v>
       </c>
       <c r="B64" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7203,25 +7203,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503170</v>
+        <v>503196</v>
       </c>
       <c r="R64" t="n">
-        <v>7134825</v>
+        <v>7134584</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119945215</v>
+        <v>119966742</v>
       </c>
       <c r="B65" t="n">
         <v>91840</v>
@@ -7329,17 +7329,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503171</v>
+        <v>503371</v>
       </c>
       <c r="R65" t="n">
-        <v>7134729</v>
+        <v>7134522</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119944998</v>
+        <v>119945215</v>
       </c>
       <c r="B67" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7509,25 +7509,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503182</v>
+        <v>503171</v>
       </c>
       <c r="R67" t="n">
-        <v>7134859</v>
+        <v>7134729</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7599,10 +7599,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966742</v>
+        <v>119944998</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7611,41 +7611,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503371</v>
+        <v>503182</v>
       </c>
       <c r="R68" t="n">
-        <v>7134522</v>
+        <v>7134859</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119966720</v>
+        <v>119966735</v>
       </c>
       <c r="B20" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503241</v>
+        <v>503371</v>
       </c>
       <c r="R20" t="n">
-        <v>7134650</v>
+        <v>7134532</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966735</v>
+        <v>119966720</v>
       </c>
       <c r="B21" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503371</v>
+        <v>503241</v>
       </c>
       <c r="R21" t="n">
-        <v>7134532</v>
+        <v>7134650</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119966742</v>
+        <v>119945215</v>
       </c>
       <c r="B65" t="n">
         <v>91840</v>
@@ -7329,17 +7329,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503371</v>
+        <v>503171</v>
       </c>
       <c r="R65" t="n">
-        <v>7134522</v>
+        <v>7134729</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119945215</v>
+        <v>119944998</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7509,25 +7509,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503171</v>
+        <v>503182</v>
       </c>
       <c r="R67" t="n">
-        <v>7134729</v>
+        <v>7134859</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7599,10 +7599,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119944998</v>
+        <v>119966742</v>
       </c>
       <c r="B68" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7611,41 +7611,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503182</v>
+        <v>503371</v>
       </c>
       <c r="R68" t="n">
-        <v>7134859</v>
+        <v>7134522</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119966729</v>
+        <v>119944976</v>
       </c>
       <c r="B15" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,37 +2199,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503291</v>
+        <v>503197</v>
       </c>
       <c r="R15" t="n">
-        <v>7135241</v>
+        <v>7134856</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119949113</v>
+        <v>119966734</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,41 +2297,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503213</v>
+        <v>503386</v>
       </c>
       <c r="R16" t="n">
-        <v>7134599</v>
+        <v>7134487</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119948911</v>
+        <v>119966747</v>
       </c>
       <c r="B17" t="n">
-        <v>79115</v>
+        <v>12337</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,41 +2399,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>101283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503190</v>
+        <v>503341</v>
       </c>
       <c r="R17" t="n">
         <v>7134550</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,6 +2463,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,10 +2494,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119966740</v>
+        <v>119945198</v>
       </c>
       <c r="B18" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,37 +2510,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503194</v>
+        <v>503176</v>
       </c>
       <c r="R18" t="n">
-        <v>7134678</v>
+        <v>7134750</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,10 +2596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119950802</v>
+        <v>119948853</v>
       </c>
       <c r="B19" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2608,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,13 +2636,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503165</v>
+        <v>503204</v>
       </c>
       <c r="R19" t="n">
-        <v>7134812</v>
+        <v>7134538</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119966735</v>
+        <v>119950932</v>
       </c>
       <c r="B20" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,41 +2710,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503371</v>
+        <v>503151</v>
       </c>
       <c r="R20" t="n">
-        <v>7134532</v>
+        <v>7134896</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2795,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966720</v>
+        <v>119966748</v>
       </c>
       <c r="B21" t="n">
-        <v>79115</v>
+        <v>79642</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,25 +2812,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503241</v>
+        <v>503392</v>
       </c>
       <c r="R21" t="n">
-        <v>7134650</v>
+        <v>7134464</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,7 +2902,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119944992</v>
+        <v>119946999</v>
       </c>
       <c r="B22" t="n">
         <v>79115</v>
@@ -2937,13 +2942,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503182</v>
+        <v>503249</v>
       </c>
       <c r="R22" t="n">
-        <v>7134856</v>
+        <v>7134683</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2999,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119953361</v>
+        <v>119948911</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>79115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,37 +3020,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503283</v>
+        <v>503190</v>
       </c>
       <c r="R23" t="n">
-        <v>7135226</v>
+        <v>7134550</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119953316</v>
+        <v>119944992</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>79115</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,41 +3118,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503249</v>
+        <v>503182</v>
       </c>
       <c r="R24" t="n">
-        <v>7135183</v>
+        <v>7134856</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,7 +3208,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119966743</v>
+        <v>119950975</v>
       </c>
       <c r="B25" t="n">
         <v>91840</v>
@@ -3239,17 +3244,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503321</v>
+        <v>503152</v>
       </c>
       <c r="R25" t="n">
-        <v>7134576</v>
+        <v>7134944</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3305,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119953277</v>
+        <v>119966744</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3317,41 +3322,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503236</v>
+        <v>503354</v>
       </c>
       <c r="R26" t="n">
-        <v>7135178</v>
+        <v>7134553</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3407,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119947420</v>
+        <v>119966737</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,41 +3424,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503213</v>
+        <v>503354</v>
       </c>
       <c r="R27" t="n">
-        <v>7134622</v>
+        <v>7134564</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3509,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119948845</v>
+        <v>119950877</v>
       </c>
       <c r="B28" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,25 +3526,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503204</v>
+        <v>503166</v>
       </c>
       <c r="R28" t="n">
-        <v>7134543</v>
+        <v>7134864</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3611,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119966728</v>
+        <v>119950521</v>
       </c>
       <c r="B29" t="n">
-        <v>79608</v>
+        <v>79115</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3627,37 +3632,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503285</v>
+        <v>503238</v>
       </c>
       <c r="R29" t="n">
-        <v>7134565</v>
+        <v>7134692</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3713,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119953208</v>
+        <v>119950926</v>
       </c>
       <c r="B30" t="n">
-        <v>79608</v>
+        <v>79115</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3729,37 +3734,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503164</v>
+        <v>503153</v>
       </c>
       <c r="R30" t="n">
-        <v>7135128</v>
+        <v>7134897</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3815,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950727</v>
+        <v>119953375</v>
       </c>
       <c r="B31" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,37 +3836,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503147</v>
+        <v>503279</v>
       </c>
       <c r="R31" t="n">
-        <v>7134810</v>
+        <v>7135237</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3917,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950704</v>
+        <v>119953277</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3929,41 +3934,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503155</v>
+        <v>503236</v>
       </c>
       <c r="R32" t="n">
-        <v>7134772</v>
+        <v>7135178</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4019,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950926</v>
+        <v>119966741</v>
       </c>
       <c r="B33" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4035,37 +4040,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503153</v>
+        <v>503195</v>
       </c>
       <c r="R33" t="n">
-        <v>7134897</v>
+        <v>7134698</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4121,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119949136</v>
+        <v>119966733</v>
       </c>
       <c r="B34" t="n">
-        <v>57463</v>
+        <v>79643</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4133,43 +4138,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503213</v>
+        <v>503392</v>
       </c>
       <c r="R34" t="n">
-        <v>7134603</v>
+        <v>7134464</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119966748</v>
+        <v>119966735</v>
       </c>
       <c r="B35" t="n">
-        <v>79642</v>
+        <v>78262</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,25 +4240,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503392</v>
+        <v>503371</v>
       </c>
       <c r="R35" t="n">
-        <v>7134464</v>
+        <v>7134532</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119950857</v>
+        <v>119947387</v>
       </c>
       <c r="B36" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503168</v>
+        <v>503210</v>
       </c>
       <c r="R36" t="n">
-        <v>7134856</v>
+        <v>7134632</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119953290</v>
+        <v>119947420</v>
       </c>
       <c r="B37" t="n">
-        <v>79642</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4448,37 +4448,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503235</v>
+        <v>503213</v>
       </c>
       <c r="R37" t="n">
-        <v>7135189</v>
+        <v>7134622</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119953353</v>
+        <v>119966729</v>
       </c>
       <c r="B38" t="n">
-        <v>90527</v>
+        <v>79608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,41 +4546,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503265</v>
+        <v>503291</v>
       </c>
       <c r="R38" t="n">
-        <v>7135233</v>
+        <v>7135241</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119944976</v>
+        <v>119950802</v>
       </c>
       <c r="B39" t="n">
-        <v>78262</v>
+        <v>89633</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,21 +4652,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503197</v>
+        <v>503165</v>
       </c>
       <c r="R39" t="n">
-        <v>7134856</v>
+        <v>7134812</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119944974</v>
+        <v>119953208</v>
       </c>
       <c r="B40" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4754,34 +4754,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503197</v>
+        <v>503164</v>
       </c>
       <c r="R40" t="n">
-        <v>7134847</v>
+        <v>7135128</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119953308</v>
+        <v>119966740</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4856,37 +4856,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503244</v>
+        <v>503194</v>
       </c>
       <c r="R41" t="n">
-        <v>7135195</v>
+        <v>7134678</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119966739</v>
+        <v>119950704</v>
       </c>
       <c r="B42" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4954,41 +4954,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503196</v>
+        <v>503155</v>
       </c>
       <c r="R42" t="n">
-        <v>7134493</v>
+        <v>7134772</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119953313</v>
+        <v>119966726</v>
       </c>
       <c r="B43" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5056,41 +5056,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503239</v>
+        <v>503285</v>
       </c>
       <c r="R43" t="n">
-        <v>7135198</v>
+        <v>7134565</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119950877</v>
+        <v>119966739</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5158,41 +5158,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503166</v>
+        <v>503196</v>
       </c>
       <c r="R44" t="n">
-        <v>7134864</v>
+        <v>7134493</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119945252</v>
+        <v>119951025</v>
       </c>
       <c r="B45" t="n">
-        <v>79115</v>
+        <v>92030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5264,21 +5264,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5291,10 +5291,10 @@
         <v>503166</v>
       </c>
       <c r="R45" t="n">
-        <v>7134711</v>
+        <v>7134990</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966733</v>
+        <v>119966722</v>
       </c>
       <c r="B46" t="n">
-        <v>79643</v>
+        <v>89633</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,25 +5362,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503392</v>
+        <v>503218</v>
       </c>
       <c r="R46" t="n">
-        <v>7134464</v>
+        <v>7134517</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119950521</v>
+        <v>119948976</v>
       </c>
       <c r="B47" t="n">
-        <v>79115</v>
+        <v>89633</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5468,21 +5468,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503238</v>
+        <v>503222</v>
       </c>
       <c r="R47" t="n">
-        <v>7134692</v>
+        <v>7134576</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119948853</v>
+        <v>119944998</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5566,25 +5566,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5594,13 +5594,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503204</v>
+        <v>503182</v>
       </c>
       <c r="R48" t="n">
-        <v>7134538</v>
+        <v>7134859</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119946999</v>
+        <v>119966724</v>
       </c>
       <c r="B49" t="n">
-        <v>79115</v>
+        <v>57463</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5672,37 +5672,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503249</v>
+        <v>503195</v>
       </c>
       <c r="R49" t="n">
-        <v>7134683</v>
+        <v>7134698</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5732,6 +5732,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5758,7 +5763,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119950975</v>
+        <v>119966743</v>
       </c>
       <c r="B50" t="n">
         <v>91840</v>
@@ -5794,17 +5799,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503152</v>
+        <v>503321</v>
       </c>
       <c r="R50" t="n">
-        <v>7134944</v>
+        <v>7134576</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5860,10 +5865,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119945198</v>
+        <v>119966746</v>
       </c>
       <c r="B51" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5872,41 +5877,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503176</v>
+        <v>503256</v>
       </c>
       <c r="R51" t="n">
-        <v>7134750</v>
+        <v>7134674</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5962,7 +5967,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119966732</v>
+        <v>119953308</v>
       </c>
       <c r="B52" t="n">
         <v>79607</v>
@@ -5998,17 +6003,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503285</v>
+        <v>503244</v>
       </c>
       <c r="R52" t="n">
-        <v>7135231</v>
+        <v>7135195</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6064,10 +6069,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119966726</v>
+        <v>119950857</v>
       </c>
       <c r="B53" t="n">
-        <v>79636</v>
+        <v>78262</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6076,41 +6081,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503285</v>
+        <v>503168</v>
       </c>
       <c r="R53" t="n">
-        <v>7134565</v>
+        <v>7134856</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6166,10 +6171,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119966722</v>
+        <v>119953290</v>
       </c>
       <c r="B54" t="n">
-        <v>89633</v>
+        <v>79642</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6178,41 +6183,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503218</v>
+        <v>503235</v>
       </c>
       <c r="R54" t="n">
-        <v>7134517</v>
+        <v>7135189</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6268,10 +6273,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119947013</v>
+        <v>119966731</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6284,37 +6289,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503258</v>
+        <v>503310</v>
       </c>
       <c r="R55" t="n">
-        <v>7134669</v>
+        <v>7134560</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6370,10 +6375,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119966724</v>
+        <v>119947043</v>
       </c>
       <c r="B56" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6382,41 +6387,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503195</v>
+        <v>503245</v>
       </c>
       <c r="R56" t="n">
-        <v>7134698</v>
+        <v>7134683</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6446,11 +6451,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6477,7 +6477,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119966744</v>
+        <v>119949113</v>
       </c>
       <c r="B57" t="n">
         <v>91840</v>
@@ -6513,17 +6513,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503354</v>
+        <v>503213</v>
       </c>
       <c r="R57" t="n">
-        <v>7134553</v>
+        <v>7134599</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119966746</v>
+        <v>119945137</v>
       </c>
       <c r="B58" t="n">
         <v>91840</v>
@@ -6615,17 +6615,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503256</v>
+        <v>503172</v>
       </c>
       <c r="R58" t="n">
-        <v>7134674</v>
+        <v>7134763</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119948976</v>
+        <v>119948938</v>
       </c>
       <c r="B59" t="n">
         <v>89633</v>
@@ -6721,13 +6721,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503222</v>
+        <v>503207</v>
       </c>
       <c r="R59" t="n">
-        <v>7134576</v>
+        <v>7134561</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119947114</v>
+        <v>119966719</v>
       </c>
       <c r="B60" t="n">
-        <v>78171</v>
+        <v>90527</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6795,41 +6795,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503256</v>
+        <v>503312</v>
       </c>
       <c r="R60" t="n">
-        <v>7134674</v>
+        <v>7134559</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6885,10 +6885,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119945243</v>
+        <v>119945252</v>
       </c>
       <c r="B61" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6901,21 +6901,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503165</v>
+        <v>503166</v>
       </c>
       <c r="R61" t="n">
-        <v>7134719</v>
+        <v>7134711</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119966741</v>
+        <v>119966728</v>
       </c>
       <c r="B62" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7003,21 +7003,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503195</v>
+        <v>503285</v>
       </c>
       <c r="R62" t="n">
-        <v>7134698</v>
+        <v>7134565</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119945075</v>
+        <v>119953361</v>
       </c>
       <c r="B63" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7105,37 +7105,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503170</v>
+        <v>503283</v>
       </c>
       <c r="R63" t="n">
-        <v>7134825</v>
+        <v>7135226</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119949016</v>
+        <v>119947013</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7203,25 +7203,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503196</v>
+        <v>503258</v>
       </c>
       <c r="R64" t="n">
-        <v>7134584</v>
+        <v>7134669</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7293,10 +7293,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119945215</v>
+        <v>119966749</v>
       </c>
       <c r="B65" t="n">
-        <v>91840</v>
+        <v>4915</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7305,41 +7305,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>101994</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503171</v>
+        <v>503364</v>
       </c>
       <c r="R65" t="n">
-        <v>7134729</v>
+        <v>7134522</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7369,6 +7369,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7395,10 +7400,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119948938</v>
+        <v>119950732</v>
       </c>
       <c r="B66" t="n">
-        <v>89633</v>
+        <v>79115</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7411,21 +7416,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7435,10 +7440,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503207</v>
+        <v>503146</v>
       </c>
       <c r="R66" t="n">
-        <v>7134561</v>
+        <v>7134809</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7497,10 +7502,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119944998</v>
+        <v>119953353</v>
       </c>
       <c r="B67" t="n">
-        <v>78262</v>
+        <v>90527</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7509,41 +7514,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503182</v>
+        <v>503265</v>
       </c>
       <c r="R67" t="n">
-        <v>7134859</v>
+        <v>7135233</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7599,10 +7604,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966742</v>
+        <v>119945075</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7611,41 +7616,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503371</v>
+        <v>503170</v>
       </c>
       <c r="R68" t="n">
-        <v>7134522</v>
+        <v>7134825</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7701,10 +7706,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119966719</v>
+        <v>119945215</v>
       </c>
       <c r="B69" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7717,37 +7722,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503312</v>
+        <v>503171</v>
       </c>
       <c r="R69" t="n">
-        <v>7134559</v>
+        <v>7134729</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7803,10 +7808,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119966731</v>
+        <v>119949136</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>57463</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7819,34 +7824,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503310</v>
+        <v>503213</v>
       </c>
       <c r="R70" t="n">
-        <v>7134560</v>
+        <v>7134603</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7905,10 +7915,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119945137</v>
+        <v>119944974</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7917,25 +7927,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7945,10 +7955,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503172</v>
+        <v>503197</v>
       </c>
       <c r="R71" t="n">
-        <v>7134763</v>
+        <v>7134847</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8007,10 +8017,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119950972</v>
+        <v>119953313</v>
       </c>
       <c r="B72" t="n">
-        <v>91883</v>
+        <v>79608</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8023,34 +8033,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5448</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503157</v>
+        <v>503239</v>
       </c>
       <c r="R72" t="n">
-        <v>7134940</v>
+        <v>7135198</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8109,10 +8119,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119966734</v>
+        <v>119950727</v>
       </c>
       <c r="B73" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8125,37 +8135,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503386</v>
+        <v>503147</v>
       </c>
       <c r="R73" t="n">
-        <v>7134487</v>
+        <v>7134810</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8211,10 +8221,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119947043</v>
+        <v>119948845</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8223,25 +8233,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8251,10 +8261,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503245</v>
+        <v>503204</v>
       </c>
       <c r="R74" t="n">
-        <v>7134683</v>
+        <v>7134543</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8313,10 +8323,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119951025</v>
+        <v>119945243</v>
       </c>
       <c r="B75" t="n">
-        <v>92030</v>
+        <v>78171</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8329,21 +8339,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8353,13 +8363,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503166</v>
+        <v>503165</v>
       </c>
       <c r="R75" t="n">
-        <v>7134990</v>
+        <v>7134719</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8415,10 +8425,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119953375</v>
+        <v>119953316</v>
       </c>
       <c r="B76" t="n">
-        <v>78171</v>
+        <v>79636</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8427,25 +8437,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8455,10 +8465,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503279</v>
+        <v>503249</v>
       </c>
       <c r="R76" t="n">
-        <v>7135237</v>
+        <v>7135183</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8517,10 +8527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966749</v>
+        <v>119947114</v>
       </c>
       <c r="B77" t="n">
-        <v>4915</v>
+        <v>78171</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8533,37 +8543,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>101994</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503364</v>
+        <v>503256</v>
       </c>
       <c r="R77" t="n">
-        <v>7134522</v>
+        <v>7134674</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8593,11 +8603,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8624,10 +8629,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119947387</v>
+        <v>119966732</v>
       </c>
       <c r="B78" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8640,37 +8645,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503210</v>
+        <v>503285</v>
       </c>
       <c r="R78" t="n">
-        <v>7134632</v>
+        <v>7135231</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8726,10 +8731,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119966737</v>
+        <v>119950972</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>91883</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8742,37 +8747,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503354</v>
+        <v>503157</v>
       </c>
       <c r="R79" t="n">
-        <v>7134564</v>
+        <v>7134940</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8828,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119950932</v>
+        <v>119966720</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8840,41 +8845,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503151</v>
+        <v>503241</v>
       </c>
       <c r="R80" t="n">
-        <v>7134896</v>
+        <v>7134650</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8930,10 +8935,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119966747</v>
+        <v>119949016</v>
       </c>
       <c r="B81" t="n">
-        <v>12337</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8942,41 +8947,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>101283</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503341</v>
+        <v>503196</v>
       </c>
       <c r="R81" t="n">
-        <v>7134550</v>
+        <v>7134584</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9006,11 +9011,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119950732</v>
+        <v>119966742</v>
       </c>
       <c r="B82" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9049,41 +9049,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503146</v>
+        <v>503371</v>
       </c>
       <c r="R82" t="n">
-        <v>7134809</v>
+        <v>7134522</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119947387</v>
+        <v>119966729</v>
       </c>
       <c r="B36" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,37 +4346,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503210</v>
+        <v>503291</v>
       </c>
       <c r="R36" t="n">
-        <v>7134632</v>
+        <v>7135241</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119947420</v>
+        <v>119966740</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,41 +4444,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503213</v>
+        <v>503194</v>
       </c>
       <c r="R37" t="n">
-        <v>7134622</v>
+        <v>7134678</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119966729</v>
+        <v>119950704</v>
       </c>
       <c r="B38" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,41 +4546,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503291</v>
+        <v>503155</v>
       </c>
       <c r="R38" t="n">
-        <v>7135241</v>
+        <v>7134772</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119966740</v>
+        <v>119947387</v>
       </c>
       <c r="B41" t="n">
         <v>78171</v>
@@ -4876,17 +4876,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503194</v>
+        <v>503210</v>
       </c>
       <c r="R41" t="n">
-        <v>7134678</v>
+        <v>7134632</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119950704</v>
+        <v>119947420</v>
       </c>
       <c r="B42" t="n">
         <v>91840</v>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503155</v>
+        <v>503213</v>
       </c>
       <c r="R42" t="n">
-        <v>7134772</v>
+        <v>7134622</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966722</v>
+        <v>119944998</v>
       </c>
       <c r="B46" t="n">
-        <v>89633</v>
+        <v>78262</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5366,37 +5366,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503218</v>
+        <v>503182</v>
       </c>
       <c r="R46" t="n">
-        <v>7134517</v>
+        <v>7134859</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119944998</v>
+        <v>119966722</v>
       </c>
       <c r="B48" t="n">
-        <v>78262</v>
+        <v>89633</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5570,37 +5570,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503182</v>
+        <v>503218</v>
       </c>
       <c r="R48" t="n">
-        <v>7134859</v>
+        <v>7134517</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6375,10 +6375,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119947043</v>
+        <v>119966719</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6391,37 +6391,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503245</v>
+        <v>503312</v>
       </c>
       <c r="R56" t="n">
-        <v>7134683</v>
+        <v>7134559</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119949113</v>
+        <v>119947043</v>
       </c>
       <c r="B57" t="n">
         <v>91840</v>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503213</v>
+        <v>503245</v>
       </c>
       <c r="R57" t="n">
-        <v>7134599</v>
+        <v>7134683</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6579,7 +6579,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119945137</v>
+        <v>119949113</v>
       </c>
       <c r="B58" t="n">
         <v>91840</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503172</v>
+        <v>503213</v>
       </c>
       <c r="R58" t="n">
-        <v>7134763</v>
+        <v>7134599</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119948938</v>
+        <v>119945137</v>
       </c>
       <c r="B59" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6693,25 +6693,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6721,13 +6721,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503207</v>
+        <v>503172</v>
       </c>
       <c r="R59" t="n">
-        <v>7134561</v>
+        <v>7134763</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119966719</v>
+        <v>119948938</v>
       </c>
       <c r="B60" t="n">
-        <v>90527</v>
+        <v>89633</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6795,41 +6795,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503312</v>
+        <v>503207</v>
       </c>
       <c r="R60" t="n">
-        <v>7134559</v>
+        <v>7134561</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8527,10 +8527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119947114</v>
+        <v>119966732</v>
       </c>
       <c r="B77" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8543,37 +8543,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503256</v>
+        <v>503285</v>
       </c>
       <c r="R77" t="n">
-        <v>7134674</v>
+        <v>7135231</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119966732</v>
+        <v>119950972</v>
       </c>
       <c r="B78" t="n">
-        <v>79607</v>
+        <v>91883</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8645,37 +8645,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>5448</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503285</v>
+        <v>503157</v>
       </c>
       <c r="R78" t="n">
-        <v>7135231</v>
+        <v>7134940</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119950972</v>
+        <v>119966720</v>
       </c>
       <c r="B79" t="n">
-        <v>91883</v>
+        <v>79115</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8747,37 +8747,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5448</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503157</v>
+        <v>503241</v>
       </c>
       <c r="R79" t="n">
-        <v>7134940</v>
+        <v>7134650</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119966720</v>
+        <v>119947114</v>
       </c>
       <c r="B80" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8849,37 +8849,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503241</v>
+        <v>503256</v>
       </c>
       <c r="R80" t="n">
-        <v>7134650</v>
+        <v>7134674</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119944976</v>
+        <v>119949136</v>
       </c>
       <c r="B15" t="n">
-        <v>78262</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,37 +2199,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503197</v>
+        <v>503213</v>
       </c>
       <c r="R15" t="n">
-        <v>7134856</v>
+        <v>7134603</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2285,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119966734</v>
+        <v>119953375</v>
       </c>
       <c r="B16" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,37 +2306,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503386</v>
+        <v>503279</v>
       </c>
       <c r="R16" t="n">
-        <v>7134487</v>
+        <v>7135237</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119966747</v>
+        <v>119966734</v>
       </c>
       <c r="B17" t="n">
-        <v>12337</v>
+        <v>78262</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,25 +2404,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101283</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2427,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503341</v>
+        <v>503386</v>
       </c>
       <c r="R17" t="n">
-        <v>7134550</v>
+        <v>7134487</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,11 +2468,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119945198</v>
+        <v>119953290</v>
       </c>
       <c r="B18" t="n">
-        <v>78262</v>
+        <v>79642</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2506,41 +2506,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503176</v>
+        <v>503235</v>
       </c>
       <c r="R18" t="n">
-        <v>7134750</v>
+        <v>7135189</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119950932</v>
+        <v>119966740</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2710,41 +2710,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503151</v>
+        <v>503194</v>
       </c>
       <c r="R20" t="n">
-        <v>7134896</v>
+        <v>7134678</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966748</v>
+        <v>119953361</v>
       </c>
       <c r="B21" t="n">
-        <v>79642</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2812,41 +2812,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503392</v>
+        <v>503283</v>
       </c>
       <c r="R21" t="n">
-        <v>7134464</v>
+        <v>7135226</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119946999</v>
+        <v>119953353</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,41 +2914,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503249</v>
+        <v>503265</v>
       </c>
       <c r="R22" t="n">
-        <v>7134683</v>
+        <v>7135233</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119948911</v>
+        <v>119966743</v>
       </c>
       <c r="B23" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,41 +3016,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503190</v>
+        <v>503321</v>
       </c>
       <c r="R23" t="n">
-        <v>7134550</v>
+        <v>7134576</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119944992</v>
+        <v>119950877</v>
       </c>
       <c r="B24" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3118,25 +3118,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3146,13 +3146,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503182</v>
+        <v>503166</v>
       </c>
       <c r="R24" t="n">
-        <v>7134856</v>
+        <v>7134864</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119950975</v>
+        <v>119966739</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3220,41 +3220,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503152</v>
+        <v>503196</v>
       </c>
       <c r="R25" t="n">
-        <v>7134944</v>
+        <v>7134493</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966744</v>
+        <v>119953313</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3322,41 +3322,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503354</v>
+        <v>503239</v>
       </c>
       <c r="R26" t="n">
-        <v>7134553</v>
+        <v>7135198</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119966737</v>
+        <v>119966729</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503354</v>
+        <v>503291</v>
       </c>
       <c r="R27" t="n">
-        <v>7134564</v>
+        <v>7135241</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950877</v>
+        <v>119966728</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,41 +3526,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503166</v>
+        <v>503285</v>
       </c>
       <c r="R28" t="n">
-        <v>7134864</v>
+        <v>7134565</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950521</v>
+        <v>119948976</v>
       </c>
       <c r="B29" t="n">
-        <v>79115</v>
+        <v>89633</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3632,21 +3632,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503238</v>
+        <v>503222</v>
       </c>
       <c r="R29" t="n">
-        <v>7134692</v>
+        <v>7134576</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3718,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950926</v>
+        <v>119950857</v>
       </c>
       <c r="B30" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503153</v>
+        <v>503168</v>
       </c>
       <c r="R30" t="n">
-        <v>7134897</v>
+        <v>7134856</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119953375</v>
+        <v>119966722</v>
       </c>
       <c r="B31" t="n">
-        <v>78171</v>
+        <v>89633</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3836,37 +3836,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503279</v>
+        <v>503218</v>
       </c>
       <c r="R31" t="n">
-        <v>7135237</v>
+        <v>7134517</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119953277</v>
+        <v>119947043</v>
       </c>
       <c r="B32" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,41 +3934,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503236</v>
+        <v>503245</v>
       </c>
       <c r="R32" t="n">
-        <v>7135178</v>
+        <v>7134683</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119966741</v>
+        <v>119947420</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,41 +4036,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503195</v>
+        <v>503213</v>
       </c>
       <c r="R33" t="n">
-        <v>7134698</v>
+        <v>7134622</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119966733</v>
+        <v>119950975</v>
       </c>
       <c r="B34" t="n">
-        <v>79643</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4142,37 +4142,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503392</v>
+        <v>503152</v>
       </c>
       <c r="R34" t="n">
-        <v>7134464</v>
+        <v>7134944</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119966735</v>
+        <v>119966742</v>
       </c>
       <c r="B35" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,25 +4240,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4271,7 +4271,7 @@
         <v>503371</v>
       </c>
       <c r="R35" t="n">
-        <v>7134532</v>
+        <v>7134522</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119966729</v>
+        <v>119966744</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,25 +4342,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503291</v>
+        <v>503354</v>
       </c>
       <c r="R36" t="n">
-        <v>7135241</v>
+        <v>7134553</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119966740</v>
+        <v>119949113</v>
       </c>
       <c r="B37" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,41 +4444,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503194</v>
+        <v>503213</v>
       </c>
       <c r="R37" t="n">
-        <v>7134678</v>
+        <v>7134599</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950704</v>
+        <v>119951025</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,13 +4574,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503155</v>
+        <v>503166</v>
       </c>
       <c r="R38" t="n">
-        <v>7134772</v>
+        <v>7134990</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119950802</v>
+        <v>119947387</v>
       </c>
       <c r="B39" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,21 +4652,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503165</v>
+        <v>503210</v>
       </c>
       <c r="R39" t="n">
-        <v>7134812</v>
+        <v>7134632</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119953208</v>
+        <v>119946999</v>
       </c>
       <c r="B40" t="n">
-        <v>79608</v>
+        <v>79115</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4754,34 +4754,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503164</v>
+        <v>503249</v>
       </c>
       <c r="R40" t="n">
-        <v>7135128</v>
+        <v>7134683</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119947387</v>
+        <v>119966746</v>
       </c>
       <c r="B41" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4852,41 +4852,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503210</v>
+        <v>503256</v>
       </c>
       <c r="R41" t="n">
-        <v>7134632</v>
+        <v>7134674</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119947420</v>
+        <v>119953208</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4954,38 +4954,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503213</v>
+        <v>503164</v>
       </c>
       <c r="R42" t="n">
-        <v>7134622</v>
+        <v>7135128</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119966726</v>
+        <v>119950926</v>
       </c>
       <c r="B43" t="n">
-        <v>79636</v>
+        <v>79115</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5056,41 +5056,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503285</v>
+        <v>503153</v>
       </c>
       <c r="R43" t="n">
-        <v>7134565</v>
+        <v>7134897</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966739</v>
+        <v>119966726</v>
       </c>
       <c r="B44" t="n">
-        <v>78171</v>
+        <v>79636</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5158,25 +5158,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5186,10 +5186,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503196</v>
+        <v>503285</v>
       </c>
       <c r="R44" t="n">
-        <v>7134493</v>
+        <v>7134565</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119951025</v>
+        <v>119950521</v>
       </c>
       <c r="B45" t="n">
-        <v>92030</v>
+        <v>79115</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5264,21 +5264,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5288,13 +5288,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503166</v>
+        <v>503238</v>
       </c>
       <c r="R45" t="n">
-        <v>7134990</v>
+        <v>7134692</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119944998</v>
+        <v>119945215</v>
       </c>
       <c r="B46" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,25 +5362,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503182</v>
+        <v>503171</v>
       </c>
       <c r="R46" t="n">
-        <v>7134859</v>
+        <v>7134729</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119948976</v>
+        <v>119948938</v>
       </c>
       <c r="B47" t="n">
         <v>89633</v>
@@ -5492,13 +5492,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503222</v>
+        <v>503207</v>
       </c>
       <c r="R47" t="n">
-        <v>7134576</v>
+        <v>7134561</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119966722</v>
+        <v>119966733</v>
       </c>
       <c r="B48" t="n">
-        <v>89633</v>
+        <v>79643</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5566,25 +5566,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5594,10 +5594,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503218</v>
+        <v>503392</v>
       </c>
       <c r="R48" t="n">
-        <v>7134517</v>
+        <v>7134464</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119966724</v>
+        <v>119948845</v>
       </c>
       <c r="B49" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5672,37 +5672,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503195</v>
+        <v>503204</v>
       </c>
       <c r="R49" t="n">
-        <v>7134698</v>
+        <v>7134543</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5732,11 +5732,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5763,10 +5758,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119966743</v>
+        <v>119950732</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5775,41 +5770,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503321</v>
+        <v>503146</v>
       </c>
       <c r="R50" t="n">
-        <v>7134576</v>
+        <v>7134809</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5865,7 +5860,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119966746</v>
+        <v>119950932</v>
       </c>
       <c r="B51" t="n">
         <v>91840</v>
@@ -5901,17 +5896,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503256</v>
+        <v>503151</v>
       </c>
       <c r="R51" t="n">
-        <v>7134674</v>
+        <v>7134896</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5967,10 +5962,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119953308</v>
+        <v>119945198</v>
       </c>
       <c r="B52" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5983,34 +5978,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503244</v>
+        <v>503176</v>
       </c>
       <c r="R52" t="n">
-        <v>7135195</v>
+        <v>7134750</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6069,7 +6064,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119950857</v>
+        <v>119944976</v>
       </c>
       <c r="B53" t="n">
         <v>78262</v>
@@ -6109,13 +6104,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503168</v>
+        <v>503197</v>
       </c>
       <c r="R53" t="n">
         <v>7134856</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6171,10 +6166,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119953290</v>
+        <v>119944974</v>
       </c>
       <c r="B54" t="n">
-        <v>79642</v>
+        <v>78171</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6183,41 +6178,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503235</v>
+        <v>503197</v>
       </c>
       <c r="R54" t="n">
-        <v>7135189</v>
+        <v>7134847</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6273,10 +6268,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119966731</v>
+        <v>119966749</v>
       </c>
       <c r="B55" t="n">
-        <v>78263</v>
+        <v>4915</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6289,21 +6284,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>101994</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6313,10 +6308,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503310</v>
+        <v>503364</v>
       </c>
       <c r="R55" t="n">
-        <v>7134560</v>
+        <v>7134522</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6349,6 +6344,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6375,10 +6375,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119966719</v>
+        <v>119953308</v>
       </c>
       <c r="B56" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6387,41 +6387,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503312</v>
+        <v>503244</v>
       </c>
       <c r="R56" t="n">
-        <v>7134559</v>
+        <v>7135195</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119947043</v>
+        <v>119950972</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6489,25 +6489,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503245</v>
+        <v>503157</v>
       </c>
       <c r="R57" t="n">
-        <v>7134683</v>
+        <v>7134940</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6579,10 +6579,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119949113</v>
+        <v>119945243</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6591,25 +6591,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503213</v>
+        <v>503165</v>
       </c>
       <c r="R58" t="n">
-        <v>7134599</v>
+        <v>7134719</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119945137</v>
+        <v>119953316</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>79636</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6697,34 +6697,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503172</v>
+        <v>503249</v>
       </c>
       <c r="R59" t="n">
-        <v>7134763</v>
+        <v>7135183</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119948938</v>
+        <v>119947013</v>
       </c>
       <c r="B60" t="n">
-        <v>89633</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6799,21 +6799,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503207</v>
+        <v>503258</v>
       </c>
       <c r="R60" t="n">
-        <v>7134561</v>
+        <v>7134669</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6885,10 +6885,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119945252</v>
+        <v>119945075</v>
       </c>
       <c r="B61" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6901,21 +6901,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503166</v>
+        <v>503170</v>
       </c>
       <c r="R61" t="n">
-        <v>7134711</v>
+        <v>7134825</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119966728</v>
+        <v>119944992</v>
       </c>
       <c r="B62" t="n">
-        <v>79608</v>
+        <v>79115</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7003,37 +7003,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503285</v>
+        <v>503182</v>
       </c>
       <c r="R62" t="n">
-        <v>7134565</v>
+        <v>7134856</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119953361</v>
+        <v>119966724</v>
       </c>
       <c r="B63" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7105,37 +7105,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503283</v>
+        <v>503195</v>
       </c>
       <c r="R63" t="n">
-        <v>7135226</v>
+        <v>7134698</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7165,6 +7165,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7191,10 +7196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119947013</v>
+        <v>119949016</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7203,25 +7208,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7231,13 +7236,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503258</v>
+        <v>503196</v>
       </c>
       <c r="R64" t="n">
-        <v>7134669</v>
+        <v>7134584</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7293,10 +7298,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119966749</v>
+        <v>119950704</v>
       </c>
       <c r="B65" t="n">
-        <v>4915</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7305,41 +7310,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>101994</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503364</v>
+        <v>503155</v>
       </c>
       <c r="R65" t="n">
-        <v>7134522</v>
+        <v>7134772</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7369,11 +7374,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7400,10 +7400,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119950732</v>
+        <v>119966719</v>
       </c>
       <c r="B66" t="n">
-        <v>79115</v>
+        <v>90527</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7412,41 +7412,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503146</v>
+        <v>503312</v>
       </c>
       <c r="R66" t="n">
-        <v>7134809</v>
+        <v>7134559</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119953353</v>
+        <v>119944998</v>
       </c>
       <c r="B67" t="n">
-        <v>90527</v>
+        <v>78262</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7514,41 +7514,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503265</v>
+        <v>503182</v>
       </c>
       <c r="R67" t="n">
-        <v>7135233</v>
+        <v>7134859</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7604,10 +7604,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119945075</v>
+        <v>119966735</v>
       </c>
       <c r="B68" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7620,37 +7620,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503170</v>
+        <v>503371</v>
       </c>
       <c r="R68" t="n">
-        <v>7134825</v>
+        <v>7134532</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119945215</v>
+        <v>119945252</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7718,25 +7718,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7746,13 +7746,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503171</v>
+        <v>503166</v>
       </c>
       <c r="R69" t="n">
-        <v>7134729</v>
+        <v>7134711</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119949136</v>
+        <v>119966731</v>
       </c>
       <c r="B70" t="n">
-        <v>57463</v>
+        <v>78263</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7824,39 +7824,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503213</v>
+        <v>503310</v>
       </c>
       <c r="R70" t="n">
-        <v>7134603</v>
+        <v>7134560</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7915,7 +7910,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119944974</v>
+        <v>119947114</v>
       </c>
       <c r="B71" t="n">
         <v>78171</v>
@@ -7955,10 +7950,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503197</v>
+        <v>503256</v>
       </c>
       <c r="R71" t="n">
-        <v>7134847</v>
+        <v>7134674</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8017,7 +8012,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119953313</v>
+        <v>119953277</v>
       </c>
       <c r="B72" t="n">
         <v>79608</v>
@@ -8057,13 +8052,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503239</v>
+        <v>503236</v>
       </c>
       <c r="R72" t="n">
-        <v>7135198</v>
+        <v>7135178</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8119,10 +8114,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119950727</v>
+        <v>119966741</v>
       </c>
       <c r="B73" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8135,37 +8130,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503147</v>
+        <v>503195</v>
       </c>
       <c r="R73" t="n">
-        <v>7134810</v>
+        <v>7134698</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8221,10 +8216,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119948845</v>
+        <v>119966747</v>
       </c>
       <c r="B74" t="n">
-        <v>78171</v>
+        <v>12337</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8233,41 +8228,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>101283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503204</v>
+        <v>503341</v>
       </c>
       <c r="R74" t="n">
-        <v>7134543</v>
+        <v>7134550</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8297,6 +8292,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8323,10 +8323,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119945243</v>
+        <v>119966748</v>
       </c>
       <c r="B75" t="n">
-        <v>78171</v>
+        <v>79642</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8335,41 +8335,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503165</v>
+        <v>503392</v>
       </c>
       <c r="R75" t="n">
-        <v>7134719</v>
+        <v>7134464</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119953316</v>
+        <v>119966720</v>
       </c>
       <c r="B76" t="n">
-        <v>79636</v>
+        <v>79115</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8437,41 +8437,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503249</v>
+        <v>503241</v>
       </c>
       <c r="R76" t="n">
-        <v>7135183</v>
+        <v>7134650</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8527,10 +8527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966732</v>
+        <v>119950802</v>
       </c>
       <c r="B77" t="n">
-        <v>79607</v>
+        <v>89633</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8543,37 +8543,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503285</v>
+        <v>503165</v>
       </c>
       <c r="R77" t="n">
-        <v>7135231</v>
+        <v>7134812</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119950972</v>
+        <v>119966737</v>
       </c>
       <c r="B78" t="n">
-        <v>91883</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8645,37 +8645,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5448</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503157</v>
+        <v>503354</v>
       </c>
       <c r="R78" t="n">
-        <v>7134940</v>
+        <v>7134564</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119966720</v>
+        <v>119966732</v>
       </c>
       <c r="B79" t="n">
-        <v>79115</v>
+        <v>79607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8747,21 +8747,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503241</v>
+        <v>503285</v>
       </c>
       <c r="R79" t="n">
-        <v>7134650</v>
+        <v>7135231</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119947114</v>
+        <v>119950727</v>
       </c>
       <c r="B80" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8849,21 +8849,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8873,13 +8873,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503256</v>
+        <v>503147</v>
       </c>
       <c r="R80" t="n">
-        <v>7134674</v>
+        <v>7134810</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119949016</v>
+        <v>119945137</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503196</v>
+        <v>503172</v>
       </c>
       <c r="R81" t="n">
-        <v>7134584</v>
+        <v>7134763</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119966742</v>
+        <v>119948911</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9049,41 +9049,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503371</v>
+        <v>503190</v>
       </c>
       <c r="R82" t="n">
-        <v>7134522</v>
+        <v>7134550</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2698,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119966740</v>
+        <v>119966743</v>
       </c>
       <c r="B20" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2710,25 +2710,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503194</v>
+        <v>503321</v>
       </c>
       <c r="R20" t="n">
-        <v>7134678</v>
+        <v>7134576</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119953361</v>
+        <v>119966740</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,37 +2816,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503283</v>
+        <v>503194</v>
       </c>
       <c r="R21" t="n">
-        <v>7135226</v>
+        <v>7134678</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119953353</v>
+        <v>119953361</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,25 +2914,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503265</v>
+        <v>503283</v>
       </c>
       <c r="R22" t="n">
-        <v>7135233</v>
+        <v>7135226</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119966743</v>
+        <v>119953353</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,37 +3020,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503321</v>
+        <v>503265</v>
       </c>
       <c r="R23" t="n">
-        <v>7134576</v>
+        <v>7135233</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119949113</v>
+        <v>119951025</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,25 +4444,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4472,13 +4472,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503213</v>
+        <v>503166</v>
       </c>
       <c r="R37" t="n">
-        <v>7134599</v>
+        <v>7134990</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119951025</v>
+        <v>119949113</v>
       </c>
       <c r="B38" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,13 +4574,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503166</v>
+        <v>503213</v>
       </c>
       <c r="R38" t="n">
-        <v>7134990</v>
+        <v>7134599</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119945215</v>
+        <v>119948845</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,25 +5362,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503171</v>
+        <v>503204</v>
       </c>
       <c r="R46" t="n">
-        <v>7134729</v>
+        <v>7134543</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119948938</v>
+        <v>119945215</v>
       </c>
       <c r="B47" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5464,25 +5464,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5492,13 +5492,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503207</v>
+        <v>503171</v>
       </c>
       <c r="R47" t="n">
-        <v>7134561</v>
+        <v>7134729</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119966733</v>
+        <v>119948938</v>
       </c>
       <c r="B48" t="n">
-        <v>79643</v>
+        <v>89633</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5566,41 +5566,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503392</v>
+        <v>503207</v>
       </c>
       <c r="R48" t="n">
-        <v>7134464</v>
+        <v>7134561</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119948845</v>
+        <v>119966733</v>
       </c>
       <c r="B49" t="n">
-        <v>78171</v>
+        <v>79643</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5668,41 +5668,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503204</v>
+        <v>503392</v>
       </c>
       <c r="R49" t="n">
-        <v>7134543</v>
+        <v>7134464</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119950932</v>
+        <v>119944976</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5872,25 +5872,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503151</v>
+        <v>503197</v>
       </c>
       <c r="R51" t="n">
-        <v>7134896</v>
+        <v>7134856</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6064,10 +6064,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119944976</v>
+        <v>119944974</v>
       </c>
       <c r="B53" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6080,21 +6080,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
         <v>503197</v>
       </c>
       <c r="R53" t="n">
-        <v>7134856</v>
+        <v>7134847</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6166,10 +6166,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119944974</v>
+        <v>119950932</v>
       </c>
       <c r="B54" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6178,25 +6178,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503197</v>
+        <v>503151</v>
       </c>
       <c r="R54" t="n">
-        <v>7134847</v>
+        <v>7134896</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119966724</v>
+        <v>119966719</v>
       </c>
       <c r="B63" t="n">
-        <v>57463</v>
+        <v>90527</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7101,25 +7101,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7129,10 +7129,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503195</v>
+        <v>503312</v>
       </c>
       <c r="R63" t="n">
-        <v>7134698</v>
+        <v>7134559</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7165,11 +7165,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7400,10 +7395,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119966719</v>
+        <v>119966724</v>
       </c>
       <c r="B66" t="n">
-        <v>90527</v>
+        <v>57463</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7412,25 +7407,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7440,10 +7435,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503312</v>
+        <v>503195</v>
       </c>
       <c r="R66" t="n">
-        <v>7134559</v>
+        <v>7134698</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7476,6 +7471,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8425,10 +8425,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966720</v>
+        <v>119966732</v>
       </c>
       <c r="B76" t="n">
-        <v>79115</v>
+        <v>79607</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8441,21 +8441,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8465,10 +8465,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503241</v>
+        <v>503285</v>
       </c>
       <c r="R76" t="n">
-        <v>7134650</v>
+        <v>7135231</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8527,10 +8527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119950802</v>
+        <v>119966720</v>
       </c>
       <c r="B77" t="n">
-        <v>89633</v>
+        <v>79115</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8543,37 +8543,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503165</v>
+        <v>503241</v>
       </c>
       <c r="R77" t="n">
-        <v>7134812</v>
+        <v>7134650</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119966737</v>
+        <v>119950802</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8645,37 +8645,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503354</v>
+        <v>503165</v>
       </c>
       <c r="R78" t="n">
-        <v>7134564</v>
+        <v>7134812</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119966732</v>
+        <v>119966737</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8747,21 +8747,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503285</v>
+        <v>503354</v>
       </c>
       <c r="R79" t="n">
-        <v>7135231</v>
+        <v>7134564</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119950727</v>
+        <v>119945137</v>
       </c>
       <c r="B80" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8845,25 +8845,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8873,13 +8873,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503147</v>
+        <v>503172</v>
       </c>
       <c r="R80" t="n">
-        <v>7134810</v>
+        <v>7134763</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119945137</v>
+        <v>119948911</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8947,25 +8947,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503172</v>
+        <v>503190</v>
       </c>
       <c r="R81" t="n">
-        <v>7134763</v>
+        <v>7134550</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119948911</v>
+        <v>119950727</v>
       </c>
       <c r="B82" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,21 +9053,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9077,13 +9077,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503190</v>
+        <v>503147</v>
       </c>
       <c r="R82" t="n">
-        <v>7134550</v>
+        <v>7134810</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119949136</v>
+        <v>119951025</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>92030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,42 +2199,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503213</v>
+        <v>503166</v>
       </c>
       <c r="R15" t="n">
-        <v>7134603</v>
+        <v>7134990</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2290,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119953375</v>
+        <v>119950926</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,37 +2301,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503279</v>
+        <v>503153</v>
       </c>
       <c r="R16" t="n">
-        <v>7135237</v>
+        <v>7134897</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119966734</v>
+        <v>119944992</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,37 +2403,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503386</v>
+        <v>503182</v>
       </c>
       <c r="R17" t="n">
-        <v>7134487</v>
+        <v>7134856</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2494,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119953290</v>
+        <v>119953353</v>
       </c>
       <c r="B18" t="n">
-        <v>79642</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,21 +2505,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2534,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503235</v>
+        <v>503265</v>
       </c>
       <c r="R18" t="n">
-        <v>7135189</v>
+        <v>7135233</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119948853</v>
+        <v>119966726</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>79636</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,37 +2607,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503204</v>
+        <v>503285</v>
       </c>
       <c r="R19" t="n">
-        <v>7134538</v>
+        <v>7134565</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119966743</v>
+        <v>119945198</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2710,41 +2705,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503321</v>
+        <v>503176</v>
       </c>
       <c r="R20" t="n">
-        <v>7134576</v>
+        <v>7134750</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2800,7 +2795,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966740</v>
+        <v>119947114</v>
       </c>
       <c r="B21" t="n">
         <v>78171</v>
@@ -2836,17 +2831,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503194</v>
+        <v>503256</v>
       </c>
       <c r="R21" t="n">
-        <v>7134678</v>
+        <v>7134674</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2902,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119953361</v>
+        <v>119950521</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>79115</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2918,37 +2913,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503283</v>
+        <v>503238</v>
       </c>
       <c r="R22" t="n">
-        <v>7135226</v>
+        <v>7134692</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3004,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119953353</v>
+        <v>119946999</v>
       </c>
       <c r="B23" t="n">
-        <v>90527</v>
+        <v>79115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,41 +3011,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503265</v>
+        <v>503249</v>
       </c>
       <c r="R23" t="n">
-        <v>7135233</v>
+        <v>7134683</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3106,10 +3101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119950877</v>
+        <v>119945252</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3118,25 +3113,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3149,7 +3144,7 @@
         <v>503166</v>
       </c>
       <c r="R24" t="n">
-        <v>7134864</v>
+        <v>7134711</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3208,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119966739</v>
+        <v>119966747</v>
       </c>
       <c r="B25" t="n">
-        <v>78171</v>
+        <v>12337</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3220,25 +3215,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>101283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503196</v>
+        <v>503341</v>
       </c>
       <c r="R25" t="n">
-        <v>7134493</v>
+        <v>7134550</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3284,6 +3279,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119953313</v>
+        <v>119966732</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503239</v>
+        <v>503285</v>
       </c>
       <c r="R26" t="n">
-        <v>7135198</v>
+        <v>7135231</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119966729</v>
+        <v>119950727</v>
       </c>
       <c r="B27" t="n">
-        <v>79608</v>
+        <v>78263</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3428,37 +3428,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503291</v>
+        <v>503147</v>
       </c>
       <c r="R27" t="n">
-        <v>7135241</v>
+        <v>7134810</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119966728</v>
+        <v>119950704</v>
       </c>
       <c r="B28" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,41 +3526,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503285</v>
+        <v>503155</v>
       </c>
       <c r="R28" t="n">
-        <v>7134565</v>
+        <v>7134772</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119948976</v>
+        <v>119966742</v>
       </c>
       <c r="B29" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3628,41 +3628,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503222</v>
+        <v>503371</v>
       </c>
       <c r="R29" t="n">
-        <v>7134576</v>
+        <v>7134522</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3718,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950857</v>
+        <v>119945137</v>
       </c>
       <c r="B30" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3730,25 +3730,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503168</v>
+        <v>503172</v>
       </c>
       <c r="R30" t="n">
-        <v>7134856</v>
+        <v>7134763</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119966722</v>
+        <v>119944974</v>
       </c>
       <c r="B31" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3836,37 +3836,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503218</v>
+        <v>503197</v>
       </c>
       <c r="R31" t="n">
-        <v>7134517</v>
+        <v>7134847</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119947043</v>
+        <v>119953375</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,38 +3934,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503245</v>
+        <v>503279</v>
       </c>
       <c r="R32" t="n">
-        <v>7134683</v>
+        <v>7135237</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119947420</v>
+        <v>119950975</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503213</v>
+        <v>503152</v>
       </c>
       <c r="R33" t="n">
-        <v>7134622</v>
+        <v>7134944</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950975</v>
+        <v>119947387</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4138,25 +4138,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503152</v>
+        <v>503210</v>
       </c>
       <c r="R34" t="n">
-        <v>7134944</v>
+        <v>7134632</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119966742</v>
+        <v>119953208</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,41 +4240,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503371</v>
+        <v>503164</v>
       </c>
       <c r="R35" t="n">
-        <v>7134522</v>
+        <v>7135128</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119966744</v>
+        <v>119966748</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>79642</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503354</v>
+        <v>503392</v>
       </c>
       <c r="R36" t="n">
-        <v>7134553</v>
+        <v>7134464</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119951025</v>
+        <v>119949136</v>
       </c>
       <c r="B37" t="n">
-        <v>92030</v>
+        <v>57463</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4448,37 +4448,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503166</v>
+        <v>503213</v>
       </c>
       <c r="R37" t="n">
-        <v>7134990</v>
+        <v>7134603</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,7 +4539,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119949113</v>
+        <v>119947420</v>
       </c>
       <c r="B38" t="n">
         <v>91840</v>
@@ -4577,7 +4582,7 @@
         <v>503213</v>
       </c>
       <c r="R38" t="n">
-        <v>7134599</v>
+        <v>7134622</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4636,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119947387</v>
+        <v>119947013</v>
       </c>
       <c r="B39" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,21 +4657,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,13 +4681,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503210</v>
+        <v>503258</v>
       </c>
       <c r="R39" t="n">
-        <v>7134632</v>
+        <v>7134669</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4738,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119946999</v>
+        <v>119966743</v>
       </c>
       <c r="B40" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4750,41 +4755,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503249</v>
+        <v>503321</v>
       </c>
       <c r="R40" t="n">
-        <v>7134683</v>
+        <v>7134576</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4840,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119966746</v>
+        <v>119953308</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4852,41 +4857,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503256</v>
+        <v>503244</v>
       </c>
       <c r="R41" t="n">
-        <v>7134674</v>
+        <v>7135195</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4942,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119953208</v>
+        <v>119950857</v>
       </c>
       <c r="B42" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4958,37 +4963,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503164</v>
+        <v>503168</v>
       </c>
       <c r="R42" t="n">
-        <v>7135128</v>
+        <v>7134856</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5044,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119950926</v>
+        <v>119966740</v>
       </c>
       <c r="B43" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5060,37 +5065,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503153</v>
+        <v>503194</v>
       </c>
       <c r="R43" t="n">
-        <v>7134897</v>
+        <v>7134678</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5146,10 +5151,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966726</v>
+        <v>119966737</v>
       </c>
       <c r="B44" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5158,25 +5163,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5186,10 +5191,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503285</v>
+        <v>503354</v>
       </c>
       <c r="R44" t="n">
-        <v>7134565</v>
+        <v>7134564</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5248,10 +5253,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119950521</v>
+        <v>119948845</v>
       </c>
       <c r="B45" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5264,21 +5269,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5288,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503238</v>
+        <v>503204</v>
       </c>
       <c r="R45" t="n">
-        <v>7134692</v>
+        <v>7134543</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5350,10 +5355,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119948845</v>
+        <v>119949113</v>
       </c>
       <c r="B46" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,25 +5367,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5390,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503204</v>
+        <v>503213</v>
       </c>
       <c r="R46" t="n">
-        <v>7134543</v>
+        <v>7134599</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5452,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119945215</v>
+        <v>119966728</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5464,41 +5469,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503171</v>
+        <v>503285</v>
       </c>
       <c r="R47" t="n">
-        <v>7134729</v>
+        <v>7134565</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5554,10 +5559,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119948938</v>
+        <v>119949016</v>
       </c>
       <c r="B48" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5566,25 +5571,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5594,13 +5599,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503207</v>
+        <v>503196</v>
       </c>
       <c r="R48" t="n">
-        <v>7134561</v>
+        <v>7134584</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5656,10 +5661,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119966733</v>
+        <v>119947043</v>
       </c>
       <c r="B49" t="n">
-        <v>79643</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5672,37 +5677,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503392</v>
+        <v>503245</v>
       </c>
       <c r="R49" t="n">
-        <v>7134464</v>
+        <v>7134683</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5758,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119950732</v>
+        <v>119966746</v>
       </c>
       <c r="B50" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5770,41 +5775,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503146</v>
+        <v>503256</v>
       </c>
       <c r="R50" t="n">
-        <v>7134809</v>
+        <v>7134674</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5860,10 +5865,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119944976</v>
+        <v>119966724</v>
       </c>
       <c r="B51" t="n">
-        <v>78262</v>
+        <v>57463</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5876,37 +5881,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503197</v>
+        <v>503195</v>
       </c>
       <c r="R51" t="n">
-        <v>7134856</v>
+        <v>7134698</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5936,6 +5941,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5962,10 +5972,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119945198</v>
+        <v>119945075</v>
       </c>
       <c r="B52" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5978,21 +5988,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6002,10 +6012,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503176</v>
+        <v>503170</v>
       </c>
       <c r="R52" t="n">
-        <v>7134750</v>
+        <v>7134825</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6064,10 +6074,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119944974</v>
+        <v>119953361</v>
       </c>
       <c r="B53" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6080,37 +6090,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503197</v>
+        <v>503283</v>
       </c>
       <c r="R53" t="n">
-        <v>7134847</v>
+        <v>7135226</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6166,7 +6176,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119950932</v>
+        <v>119950877</v>
       </c>
       <c r="B54" t="n">
         <v>91840</v>
@@ -6206,10 +6216,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503151</v>
+        <v>503166</v>
       </c>
       <c r="R54" t="n">
-        <v>7134896</v>
+        <v>7134864</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6268,10 +6278,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119966749</v>
+        <v>119966744</v>
       </c>
       <c r="B55" t="n">
-        <v>4915</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6280,25 +6290,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101994</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6308,10 +6318,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503364</v>
+        <v>503354</v>
       </c>
       <c r="R55" t="n">
-        <v>7134522</v>
+        <v>7134553</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6344,11 +6354,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6375,10 +6380,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119953308</v>
+        <v>119953277</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6391,21 +6396,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6415,13 +6420,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503244</v>
+        <v>503236</v>
       </c>
       <c r="R56" t="n">
-        <v>7135195</v>
+        <v>7135178</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6477,10 +6482,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119950972</v>
+        <v>119950932</v>
       </c>
       <c r="B57" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6489,25 +6494,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6517,10 +6522,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503157</v>
+        <v>503151</v>
       </c>
       <c r="R57" t="n">
-        <v>7134940</v>
+        <v>7134896</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6579,10 +6584,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119945243</v>
+        <v>119966720</v>
       </c>
       <c r="B58" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6595,37 +6600,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503165</v>
+        <v>503241</v>
       </c>
       <c r="R58" t="n">
-        <v>7134719</v>
+        <v>7134650</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6681,10 +6686,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119953316</v>
+        <v>119950972</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>91883</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6693,38 +6698,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>5448</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503249</v>
+        <v>503157</v>
       </c>
       <c r="R59" t="n">
-        <v>7135183</v>
+        <v>7134940</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6783,10 +6788,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119947013</v>
+        <v>119966735</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6799,37 +6804,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503258</v>
+        <v>503371</v>
       </c>
       <c r="R60" t="n">
-        <v>7134669</v>
+        <v>7134532</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6885,10 +6890,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119945075</v>
+        <v>119948853</v>
       </c>
       <c r="B61" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6897,25 +6902,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6925,10 +6930,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503170</v>
+        <v>503204</v>
       </c>
       <c r="R61" t="n">
-        <v>7134825</v>
+        <v>7134538</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6987,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119944992</v>
+        <v>119948976</v>
       </c>
       <c r="B62" t="n">
-        <v>79115</v>
+        <v>89633</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7003,21 +7008,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7027,13 +7032,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503182</v>
+        <v>503222</v>
       </c>
       <c r="R62" t="n">
-        <v>7134856</v>
+        <v>7134576</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7089,10 +7094,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119966719</v>
+        <v>119945243</v>
       </c>
       <c r="B63" t="n">
-        <v>90527</v>
+        <v>78171</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7101,41 +7106,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503312</v>
+        <v>503165</v>
       </c>
       <c r="R63" t="n">
-        <v>7134559</v>
+        <v>7134719</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7191,10 +7196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119949016</v>
+        <v>119948911</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7203,25 +7208,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7231,10 +7236,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503196</v>
+        <v>503190</v>
       </c>
       <c r="R64" t="n">
-        <v>7134584</v>
+        <v>7134550</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7293,10 +7298,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119950704</v>
+        <v>119953290</v>
       </c>
       <c r="B65" t="n">
-        <v>91840</v>
+        <v>79642</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7309,37 +7314,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503155</v>
+        <v>503235</v>
       </c>
       <c r="R65" t="n">
-        <v>7134772</v>
+        <v>7135189</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7395,10 +7400,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119966724</v>
+        <v>119944976</v>
       </c>
       <c r="B66" t="n">
-        <v>57463</v>
+        <v>78262</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7411,37 +7416,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503195</v>
+        <v>503197</v>
       </c>
       <c r="R66" t="n">
-        <v>7134698</v>
+        <v>7134856</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7471,11 +7476,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7502,10 +7502,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119944998</v>
+        <v>119945215</v>
       </c>
       <c r="B67" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7514,25 +7514,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503182</v>
+        <v>503171</v>
       </c>
       <c r="R67" t="n">
-        <v>7134859</v>
+        <v>7134729</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7604,10 +7604,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966735</v>
+        <v>119966731</v>
       </c>
       <c r="B68" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7620,21 +7620,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503371</v>
+        <v>503310</v>
       </c>
       <c r="R68" t="n">
-        <v>7134532</v>
+        <v>7134560</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119945252</v>
+        <v>119966741</v>
       </c>
       <c r="B69" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7722,37 +7722,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503166</v>
+        <v>503195</v>
       </c>
       <c r="R69" t="n">
-        <v>7134711</v>
+        <v>7134698</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119966731</v>
+        <v>119948938</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>89633</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7824,37 +7824,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503310</v>
+        <v>503207</v>
       </c>
       <c r="R70" t="n">
-        <v>7134560</v>
+        <v>7134561</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119947114</v>
+        <v>119966739</v>
       </c>
       <c r="B71" t="n">
         <v>78171</v>
@@ -7946,17 +7946,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503256</v>
+        <v>503196</v>
       </c>
       <c r="R71" t="n">
-        <v>7134674</v>
+        <v>7134493</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8012,10 +8012,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119953277</v>
+        <v>119953316</v>
       </c>
       <c r="B72" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8024,25 +8024,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8052,13 +8052,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503236</v>
+        <v>503249</v>
       </c>
       <c r="R72" t="n">
-        <v>7135178</v>
+        <v>7135183</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119966741</v>
+        <v>119966733</v>
       </c>
       <c r="B73" t="n">
-        <v>78171</v>
+        <v>79643</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8126,25 +8126,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503195</v>
+        <v>503392</v>
       </c>
       <c r="R73" t="n">
-        <v>7134698</v>
+        <v>7134464</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8216,10 +8216,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119966747</v>
+        <v>119950802</v>
       </c>
       <c r="B74" t="n">
-        <v>12337</v>
+        <v>89633</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8228,41 +8228,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>101283</v>
+        <v>1962</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503341</v>
+        <v>503165</v>
       </c>
       <c r="R74" t="n">
-        <v>7134550</v>
+        <v>7134812</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8292,11 +8292,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8323,10 +8318,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119966748</v>
+        <v>119966734</v>
       </c>
       <c r="B75" t="n">
-        <v>79642</v>
+        <v>78262</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8335,25 +8330,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8363,10 +8358,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503392</v>
+        <v>503386</v>
       </c>
       <c r="R75" t="n">
-        <v>7134464</v>
+        <v>7134487</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8425,10 +8420,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966732</v>
+        <v>119966722</v>
       </c>
       <c r="B76" t="n">
-        <v>79607</v>
+        <v>89633</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8441,21 +8436,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8465,10 +8460,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503285</v>
+        <v>503218</v>
       </c>
       <c r="R76" t="n">
-        <v>7135231</v>
+        <v>7134517</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8527,10 +8522,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966720</v>
+        <v>119944998</v>
       </c>
       <c r="B77" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8543,37 +8538,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503241</v>
+        <v>503182</v>
       </c>
       <c r="R77" t="n">
-        <v>7134650</v>
+        <v>7134859</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8629,10 +8624,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119950802</v>
+        <v>119966719</v>
       </c>
       <c r="B78" t="n">
-        <v>89633</v>
+        <v>90527</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8641,41 +8636,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503165</v>
+        <v>503312</v>
       </c>
       <c r="R78" t="n">
-        <v>7134812</v>
+        <v>7134559</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8731,10 +8726,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119966737</v>
+        <v>119966749</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>4915</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8747,21 +8742,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>101994</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8771,10 +8766,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503354</v>
+        <v>503364</v>
       </c>
       <c r="R79" t="n">
-        <v>7134564</v>
+        <v>7134522</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8807,6 +8802,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119945137</v>
+        <v>119950732</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8845,25 +8845,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8873,13 +8873,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503172</v>
+        <v>503146</v>
       </c>
       <c r="R80" t="n">
-        <v>7134763</v>
+        <v>7134809</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119948911</v>
+        <v>119953313</v>
       </c>
       <c r="B81" t="n">
-        <v>79115</v>
+        <v>79608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8951,34 +8951,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503190</v>
+        <v>503239</v>
       </c>
       <c r="R81" t="n">
-        <v>7134550</v>
+        <v>7135198</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119950727</v>
+        <v>119966729</v>
       </c>
       <c r="B82" t="n">
-        <v>78263</v>
+        <v>79608</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,37 +9053,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503147</v>
+        <v>503291</v>
       </c>
       <c r="R82" t="n">
-        <v>7134810</v>
+        <v>7135241</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119953353</v>
+        <v>119950521</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>79115</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,41 +2501,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503265</v>
+        <v>503238</v>
       </c>
       <c r="R18" t="n">
-        <v>7135233</v>
+        <v>7134692</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119966726</v>
+        <v>119945198</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>78262</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,41 +2603,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503285</v>
+        <v>503176</v>
       </c>
       <c r="R19" t="n">
-        <v>7134565</v>
+        <v>7134750</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119945198</v>
+        <v>119947114</v>
       </c>
       <c r="B20" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503176</v>
+        <v>503256</v>
       </c>
       <c r="R20" t="n">
-        <v>7134750</v>
+        <v>7134674</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119947114</v>
+        <v>119953353</v>
       </c>
       <c r="B21" t="n">
-        <v>78171</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,41 +2807,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503256</v>
+        <v>503265</v>
       </c>
       <c r="R21" t="n">
-        <v>7134674</v>
+        <v>7135233</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950521</v>
+        <v>119966726</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>79636</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,41 +2909,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503238</v>
+        <v>503285</v>
       </c>
       <c r="R22" t="n">
-        <v>7134692</v>
+        <v>7134565</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119966747</v>
+        <v>119966732</v>
       </c>
       <c r="B25" t="n">
-        <v>12337</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101283</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503341</v>
+        <v>503285</v>
       </c>
       <c r="R25" t="n">
-        <v>7134550</v>
+        <v>7135231</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3279,11 +3279,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966732</v>
+        <v>119966747</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>12337</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3322,25 +3317,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>101283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503285</v>
+        <v>503341</v>
       </c>
       <c r="R26" t="n">
-        <v>7135231</v>
+        <v>7134550</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3386,6 +3381,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119953375</v>
+        <v>119950975</v>
       </c>
       <c r="B32" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,38 +3934,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503279</v>
+        <v>503152</v>
       </c>
       <c r="R32" t="n">
-        <v>7135237</v>
+        <v>7134944</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950975</v>
+        <v>119947387</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,25 +4036,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503152</v>
+        <v>503210</v>
       </c>
       <c r="R33" t="n">
-        <v>7134944</v>
+        <v>7134632</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119947387</v>
+        <v>119953375</v>
       </c>
       <c r="B34" t="n">
         <v>78171</v>
@@ -4162,14 +4162,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503210</v>
+        <v>503279</v>
       </c>
       <c r="R34" t="n">
-        <v>7134632</v>
+        <v>7135237</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119949136</v>
+        <v>119947013</v>
       </c>
       <c r="B37" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4448,42 +4448,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503213</v>
+        <v>503258</v>
       </c>
       <c r="R37" t="n">
-        <v>7134603</v>
+        <v>7134669</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4539,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119947420</v>
+        <v>119953308</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4551,38 +4546,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503213</v>
+        <v>503244</v>
       </c>
       <c r="R38" t="n">
-        <v>7134622</v>
+        <v>7135195</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4641,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119947013</v>
+        <v>119950857</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4657,21 +4652,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4681,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503258</v>
+        <v>503168</v>
       </c>
       <c r="R39" t="n">
-        <v>7134669</v>
+        <v>7134856</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,10 +4840,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119953308</v>
+        <v>119949136</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4861,37 +4856,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503244</v>
+        <v>503213</v>
       </c>
       <c r="R41" t="n">
-        <v>7135195</v>
+        <v>7134603</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119950857</v>
+        <v>119947420</v>
       </c>
       <c r="B42" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,25 +4959,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503168</v>
+        <v>503213</v>
       </c>
       <c r="R42" t="n">
-        <v>7134856</v>
+        <v>7134622</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5253,10 +5253,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119948845</v>
+        <v>119966728</v>
       </c>
       <c r="B45" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5269,37 +5269,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503204</v>
+        <v>503285</v>
       </c>
       <c r="R45" t="n">
-        <v>7134543</v>
+        <v>7134565</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119949113</v>
+        <v>119948845</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5367,25 +5367,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503213</v>
+        <v>503204</v>
       </c>
       <c r="R46" t="n">
-        <v>7134599</v>
+        <v>7134543</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966728</v>
+        <v>119949113</v>
       </c>
       <c r="B47" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5469,41 +5469,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503285</v>
+        <v>503213</v>
       </c>
       <c r="R47" t="n">
-        <v>7134565</v>
+        <v>7134599</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7298,10 +7298,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119953290</v>
+        <v>119944976</v>
       </c>
       <c r="B65" t="n">
-        <v>79642</v>
+        <v>78262</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7310,41 +7310,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503235</v>
+        <v>503197</v>
       </c>
       <c r="R65" t="n">
-        <v>7135189</v>
+        <v>7134856</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7400,10 +7400,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119944976</v>
+        <v>119953290</v>
       </c>
       <c r="B66" t="n">
-        <v>78262</v>
+        <v>79642</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7412,41 +7412,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503197</v>
+        <v>503235</v>
       </c>
       <c r="R66" t="n">
-        <v>7134856</v>
+        <v>7135189</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7604,10 +7604,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966731</v>
+        <v>119966741</v>
       </c>
       <c r="B68" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7620,21 +7620,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503310</v>
+        <v>503195</v>
       </c>
       <c r="R68" t="n">
-        <v>7134560</v>
+        <v>7134698</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119966741</v>
+        <v>119966731</v>
       </c>
       <c r="B69" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7722,21 +7722,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503195</v>
+        <v>503310</v>
       </c>
       <c r="R69" t="n">
-        <v>7134698</v>
+        <v>7134560</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119948938</v>
+        <v>119966739</v>
       </c>
       <c r="B70" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7824,37 +7824,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503207</v>
+        <v>503196</v>
       </c>
       <c r="R70" t="n">
-        <v>7134561</v>
+        <v>7134493</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7910,10 +7910,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119966739</v>
+        <v>119953316</v>
       </c>
       <c r="B71" t="n">
-        <v>78171</v>
+        <v>79636</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7922,41 +7922,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503196</v>
+        <v>503249</v>
       </c>
       <c r="R71" t="n">
-        <v>7134493</v>
+        <v>7135183</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8012,10 +8012,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119953316</v>
+        <v>119966733</v>
       </c>
       <c r="B72" t="n">
-        <v>79636</v>
+        <v>79643</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8028,37 +8028,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503249</v>
+        <v>503392</v>
       </c>
       <c r="R72" t="n">
-        <v>7135183</v>
+        <v>7134464</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119966733</v>
+        <v>119950802</v>
       </c>
       <c r="B73" t="n">
-        <v>79643</v>
+        <v>89633</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8126,41 +8126,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503392</v>
+        <v>503165</v>
       </c>
       <c r="R73" t="n">
-        <v>7134464</v>
+        <v>7134812</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119950802</v>
+        <v>119948938</v>
       </c>
       <c r="B74" t="n">
         <v>89633</v>
@@ -8256,10 +8256,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503165</v>
+        <v>503207</v>
       </c>
       <c r="R74" t="n">
-        <v>7134812</v>
+        <v>7134561</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119950521</v>
+        <v>119953353</v>
       </c>
       <c r="B18" t="n">
-        <v>79115</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,41 +2501,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503238</v>
+        <v>503265</v>
       </c>
       <c r="R18" t="n">
-        <v>7134692</v>
+        <v>7135233</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119945198</v>
+        <v>119966726</v>
       </c>
       <c r="B19" t="n">
-        <v>78262</v>
+        <v>79636</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,41 +2603,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503176</v>
+        <v>503285</v>
       </c>
       <c r="R19" t="n">
-        <v>7134750</v>
+        <v>7134565</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119947114</v>
+        <v>119945198</v>
       </c>
       <c r="B20" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503256</v>
+        <v>503176</v>
       </c>
       <c r="R20" t="n">
-        <v>7134674</v>
+        <v>7134750</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119953353</v>
+        <v>119947114</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>78171</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,41 +2807,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503265</v>
+        <v>503256</v>
       </c>
       <c r="R21" t="n">
-        <v>7135233</v>
+        <v>7134674</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119966726</v>
+        <v>119950521</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>79115</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,41 +2909,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503285</v>
+        <v>503238</v>
       </c>
       <c r="R22" t="n">
-        <v>7134565</v>
+        <v>7134692</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119966732</v>
+        <v>119966747</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>12337</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>101283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503285</v>
+        <v>503341</v>
       </c>
       <c r="R25" t="n">
-        <v>7135231</v>
+        <v>7134550</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3279,6 +3279,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3305,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966747</v>
+        <v>119966732</v>
       </c>
       <c r="B26" t="n">
-        <v>12337</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3317,25 +3322,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101283</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503341</v>
+        <v>503285</v>
       </c>
       <c r="R26" t="n">
-        <v>7134550</v>
+        <v>7135231</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3381,11 +3386,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119950727</v>
+        <v>119944974</v>
       </c>
       <c r="B27" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,13 +3452,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503147</v>
+        <v>503197</v>
       </c>
       <c r="R27" t="n">
-        <v>7134810</v>
+        <v>7134847</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950704</v>
+        <v>119945137</v>
       </c>
       <c r="B28" t="n">
         <v>91840</v>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503155</v>
+        <v>503172</v>
       </c>
       <c r="R28" t="n">
-        <v>7134772</v>
+        <v>7134763</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3616,7 +3616,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119966742</v>
+        <v>119950704</v>
       </c>
       <c r="B29" t="n">
         <v>91840</v>
@@ -3652,17 +3652,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503371</v>
+        <v>503155</v>
       </c>
       <c r="R29" t="n">
-        <v>7134522</v>
+        <v>7134772</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3718,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119945137</v>
+        <v>119950727</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3730,25 +3730,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503172</v>
+        <v>503147</v>
       </c>
       <c r="R30" t="n">
-        <v>7134763</v>
+        <v>7134810</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119944974</v>
+        <v>119966742</v>
       </c>
       <c r="B31" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,41 +3832,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503197</v>
+        <v>503371</v>
       </c>
       <c r="R31" t="n">
-        <v>7134847</v>
+        <v>7134522</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950975</v>
+        <v>119953375</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,38 +3934,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503152</v>
+        <v>503279</v>
       </c>
       <c r="R32" t="n">
-        <v>7134944</v>
+        <v>7135237</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119947387</v>
+        <v>119950975</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,25 +4036,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503210</v>
+        <v>503152</v>
       </c>
       <c r="R33" t="n">
-        <v>7134632</v>
+        <v>7134944</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119953375</v>
+        <v>119947387</v>
       </c>
       <c r="B34" t="n">
         <v>78171</v>
@@ -4162,14 +4162,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503279</v>
+        <v>503210</v>
       </c>
       <c r="R34" t="n">
-        <v>7135237</v>
+        <v>7134632</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -5253,10 +5253,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119966728</v>
+        <v>119948845</v>
       </c>
       <c r="B45" t="n">
-        <v>79608</v>
+        <v>78171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5269,37 +5269,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503285</v>
+        <v>503204</v>
       </c>
       <c r="R45" t="n">
-        <v>7134565</v>
+        <v>7134543</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119948845</v>
+        <v>119949113</v>
       </c>
       <c r="B46" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5367,25 +5367,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503204</v>
+        <v>503213</v>
       </c>
       <c r="R46" t="n">
-        <v>7134543</v>
+        <v>7134599</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119949113</v>
+        <v>119966728</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5469,41 +5469,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503213</v>
+        <v>503285</v>
       </c>
       <c r="R47" t="n">
-        <v>7134599</v>
+        <v>7134565</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6074,10 +6074,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119953361</v>
+        <v>119950877</v>
       </c>
       <c r="B53" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6086,41 +6086,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503283</v>
+        <v>503166</v>
       </c>
       <c r="R53" t="n">
-        <v>7135226</v>
+        <v>7134864</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119950877</v>
+        <v>119966744</v>
       </c>
       <c r="B54" t="n">
         <v>91840</v>
@@ -6212,17 +6212,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503166</v>
+        <v>503354</v>
       </c>
       <c r="R54" t="n">
-        <v>7134864</v>
+        <v>7134553</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6278,10 +6278,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119966744</v>
+        <v>119953361</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6290,41 +6290,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503354</v>
+        <v>503283</v>
       </c>
       <c r="R55" t="n">
-        <v>7134553</v>
+        <v>7135226</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119950972</v>
+        <v>119948976</v>
       </c>
       <c r="B59" t="n">
-        <v>91883</v>
+        <v>89633</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6702,21 +6702,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5448</v>
+        <v>1962</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503157</v>
+        <v>503222</v>
       </c>
       <c r="R59" t="n">
-        <v>7134940</v>
+        <v>7134576</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6788,10 +6788,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119966735</v>
+        <v>119945243</v>
       </c>
       <c r="B60" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6804,37 +6804,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503371</v>
+        <v>503165</v>
       </c>
       <c r="R60" t="n">
-        <v>7134532</v>
+        <v>7134719</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119948976</v>
+        <v>119950972</v>
       </c>
       <c r="B62" t="n">
-        <v>89633</v>
+        <v>91883</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7008,21 +7008,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>5448</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7032,10 +7032,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503222</v>
+        <v>503157</v>
       </c>
       <c r="R62" t="n">
-        <v>7134576</v>
+        <v>7134940</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7094,10 +7094,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119945243</v>
+        <v>119966735</v>
       </c>
       <c r="B63" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7110,37 +7110,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503165</v>
+        <v>503371</v>
       </c>
       <c r="R63" t="n">
-        <v>7134719</v>
+        <v>7134532</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7604,10 +7604,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966741</v>
+        <v>119966731</v>
       </c>
       <c r="B68" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7620,21 +7620,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503195</v>
+        <v>503310</v>
       </c>
       <c r="R68" t="n">
-        <v>7134698</v>
+        <v>7134560</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119966731</v>
+        <v>119966741</v>
       </c>
       <c r="B69" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7722,21 +7722,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503310</v>
+        <v>503195</v>
       </c>
       <c r="R69" t="n">
-        <v>7134560</v>
+        <v>7134698</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119966739</v>
+        <v>119948938</v>
       </c>
       <c r="B70" t="n">
-        <v>78171</v>
+        <v>89633</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7824,37 +7824,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503196</v>
+        <v>503207</v>
       </c>
       <c r="R70" t="n">
-        <v>7134493</v>
+        <v>7134561</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7910,10 +7910,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119953316</v>
+        <v>119966739</v>
       </c>
       <c r="B71" t="n">
-        <v>79636</v>
+        <v>78171</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7922,41 +7922,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503249</v>
+        <v>503196</v>
       </c>
       <c r="R71" t="n">
-        <v>7135183</v>
+        <v>7134493</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8012,10 +8012,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119966733</v>
+        <v>119953316</v>
       </c>
       <c r="B72" t="n">
-        <v>79643</v>
+        <v>79636</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8028,37 +8028,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503392</v>
+        <v>503249</v>
       </c>
       <c r="R72" t="n">
-        <v>7134464</v>
+        <v>7135183</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119950802</v>
+        <v>119966733</v>
       </c>
       <c r="B73" t="n">
-        <v>89633</v>
+        <v>79643</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8126,41 +8126,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1962</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503165</v>
+        <v>503392</v>
       </c>
       <c r="R73" t="n">
-        <v>7134812</v>
+        <v>7134464</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119948938</v>
+        <v>119950802</v>
       </c>
       <c r="B74" t="n">
         <v>89633</v>
@@ -8256,10 +8256,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503207</v>
+        <v>503165</v>
       </c>
       <c r="R74" t="n">
-        <v>7134561</v>
+        <v>7134812</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119953353</v>
+        <v>119950521</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>79115</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,41 +2501,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503265</v>
+        <v>503238</v>
       </c>
       <c r="R18" t="n">
-        <v>7135233</v>
+        <v>7134692</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119966726</v>
+        <v>119945198</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>78262</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,41 +2603,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503285</v>
+        <v>503176</v>
       </c>
       <c r="R19" t="n">
-        <v>7134565</v>
+        <v>7134750</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119945198</v>
+        <v>119947114</v>
       </c>
       <c r="B20" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503176</v>
+        <v>503256</v>
       </c>
       <c r="R20" t="n">
-        <v>7134750</v>
+        <v>7134674</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119947114</v>
+        <v>119953353</v>
       </c>
       <c r="B21" t="n">
-        <v>78171</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,41 +2807,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503256</v>
+        <v>503265</v>
       </c>
       <c r="R21" t="n">
-        <v>7134674</v>
+        <v>7135233</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950521</v>
+        <v>119966726</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>79636</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,41 +2909,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503238</v>
+        <v>503285</v>
       </c>
       <c r="R22" t="n">
-        <v>7134692</v>
+        <v>7134565</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119966747</v>
+        <v>119966732</v>
       </c>
       <c r="B25" t="n">
-        <v>12337</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101283</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503341</v>
+        <v>503285</v>
       </c>
       <c r="R25" t="n">
-        <v>7134550</v>
+        <v>7135231</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3279,11 +3279,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966732</v>
+        <v>119966747</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>12337</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3322,25 +3317,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>101283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503285</v>
+        <v>503341</v>
       </c>
       <c r="R26" t="n">
-        <v>7135231</v>
+        <v>7134550</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3386,6 +3381,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119953375</v>
+        <v>119950975</v>
       </c>
       <c r="B32" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,38 +3934,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503279</v>
+        <v>503152</v>
       </c>
       <c r="R32" t="n">
-        <v>7135237</v>
+        <v>7134944</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950975</v>
+        <v>119953375</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,38 +4036,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503152</v>
+        <v>503279</v>
       </c>
       <c r="R33" t="n">
-        <v>7134944</v>
+        <v>7135237</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119950732</v>
+        <v>119953313</v>
       </c>
       <c r="B80" t="n">
-        <v>79115</v>
+        <v>79608</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8849,37 +8849,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503146</v>
+        <v>503239</v>
       </c>
       <c r="R80" t="n">
-        <v>7134809</v>
+        <v>7135198</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119953313</v>
+        <v>119966729</v>
       </c>
       <c r="B81" t="n">
         <v>79608</v>
@@ -8971,17 +8971,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503239</v>
+        <v>503291</v>
       </c>
       <c r="R81" t="n">
-        <v>7135198</v>
+        <v>7135241</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119966729</v>
+        <v>119950732</v>
       </c>
       <c r="B82" t="n">
-        <v>79608</v>
+        <v>79115</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,37 +9053,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503291</v>
+        <v>503146</v>
       </c>
       <c r="R82" t="n">
-        <v>7135241</v>
+        <v>7134809</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950975</v>
+        <v>119953375</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,38 +3934,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503152</v>
+        <v>503279</v>
       </c>
       <c r="R32" t="n">
-        <v>7134944</v>
+        <v>7135237</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119953375</v>
+        <v>119950975</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,38 +4036,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503279</v>
+        <v>503152</v>
       </c>
       <c r="R33" t="n">
-        <v>7135237</v>
+        <v>7134944</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119953208</v>
+        <v>119966748</v>
       </c>
       <c r="B35" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,41 +4240,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503164</v>
+        <v>503392</v>
       </c>
       <c r="R35" t="n">
-        <v>7135128</v>
+        <v>7134464</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119966748</v>
+        <v>119953208</v>
       </c>
       <c r="B36" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,41 +4342,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503392</v>
+        <v>503164</v>
       </c>
       <c r="R36" t="n">
-        <v>7134464</v>
+        <v>7135128</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5253,10 +5253,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119948845</v>
+        <v>119966728</v>
       </c>
       <c r="B45" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5269,37 +5269,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503204</v>
+        <v>503285</v>
       </c>
       <c r="R45" t="n">
-        <v>7134543</v>
+        <v>7134565</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119949113</v>
+        <v>119948845</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5367,25 +5367,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503213</v>
+        <v>503204</v>
       </c>
       <c r="R46" t="n">
-        <v>7134599</v>
+        <v>7134543</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966728</v>
+        <v>119949113</v>
       </c>
       <c r="B47" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5469,41 +5469,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503285</v>
+        <v>503213</v>
       </c>
       <c r="R47" t="n">
-        <v>7134565</v>
+        <v>7134599</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119948976</v>
+        <v>119950972</v>
       </c>
       <c r="B59" t="n">
-        <v>89633</v>
+        <v>91883</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6702,21 +6702,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1962</v>
+        <v>5448</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503222</v>
+        <v>503157</v>
       </c>
       <c r="R59" t="n">
-        <v>7134576</v>
+        <v>7134940</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6788,10 +6788,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119945243</v>
+        <v>119966735</v>
       </c>
       <c r="B60" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6804,37 +6804,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503165</v>
+        <v>503371</v>
       </c>
       <c r="R60" t="n">
-        <v>7134719</v>
+        <v>7134532</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119950972</v>
+        <v>119948976</v>
       </c>
       <c r="B62" t="n">
-        <v>91883</v>
+        <v>89633</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7008,21 +7008,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5448</v>
+        <v>1962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7032,10 +7032,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503157</v>
+        <v>503222</v>
       </c>
       <c r="R62" t="n">
-        <v>7134940</v>
+        <v>7134576</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7094,10 +7094,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119966735</v>
+        <v>119945243</v>
       </c>
       <c r="B63" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7110,37 +7110,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503371</v>
+        <v>503165</v>
       </c>
       <c r="R63" t="n">
-        <v>7134532</v>
+        <v>7134719</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7604,10 +7604,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966731</v>
+        <v>119966741</v>
       </c>
       <c r="B68" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7620,21 +7620,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503310</v>
+        <v>503195</v>
       </c>
       <c r="R68" t="n">
-        <v>7134560</v>
+        <v>7134698</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119966741</v>
+        <v>119966731</v>
       </c>
       <c r="B69" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7722,21 +7722,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503195</v>
+        <v>503310</v>
       </c>
       <c r="R69" t="n">
-        <v>7134698</v>
+        <v>7134560</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119953313</v>
+        <v>119950732</v>
       </c>
       <c r="B80" t="n">
-        <v>79608</v>
+        <v>79115</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8849,37 +8849,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503239</v>
+        <v>503146</v>
       </c>
       <c r="R80" t="n">
-        <v>7135198</v>
+        <v>7134809</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119966729</v>
+        <v>119953313</v>
       </c>
       <c r="B81" t="n">
         <v>79608</v>
@@ -8971,17 +8971,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503291</v>
+        <v>503239</v>
       </c>
       <c r="R81" t="n">
-        <v>7135241</v>
+        <v>7135198</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119950732</v>
+        <v>119966729</v>
       </c>
       <c r="B82" t="n">
-        <v>79115</v>
+        <v>79608</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,37 +9053,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503146</v>
+        <v>503291</v>
       </c>
       <c r="R82" t="n">
-        <v>7134809</v>
+        <v>7135241</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119966732</v>
+        <v>119966747</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>12337</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>101283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503285</v>
+        <v>503341</v>
       </c>
       <c r="R25" t="n">
-        <v>7135231</v>
+        <v>7134550</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3279,6 +3279,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3305,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966747</v>
+        <v>119966732</v>
       </c>
       <c r="B26" t="n">
-        <v>12337</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3317,25 +3322,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101283</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503341</v>
+        <v>503285</v>
       </c>
       <c r="R26" t="n">
-        <v>7134550</v>
+        <v>7135231</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3381,11 +3386,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119953375</v>
+        <v>119950975</v>
       </c>
       <c r="B32" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,38 +3934,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503279</v>
+        <v>503152</v>
       </c>
       <c r="R32" t="n">
-        <v>7135237</v>
+        <v>7134944</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950975</v>
+        <v>119953375</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,38 +4036,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503152</v>
+        <v>503279</v>
       </c>
       <c r="R33" t="n">
-        <v>7134944</v>
+        <v>7135237</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119947013</v>
+        <v>119949136</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4448,37 +4448,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503258</v>
+        <v>503213</v>
       </c>
       <c r="R37" t="n">
-        <v>7134669</v>
+        <v>7134603</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119953308</v>
+        <v>119947420</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,38 +4551,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503244</v>
+        <v>503213</v>
       </c>
       <c r="R38" t="n">
-        <v>7135195</v>
+        <v>7134622</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4636,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119950857</v>
+        <v>119947013</v>
       </c>
       <c r="B39" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,21 +4657,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4681,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503168</v>
+        <v>503258</v>
       </c>
       <c r="R39" t="n">
-        <v>7134856</v>
+        <v>7134669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4840,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119949136</v>
+        <v>119953308</v>
       </c>
       <c r="B41" t="n">
-        <v>57463</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4856,42 +4861,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503213</v>
+        <v>503244</v>
       </c>
       <c r="R41" t="n">
-        <v>7134603</v>
+        <v>7135195</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119947420</v>
+        <v>119950857</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,25 +4959,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503213</v>
+        <v>503168</v>
       </c>
       <c r="R42" t="n">
-        <v>7134622</v>
+        <v>7134856</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6074,10 +6074,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119950877</v>
+        <v>119953361</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6086,41 +6086,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503166</v>
+        <v>503283</v>
       </c>
       <c r="R53" t="n">
-        <v>7134864</v>
+        <v>7135226</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119966744</v>
+        <v>119950877</v>
       </c>
       <c r="B54" t="n">
         <v>91840</v>
@@ -6212,17 +6212,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503354</v>
+        <v>503166</v>
       </c>
       <c r="R54" t="n">
-        <v>7134553</v>
+        <v>7134864</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6278,10 +6278,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119953361</v>
+        <v>119966744</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6290,41 +6290,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503283</v>
+        <v>503354</v>
       </c>
       <c r="R55" t="n">
-        <v>7135226</v>
+        <v>7134553</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119948938</v>
+        <v>119966739</v>
       </c>
       <c r="B70" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7824,37 +7824,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503207</v>
+        <v>503196</v>
       </c>
       <c r="R70" t="n">
-        <v>7134561</v>
+        <v>7134493</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7910,10 +7910,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119966739</v>
+        <v>119953316</v>
       </c>
       <c r="B71" t="n">
-        <v>78171</v>
+        <v>79636</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7922,41 +7922,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503196</v>
+        <v>503249</v>
       </c>
       <c r="R71" t="n">
-        <v>7134493</v>
+        <v>7135183</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8012,10 +8012,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119953316</v>
+        <v>119966733</v>
       </c>
       <c r="B72" t="n">
-        <v>79636</v>
+        <v>79643</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8028,37 +8028,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503249</v>
+        <v>503392</v>
       </c>
       <c r="R72" t="n">
-        <v>7135183</v>
+        <v>7134464</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119966733</v>
+        <v>119950802</v>
       </c>
       <c r="B73" t="n">
-        <v>79643</v>
+        <v>89633</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8126,41 +8126,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503392</v>
+        <v>503165</v>
       </c>
       <c r="R73" t="n">
-        <v>7134464</v>
+        <v>7134812</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119950802</v>
+        <v>119948938</v>
       </c>
       <c r="B74" t="n">
         <v>89633</v>
@@ -8256,10 +8256,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503165</v>
+        <v>503207</v>
       </c>
       <c r="R74" t="n">
-        <v>7134812</v>
+        <v>7134561</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -5253,10 +5253,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119966728</v>
+        <v>119948845</v>
       </c>
       <c r="B45" t="n">
-        <v>79608</v>
+        <v>78171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5269,37 +5269,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503285</v>
+        <v>503204</v>
       </c>
       <c r="R45" t="n">
-        <v>7134565</v>
+        <v>7134543</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119948845</v>
+        <v>119949113</v>
       </c>
       <c r="B46" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5367,25 +5367,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503204</v>
+        <v>503213</v>
       </c>
       <c r="R46" t="n">
-        <v>7134543</v>
+        <v>7134599</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119949113</v>
+        <v>119966728</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5469,41 +5469,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503213</v>
+        <v>503285</v>
       </c>
       <c r="R47" t="n">
-        <v>7134599</v>
+        <v>7134565</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119951025</v>
+        <v>119944974</v>
       </c>
       <c r="B15" t="n">
-        <v>92030</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503166</v>
+        <v>503197</v>
       </c>
       <c r="R15" t="n">
-        <v>7134990</v>
+        <v>7134847</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119950926</v>
+        <v>119945075</v>
       </c>
       <c r="B16" t="n">
-        <v>79115</v>
+        <v>78187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503153</v>
+        <v>503170</v>
       </c>
       <c r="R16" t="n">
-        <v>7134897</v>
+        <v>7134825</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119944992</v>
+        <v>119953353</v>
       </c>
       <c r="B17" t="n">
-        <v>79115</v>
+        <v>90545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,41 +2399,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503182</v>
+        <v>503265</v>
       </c>
       <c r="R17" t="n">
-        <v>7134856</v>
+        <v>7135233</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119950521</v>
+        <v>119948938</v>
       </c>
       <c r="B18" t="n">
-        <v>79115</v>
+        <v>89650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,13 +2529,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503238</v>
+        <v>503207</v>
       </c>
       <c r="R18" t="n">
-        <v>7134692</v>
+        <v>7134561</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119945198</v>
+        <v>119950704</v>
       </c>
       <c r="B19" t="n">
-        <v>78262</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503176</v>
+        <v>503155</v>
       </c>
       <c r="R19" t="n">
-        <v>7134750</v>
+        <v>7134772</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119947114</v>
+        <v>119966743</v>
       </c>
       <c r="B20" t="n">
-        <v>78171</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,41 +2705,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503256</v>
+        <v>503321</v>
       </c>
       <c r="R20" t="n">
-        <v>7134674</v>
+        <v>7134576</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119953353</v>
+        <v>119966747</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>12337</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,41 +2807,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>101283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503265</v>
+        <v>503341</v>
       </c>
       <c r="R21" t="n">
-        <v>7135233</v>
+        <v>7134550</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2871,6 +2871,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119966726</v>
+        <v>119966733</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>79659</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,21 +2918,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503285</v>
+        <v>503392</v>
       </c>
       <c r="R22" t="n">
-        <v>7134565</v>
+        <v>7134464</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119946999</v>
+        <v>119950802</v>
       </c>
       <c r="B23" t="n">
-        <v>79115</v>
+        <v>89650</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,21 +3020,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3039,13 +3044,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503249</v>
+        <v>503165</v>
       </c>
       <c r="R23" t="n">
-        <v>7134683</v>
+        <v>7134812</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119945252</v>
+        <v>119950857</v>
       </c>
       <c r="B24" t="n">
-        <v>79115</v>
+        <v>78278</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3117,21 +3122,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,13 +3146,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503166</v>
+        <v>503168</v>
       </c>
       <c r="R24" t="n">
-        <v>7134711</v>
+        <v>7134856</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,10 +3208,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119966747</v>
+        <v>119966732</v>
       </c>
       <c r="B25" t="n">
-        <v>12337</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,25 +3220,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101283</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503341</v>
+        <v>503285</v>
       </c>
       <c r="R25" t="n">
-        <v>7134550</v>
+        <v>7135231</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3279,11 +3284,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966732</v>
+        <v>119966737</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503285</v>
+        <v>503354</v>
       </c>
       <c r="R26" t="n">
-        <v>7135231</v>
+        <v>7134564</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119944974</v>
+        <v>119966734</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3428,37 +3428,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503197</v>
+        <v>503386</v>
       </c>
       <c r="R27" t="n">
-        <v>7134847</v>
+        <v>7134487</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119945137</v>
+        <v>119949016</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503172</v>
+        <v>503196</v>
       </c>
       <c r="R28" t="n">
-        <v>7134763</v>
+        <v>7134584</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950704</v>
+        <v>119945252</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>79131</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3628,25 +3628,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503155</v>
+        <v>503166</v>
       </c>
       <c r="R29" t="n">
-        <v>7134772</v>
+        <v>7134711</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3718,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950727</v>
+        <v>119950972</v>
       </c>
       <c r="B30" t="n">
-        <v>78263</v>
+        <v>91901</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>5448</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503147</v>
+        <v>503157</v>
       </c>
       <c r="R30" t="n">
-        <v>7134810</v>
+        <v>7134940</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119966742</v>
+        <v>119950732</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>79131</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,41 +3832,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503371</v>
+        <v>503146</v>
       </c>
       <c r="R31" t="n">
-        <v>7134522</v>
+        <v>7134809</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950975</v>
+        <v>119947114</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78187</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,25 +3934,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503152</v>
+        <v>503256</v>
       </c>
       <c r="R32" t="n">
-        <v>7134944</v>
+        <v>7134674</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119953375</v>
+        <v>119948845</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>78187</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,14 +4060,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503279</v>
+        <v>503204</v>
       </c>
       <c r="R33" t="n">
-        <v>7135237</v>
+        <v>7134543</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119947387</v>
+        <v>119948853</v>
       </c>
       <c r="B34" t="n">
-        <v>78171</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4138,25 +4138,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503210</v>
+        <v>503204</v>
       </c>
       <c r="R34" t="n">
-        <v>7134632</v>
+        <v>7134538</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119966748</v>
+        <v>119966746</v>
       </c>
       <c r="B35" t="n">
-        <v>79642</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503392</v>
+        <v>503256</v>
       </c>
       <c r="R35" t="n">
-        <v>7134464</v>
+        <v>7134674</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119953208</v>
+        <v>119949136</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
+        <v>57473</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,37 +4346,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503164</v>
+        <v>503213</v>
       </c>
       <c r="R36" t="n">
-        <v>7135128</v>
+        <v>7134603</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4432,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119949136</v>
+        <v>119947043</v>
       </c>
       <c r="B37" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,46 +4449,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503213</v>
+        <v>503245</v>
       </c>
       <c r="R37" t="n">
-        <v>7134603</v>
+        <v>7134683</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119947420</v>
+        <v>119966742</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4575,17 +4575,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503213</v>
+        <v>503371</v>
       </c>
       <c r="R38" t="n">
-        <v>7134622</v>
+        <v>7134522</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119947013</v>
+        <v>119950521</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>79131</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4681,13 +4681,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503258</v>
+        <v>503238</v>
       </c>
       <c r="R39" t="n">
-        <v>7134669</v>
+        <v>7134692</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119966743</v>
+        <v>119949113</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4779,17 +4779,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503321</v>
+        <v>503213</v>
       </c>
       <c r="R40" t="n">
-        <v>7134576</v>
+        <v>7134599</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119953308</v>
+        <v>119945137</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,38 +4857,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503244</v>
+        <v>503172</v>
       </c>
       <c r="R41" t="n">
-        <v>7135195</v>
+        <v>7134763</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119950857</v>
+        <v>119947387</v>
       </c>
       <c r="B42" t="n">
-        <v>78262</v>
+        <v>78187</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,21 +4963,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503168</v>
+        <v>503210</v>
       </c>
       <c r="R42" t="n">
-        <v>7134856</v>
+        <v>7134632</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119966740</v>
+        <v>119953290</v>
       </c>
       <c r="B43" t="n">
-        <v>78171</v>
+        <v>79658</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,41 +5061,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503194</v>
+        <v>503235</v>
       </c>
       <c r="R43" t="n">
-        <v>7134678</v>
+        <v>7135189</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5151,10 +5151,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966737</v>
+        <v>119947013</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5187,17 +5187,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503354</v>
+        <v>503258</v>
       </c>
       <c r="R44" t="n">
-        <v>7134564</v>
+        <v>7134669</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5253,10 +5253,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119948845</v>
+        <v>119946999</v>
       </c>
       <c r="B45" t="n">
-        <v>78171</v>
+        <v>79131</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5269,21 +5269,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503204</v>
+        <v>503249</v>
       </c>
       <c r="R45" t="n">
-        <v>7134543</v>
+        <v>7134683</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119949113</v>
+        <v>119966728</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>79624</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5367,41 +5367,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503213</v>
+        <v>503285</v>
       </c>
       <c r="R46" t="n">
-        <v>7134599</v>
+        <v>7134565</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966728</v>
+        <v>119950975</v>
       </c>
       <c r="B47" t="n">
-        <v>79608</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5469,41 +5469,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503285</v>
+        <v>503152</v>
       </c>
       <c r="R47" t="n">
-        <v>7134565</v>
+        <v>7134944</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5559,10 +5559,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119949016</v>
+        <v>119950877</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503196</v>
+        <v>503166</v>
       </c>
       <c r="R48" t="n">
-        <v>7134584</v>
+        <v>7134864</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119947043</v>
+        <v>119966744</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5697,17 +5697,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503245</v>
+        <v>503354</v>
       </c>
       <c r="R49" t="n">
-        <v>7134683</v>
+        <v>7134553</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119966746</v>
+        <v>119945243</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>78187</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5775,41 +5775,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503256</v>
+        <v>503165</v>
       </c>
       <c r="R50" t="n">
-        <v>7134674</v>
+        <v>7134719</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119966724</v>
+        <v>119950727</v>
       </c>
       <c r="B51" t="n">
-        <v>57463</v>
+        <v>78279</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5881,37 +5881,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503195</v>
+        <v>503147</v>
       </c>
       <c r="R51" t="n">
-        <v>7134698</v>
+        <v>7134810</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5941,11 +5941,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5972,10 +5967,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119945075</v>
+        <v>119953313</v>
       </c>
       <c r="B52" t="n">
-        <v>78171</v>
+        <v>79624</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5988,34 +5983,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503170</v>
+        <v>503239</v>
       </c>
       <c r="R52" t="n">
-        <v>7134825</v>
+        <v>7135198</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6074,10 +6069,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119953361</v>
+        <v>119953208</v>
       </c>
       <c r="B53" t="n">
-        <v>79607</v>
+        <v>79624</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6090,21 +6085,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6114,13 +6109,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503283</v>
+        <v>503164</v>
       </c>
       <c r="R53" t="n">
-        <v>7135226</v>
+        <v>7135128</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6176,10 +6171,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119950877</v>
+        <v>119966726</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>79652</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6192,37 +6187,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503166</v>
+        <v>503285</v>
       </c>
       <c r="R54" t="n">
-        <v>7134864</v>
+        <v>7134565</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6278,10 +6273,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119966744</v>
+        <v>119945215</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6314,17 +6309,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503354</v>
+        <v>503171</v>
       </c>
       <c r="R55" t="n">
-        <v>7134553</v>
+        <v>7134729</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6380,10 +6375,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119953277</v>
+        <v>119966729</v>
       </c>
       <c r="B56" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6416,17 +6411,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503236</v>
+        <v>503291</v>
       </c>
       <c r="R56" t="n">
-        <v>7135178</v>
+        <v>7135241</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6482,10 +6477,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119950932</v>
+        <v>119951025</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>92048</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6494,25 +6489,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6522,13 +6517,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503151</v>
+        <v>503166</v>
       </c>
       <c r="R57" t="n">
-        <v>7134896</v>
+        <v>7134990</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6584,10 +6579,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119966720</v>
+        <v>119944992</v>
       </c>
       <c r="B58" t="n">
-        <v>79115</v>
+        <v>79131</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6620,17 +6615,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503241</v>
+        <v>503182</v>
       </c>
       <c r="R58" t="n">
-        <v>7134650</v>
+        <v>7134856</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6686,10 +6681,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119950972</v>
+        <v>119953316</v>
       </c>
       <c r="B59" t="n">
-        <v>91883</v>
+        <v>79652</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6698,38 +6693,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5448</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503157</v>
+        <v>503249</v>
       </c>
       <c r="R59" t="n">
-        <v>7134940</v>
+        <v>7135183</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6788,10 +6783,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119966735</v>
+        <v>119950932</v>
       </c>
       <c r="B60" t="n">
-        <v>78262</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6800,41 +6795,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503371</v>
+        <v>503151</v>
       </c>
       <c r="R60" t="n">
-        <v>7134532</v>
+        <v>7134896</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6890,10 +6885,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119948853</v>
+        <v>119947420</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6930,10 +6925,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503204</v>
+        <v>503213</v>
       </c>
       <c r="R61" t="n">
-        <v>7134538</v>
+        <v>7134622</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6992,10 +6987,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119948976</v>
+        <v>119944998</v>
       </c>
       <c r="B62" t="n">
-        <v>89633</v>
+        <v>78278</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7008,21 +7003,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7032,13 +7027,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503222</v>
+        <v>503182</v>
       </c>
       <c r="R62" t="n">
-        <v>7134576</v>
+        <v>7134859</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7094,10 +7089,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119945243</v>
+        <v>119953361</v>
       </c>
       <c r="B63" t="n">
-        <v>78171</v>
+        <v>79623</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7110,37 +7105,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503165</v>
+        <v>503283</v>
       </c>
       <c r="R63" t="n">
-        <v>7134719</v>
+        <v>7135226</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7196,10 +7191,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119948911</v>
+        <v>119966741</v>
       </c>
       <c r="B64" t="n">
-        <v>79115</v>
+        <v>78187</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7212,37 +7207,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503190</v>
+        <v>503195</v>
       </c>
       <c r="R64" t="n">
-        <v>7134550</v>
+        <v>7134698</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7298,10 +7293,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119944976</v>
+        <v>119950926</v>
       </c>
       <c r="B65" t="n">
-        <v>78262</v>
+        <v>79131</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7314,21 +7309,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7338,13 +7333,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503197</v>
+        <v>503153</v>
       </c>
       <c r="R65" t="n">
-        <v>7134856</v>
+        <v>7134897</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7400,10 +7395,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119953290</v>
+        <v>119966735</v>
       </c>
       <c r="B66" t="n">
-        <v>79642</v>
+        <v>78278</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7412,41 +7407,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503235</v>
+        <v>503371</v>
       </c>
       <c r="R66" t="n">
-        <v>7135189</v>
+        <v>7134532</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7502,10 +7497,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119945215</v>
+        <v>119948976</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>89650</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7514,25 +7509,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7542,13 +7537,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503171</v>
+        <v>503222</v>
       </c>
       <c r="R67" t="n">
-        <v>7134729</v>
+        <v>7134576</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7604,10 +7599,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966741</v>
+        <v>119966722</v>
       </c>
       <c r="B68" t="n">
-        <v>78171</v>
+        <v>89650</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7620,21 +7615,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7644,10 +7639,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503195</v>
+        <v>503218</v>
       </c>
       <c r="R68" t="n">
-        <v>7134698</v>
+        <v>7134517</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7706,10 +7701,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119966731</v>
+        <v>119953308</v>
       </c>
       <c r="B69" t="n">
-        <v>78263</v>
+        <v>79623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7722,37 +7717,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503310</v>
+        <v>503244</v>
       </c>
       <c r="R69" t="n">
-        <v>7134560</v>
+        <v>7135195</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7808,10 +7803,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119966739</v>
+        <v>119944976</v>
       </c>
       <c r="B70" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7824,37 +7819,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503196</v>
+        <v>503197</v>
       </c>
       <c r="R70" t="n">
-        <v>7134493</v>
+        <v>7134856</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7910,10 +7905,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119953316</v>
+        <v>119948911</v>
       </c>
       <c r="B71" t="n">
-        <v>79636</v>
+        <v>79131</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7922,38 +7917,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503249</v>
+        <v>503190</v>
       </c>
       <c r="R71" t="n">
-        <v>7135183</v>
+        <v>7134550</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8012,10 +8007,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119966733</v>
+        <v>119953277</v>
       </c>
       <c r="B72" t="n">
-        <v>79643</v>
+        <v>79624</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8024,41 +8019,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503392</v>
+        <v>503236</v>
       </c>
       <c r="R72" t="n">
-        <v>7134464</v>
+        <v>7135178</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8114,10 +8109,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119950802</v>
+        <v>119966724</v>
       </c>
       <c r="B73" t="n">
-        <v>89633</v>
+        <v>57473</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8130,37 +8125,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503165</v>
+        <v>503195</v>
       </c>
       <c r="R73" t="n">
-        <v>7134812</v>
+        <v>7134698</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8190,6 +8185,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8216,10 +8216,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119948938</v>
+        <v>119966731</v>
       </c>
       <c r="B74" t="n">
-        <v>89633</v>
+        <v>78279</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8232,37 +8232,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503207</v>
+        <v>503310</v>
       </c>
       <c r="R74" t="n">
-        <v>7134561</v>
+        <v>7134560</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8318,10 +8318,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119966734</v>
+        <v>119966740</v>
       </c>
       <c r="B75" t="n">
-        <v>78262</v>
+        <v>78187</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8334,21 +8334,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8358,10 +8358,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503386</v>
+        <v>503194</v>
       </c>
       <c r="R75" t="n">
-        <v>7134487</v>
+        <v>7134678</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8420,10 +8420,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966722</v>
+        <v>119953375</v>
       </c>
       <c r="B76" t="n">
-        <v>89633</v>
+        <v>78187</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8436,37 +8436,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503218</v>
+        <v>503279</v>
       </c>
       <c r="R76" t="n">
-        <v>7134517</v>
+        <v>7135237</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8522,10 +8522,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119944998</v>
+        <v>119966748</v>
       </c>
       <c r="B77" t="n">
-        <v>78262</v>
+        <v>79658</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8534,41 +8534,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503182</v>
+        <v>503392</v>
       </c>
       <c r="R77" t="n">
-        <v>7134859</v>
+        <v>7134464</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8624,10 +8624,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119966719</v>
+        <v>119966739</v>
       </c>
       <c r="B78" t="n">
-        <v>90527</v>
+        <v>78187</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8636,25 +8636,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503312</v>
+        <v>503196</v>
       </c>
       <c r="R78" t="n">
-        <v>7134559</v>
+        <v>7134493</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119966749</v>
+        <v>119966719</v>
       </c>
       <c r="B79" t="n">
-        <v>4915</v>
+        <v>90545</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8738,25 +8738,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>101994</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8766,10 +8766,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503364</v>
+        <v>503312</v>
       </c>
       <c r="R79" t="n">
-        <v>7134522</v>
+        <v>7134559</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8802,11 +8802,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8833,10 +8828,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119950732</v>
+        <v>119945198</v>
       </c>
       <c r="B80" t="n">
-        <v>79115</v>
+        <v>78278</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8849,21 +8844,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8873,13 +8868,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503146</v>
+        <v>503176</v>
       </c>
       <c r="R80" t="n">
-        <v>7134809</v>
+        <v>7134750</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,10 +8930,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119953313</v>
+        <v>119966720</v>
       </c>
       <c r="B81" t="n">
-        <v>79608</v>
+        <v>79131</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8951,37 +8946,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503239</v>
+        <v>503241</v>
       </c>
       <c r="R81" t="n">
-        <v>7135198</v>
+        <v>7134650</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9037,10 +9032,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119966729</v>
+        <v>119966749</v>
       </c>
       <c r="B82" t="n">
-        <v>79608</v>
+        <v>4915</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,21 +9048,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>101994</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9077,10 +9072,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503291</v>
+        <v>503364</v>
       </c>
       <c r="R82" t="n">
-        <v>7135241</v>
+        <v>7134522</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9113,6 +9108,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9142,7 +9142,7 @@
         <v>119966727</v>
       </c>
       <c r="B83" t="n">
-        <v>91886</v>
+        <v>91904</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119950704</v>
+        <v>119966733</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>79659</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,37 +2607,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503155</v>
+        <v>503392</v>
       </c>
       <c r="R19" t="n">
-        <v>7134772</v>
+        <v>7134464</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119966743</v>
+        <v>119950704</v>
       </c>
       <c r="B20" t="n">
         <v>91858</v>
@@ -2729,17 +2729,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503321</v>
+        <v>503155</v>
       </c>
       <c r="R20" t="n">
-        <v>7134576</v>
+        <v>7134772</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966747</v>
+        <v>119966743</v>
       </c>
       <c r="B21" t="n">
-        <v>12337</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101283</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503341</v>
+        <v>503321</v>
       </c>
       <c r="R21" t="n">
-        <v>7134550</v>
+        <v>7134576</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2871,11 +2871,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119966733</v>
+        <v>119966747</v>
       </c>
       <c r="B22" t="n">
-        <v>79659</v>
+        <v>12337</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,25 +2909,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>101283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503392</v>
+        <v>503341</v>
       </c>
       <c r="R22" t="n">
-        <v>7134464</v>
+        <v>7134550</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2978,6 +2973,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119945243</v>
+        <v>119953313</v>
       </c>
       <c r="B50" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5779,34 +5779,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503165</v>
+        <v>503239</v>
       </c>
       <c r="R50" t="n">
-        <v>7134719</v>
+        <v>7135198</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119950727</v>
+        <v>119953208</v>
       </c>
       <c r="B51" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5881,37 +5881,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503147</v>
+        <v>503164</v>
       </c>
       <c r="R51" t="n">
-        <v>7134810</v>
+        <v>7135128</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5967,10 +5967,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119953313</v>
+        <v>119950727</v>
       </c>
       <c r="B52" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5983,37 +5983,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503239</v>
+        <v>503147</v>
       </c>
       <c r="R52" t="n">
-        <v>7135198</v>
+        <v>7134810</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6069,10 +6069,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119953208</v>
+        <v>119945243</v>
       </c>
       <c r="B53" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6085,34 +6085,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503164</v>
+        <v>503165</v>
       </c>
       <c r="R53" t="n">
-        <v>7135128</v>
+        <v>7134719</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119966726</v>
+        <v>119945215</v>
       </c>
       <c r="B54" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6187,37 +6187,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503285</v>
+        <v>503171</v>
       </c>
       <c r="R54" t="n">
-        <v>7134565</v>
+        <v>7134729</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119945215</v>
+        <v>119966726</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6289,37 +6289,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503171</v>
+        <v>503285</v>
       </c>
       <c r="R55" t="n">
-        <v>7134729</v>
+        <v>7134565</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6579,10 +6579,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119944992</v>
+        <v>119947420</v>
       </c>
       <c r="B58" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6591,25 +6591,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6619,13 +6619,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503182</v>
+        <v>503213</v>
       </c>
       <c r="R58" t="n">
-        <v>7134856</v>
+        <v>7134622</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119953316</v>
+        <v>119944992</v>
       </c>
       <c r="B59" t="n">
-        <v>79652</v>
+        <v>79131</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6693,41 +6693,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503249</v>
+        <v>503182</v>
       </c>
       <c r="R59" t="n">
-        <v>7135183</v>
+        <v>7134856</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119950932</v>
+        <v>119953316</v>
       </c>
       <c r="B60" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6799,34 +6799,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503151</v>
+        <v>503249</v>
       </c>
       <c r="R60" t="n">
-        <v>7134896</v>
+        <v>7135183</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6885,7 +6885,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119947420</v>
+        <v>119950932</v>
       </c>
       <c r="B61" t="n">
         <v>91858</v>
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503213</v>
+        <v>503151</v>
       </c>
       <c r="R61" t="n">
-        <v>7134622</v>
+        <v>7134896</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119953361</v>
+        <v>119950926</v>
       </c>
       <c r="B63" t="n">
-        <v>79623</v>
+        <v>79131</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7105,34 +7105,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503283</v>
+        <v>503153</v>
       </c>
       <c r="R63" t="n">
-        <v>7135226</v>
+        <v>7134897</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7293,10 +7293,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119950926</v>
+        <v>119953361</v>
       </c>
       <c r="B65" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7309,34 +7309,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503153</v>
+        <v>503283</v>
       </c>
       <c r="R65" t="n">
-        <v>7134897</v>
+        <v>7135226</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119944974</v>
+        <v>119953313</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,34 +2199,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503197</v>
+        <v>503239</v>
       </c>
       <c r="R15" t="n">
-        <v>7134847</v>
+        <v>7135198</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119945075</v>
+        <v>119966726</v>
       </c>
       <c r="B16" t="n">
-        <v>78187</v>
+        <v>79652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,41 +2297,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503170</v>
+        <v>503285</v>
       </c>
       <c r="R16" t="n">
-        <v>7134825</v>
+        <v>7134565</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119953353</v>
+        <v>119966735</v>
       </c>
       <c r="B17" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,41 +2399,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503265</v>
+        <v>503371</v>
       </c>
       <c r="R17" t="n">
-        <v>7135233</v>
+        <v>7134532</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119966733</v>
+        <v>119966722</v>
       </c>
       <c r="B19" t="n">
-        <v>79659</v>
+        <v>89650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503392</v>
+        <v>503218</v>
       </c>
       <c r="R19" t="n">
-        <v>7134464</v>
+        <v>7134517</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119950704</v>
+        <v>119950802</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503155</v>
+        <v>503165</v>
       </c>
       <c r="R20" t="n">
-        <v>7134772</v>
+        <v>7134812</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966743</v>
+        <v>119947043</v>
       </c>
       <c r="B21" t="n">
         <v>91858</v>
@@ -2831,17 +2831,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503321</v>
+        <v>503245</v>
       </c>
       <c r="R21" t="n">
-        <v>7134576</v>
+        <v>7134683</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119966747</v>
+        <v>119947013</v>
       </c>
       <c r="B22" t="n">
-        <v>12337</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,41 +2909,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101283</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503341</v>
+        <v>503258</v>
       </c>
       <c r="R22" t="n">
-        <v>7134550</v>
+        <v>7134669</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,11 +2973,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950802</v>
+        <v>119951025</v>
       </c>
       <c r="B23" t="n">
-        <v>89650</v>
+        <v>92048</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,21 +3015,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503165</v>
+        <v>503166</v>
       </c>
       <c r="R23" t="n">
-        <v>7134812</v>
+        <v>7134990</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3106,7 +3101,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119950857</v>
+        <v>119966734</v>
       </c>
       <c r="B24" t="n">
         <v>78278</v>
@@ -3142,17 +3137,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503168</v>
+        <v>503386</v>
       </c>
       <c r="R24" t="n">
-        <v>7134856</v>
+        <v>7134487</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3208,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119966732</v>
+        <v>119948976</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>89650</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3224,37 +3219,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503285</v>
+        <v>503222</v>
       </c>
       <c r="R25" t="n">
-        <v>7135231</v>
+        <v>7134576</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3310,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966737</v>
+        <v>119953375</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,37 +3321,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503354</v>
+        <v>503279</v>
       </c>
       <c r="R26" t="n">
-        <v>7134564</v>
+        <v>7135237</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3412,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119966734</v>
+        <v>119966732</v>
       </c>
       <c r="B27" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3428,21 +3423,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503386</v>
+        <v>503285</v>
       </c>
       <c r="R27" t="n">
-        <v>7134487</v>
+        <v>7135231</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3514,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119949016</v>
+        <v>119950521</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,25 +3521,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503196</v>
+        <v>503238</v>
       </c>
       <c r="R28" t="n">
-        <v>7134584</v>
+        <v>7134692</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3616,10 +3611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119945252</v>
+        <v>119966744</v>
       </c>
       <c r="B29" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3628,41 +3623,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503166</v>
+        <v>503354</v>
       </c>
       <c r="R29" t="n">
-        <v>7134711</v>
+        <v>7134553</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3718,10 +3713,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950972</v>
+        <v>119966731</v>
       </c>
       <c r="B30" t="n">
-        <v>91901</v>
+        <v>78279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3734,37 +3729,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5448</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503157</v>
+        <v>503310</v>
       </c>
       <c r="R30" t="n">
-        <v>7134940</v>
+        <v>7134560</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3820,7 +3815,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950732</v>
+        <v>119945252</v>
       </c>
       <c r="B31" t="n">
         <v>79131</v>
@@ -3860,13 +3855,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503146</v>
+        <v>503166</v>
       </c>
       <c r="R31" t="n">
-        <v>7134809</v>
+        <v>7134711</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119947114</v>
+        <v>119950732</v>
       </c>
       <c r="B32" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,21 +3933,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3962,13 +3957,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503256</v>
+        <v>503146</v>
       </c>
       <c r="R32" t="n">
-        <v>7134674</v>
+        <v>7134809</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4024,7 +4019,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119948845</v>
+        <v>119945075</v>
       </c>
       <c r="B33" t="n">
         <v>78187</v>
@@ -4064,10 +4059,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503204</v>
+        <v>503170</v>
       </c>
       <c r="R33" t="n">
-        <v>7134543</v>
+        <v>7134825</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4126,7 +4121,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119948853</v>
+        <v>119949113</v>
       </c>
       <c r="B34" t="n">
         <v>91858</v>
@@ -4166,10 +4161,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503204</v>
+        <v>503213</v>
       </c>
       <c r="R34" t="n">
-        <v>7134538</v>
+        <v>7134599</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4228,10 +4223,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119966746</v>
+        <v>119966748</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>79658</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4244,21 +4239,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,10 +4263,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503256</v>
+        <v>503392</v>
       </c>
       <c r="R35" t="n">
-        <v>7134674</v>
+        <v>7134464</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4330,10 +4325,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119949136</v>
+        <v>119953361</v>
       </c>
       <c r="B36" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,42 +4341,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503213</v>
+        <v>503283</v>
       </c>
       <c r="R36" t="n">
-        <v>7134603</v>
+        <v>7135226</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4437,10 +4427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119947043</v>
+        <v>119966720</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4449,41 +4439,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503245</v>
+        <v>503241</v>
       </c>
       <c r="R37" t="n">
-        <v>7134683</v>
+        <v>7134650</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4539,10 +4529,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119966742</v>
+        <v>119953308</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4551,41 +4541,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503371</v>
+        <v>503244</v>
       </c>
       <c r="R38" t="n">
-        <v>7134522</v>
+        <v>7135195</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4641,7 +4631,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119950521</v>
+        <v>119944992</v>
       </c>
       <c r="B39" t="n">
         <v>79131</v>
@@ -4681,13 +4671,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503238</v>
+        <v>503182</v>
       </c>
       <c r="R39" t="n">
-        <v>7134692</v>
+        <v>7134856</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4743,10 +4733,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119949113</v>
+        <v>119947387</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,25 +4745,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4773,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503213</v>
+        <v>503210</v>
       </c>
       <c r="R40" t="n">
-        <v>7134599</v>
+        <v>7134632</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4845,10 +4835,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119945137</v>
+        <v>119953316</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4861,34 +4851,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503172</v>
+        <v>503249</v>
       </c>
       <c r="R41" t="n">
-        <v>7134763</v>
+        <v>7135183</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4947,10 +4937,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119947387</v>
+        <v>119946999</v>
       </c>
       <c r="B42" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,21 +4953,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4987,10 +4977,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503210</v>
+        <v>503249</v>
       </c>
       <c r="R42" t="n">
-        <v>7134632</v>
+        <v>7134683</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5049,10 +5039,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119953290</v>
+        <v>119950932</v>
       </c>
       <c r="B43" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,37 +5055,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503235</v>
+        <v>503151</v>
       </c>
       <c r="R43" t="n">
-        <v>7135189</v>
+        <v>7134896</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5151,10 +5141,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119947013</v>
+        <v>119966728</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5167,37 +5157,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503258</v>
+        <v>503285</v>
       </c>
       <c r="R44" t="n">
-        <v>7134669</v>
+        <v>7134565</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5253,10 +5243,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119946999</v>
+        <v>119953353</v>
       </c>
       <c r="B45" t="n">
-        <v>79131</v>
+        <v>90545</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5265,41 +5255,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503249</v>
+        <v>503265</v>
       </c>
       <c r="R45" t="n">
-        <v>7134683</v>
+        <v>7135233</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5355,10 +5345,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966728</v>
+        <v>119966739</v>
       </c>
       <c r="B46" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5371,21 +5361,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5395,10 +5385,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503285</v>
+        <v>503196</v>
       </c>
       <c r="R46" t="n">
-        <v>7134565</v>
+        <v>7134493</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5457,10 +5447,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119950975</v>
+        <v>119966724</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5469,41 +5459,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503152</v>
+        <v>503195</v>
       </c>
       <c r="R47" t="n">
-        <v>7134944</v>
+        <v>7134698</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5533,6 +5523,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,10 +5656,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119966744</v>
+        <v>119953277</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5673,41 +5668,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503354</v>
+        <v>503236</v>
       </c>
       <c r="R49" t="n">
-        <v>7134553</v>
+        <v>7135178</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,10 +5758,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119953313</v>
+        <v>119966740</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5779,37 +5774,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503239</v>
+        <v>503194</v>
       </c>
       <c r="R50" t="n">
-        <v>7135198</v>
+        <v>7134678</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5865,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119953208</v>
+        <v>119947114</v>
       </c>
       <c r="B51" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5881,34 +5876,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503164</v>
+        <v>503256</v>
       </c>
       <c r="R51" t="n">
-        <v>7135128</v>
+        <v>7134674</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5967,10 +5962,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119950727</v>
+        <v>119945243</v>
       </c>
       <c r="B52" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5983,21 +5978,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6007,13 +6002,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503147</v>
+        <v>503165</v>
       </c>
       <c r="R52" t="n">
-        <v>7134810</v>
+        <v>7134719</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6069,10 +6064,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119945243</v>
+        <v>119945198</v>
       </c>
       <c r="B53" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6085,21 +6080,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503165</v>
+        <v>503176</v>
       </c>
       <c r="R53" t="n">
-        <v>7134719</v>
+        <v>7134750</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6171,10 +6166,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119945215</v>
+        <v>119966719</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6187,37 +6182,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503171</v>
+        <v>503312</v>
       </c>
       <c r="R54" t="n">
-        <v>7134729</v>
+        <v>7134559</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6273,10 +6268,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119966726</v>
+        <v>119950972</v>
       </c>
       <c r="B55" t="n">
-        <v>79652</v>
+        <v>91901</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6285,41 +6280,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>5448</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503285</v>
+        <v>503157</v>
       </c>
       <c r="R55" t="n">
-        <v>7134565</v>
+        <v>7134940</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6375,10 +6370,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119966729</v>
+        <v>119966749</v>
       </c>
       <c r="B56" t="n">
-        <v>79624</v>
+        <v>4915</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6391,21 +6386,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>101994</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6415,10 +6410,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503291</v>
+        <v>503364</v>
       </c>
       <c r="R56" t="n">
-        <v>7135241</v>
+        <v>7134522</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6451,6 +6446,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6477,10 +6477,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119951025</v>
+        <v>119950727</v>
       </c>
       <c r="B57" t="n">
-        <v>92048</v>
+        <v>78279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6493,21 +6493,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503166</v>
+        <v>503147</v>
       </c>
       <c r="R57" t="n">
-        <v>7134990</v>
+        <v>7134810</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6579,10 +6579,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119947420</v>
+        <v>119944974</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6591,25 +6591,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503213</v>
+        <v>503197</v>
       </c>
       <c r="R58" t="n">
-        <v>7134622</v>
+        <v>7134847</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119944992</v>
+        <v>119944998</v>
       </c>
       <c r="B59" t="n">
-        <v>79131</v>
+        <v>78278</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6697,21 +6697,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
         <v>503182</v>
       </c>
       <c r="R59" t="n">
-        <v>7134856</v>
+        <v>7134859</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119953316</v>
+        <v>119945137</v>
       </c>
       <c r="B60" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6799,34 +6799,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503249</v>
+        <v>503172</v>
       </c>
       <c r="R60" t="n">
-        <v>7135183</v>
+        <v>7134763</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6885,10 +6885,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119950932</v>
+        <v>119966741</v>
       </c>
       <c r="B61" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6897,41 +6897,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503151</v>
+        <v>503195</v>
       </c>
       <c r="R61" t="n">
-        <v>7134896</v>
+        <v>7134698</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119944998</v>
+        <v>119966743</v>
       </c>
       <c r="B62" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6999,41 +6999,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503182</v>
+        <v>503321</v>
       </c>
       <c r="R62" t="n">
-        <v>7134859</v>
+        <v>7134576</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119950926</v>
+        <v>119950975</v>
       </c>
       <c r="B63" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7101,25 +7101,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7129,13 +7129,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503153</v>
+        <v>503152</v>
       </c>
       <c r="R63" t="n">
-        <v>7134897</v>
+        <v>7134944</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119966741</v>
+        <v>119966746</v>
       </c>
       <c r="B64" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7203,25 +7203,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503195</v>
+        <v>503256</v>
       </c>
       <c r="R64" t="n">
-        <v>7134698</v>
+        <v>7134674</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7293,10 +7293,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119953361</v>
+        <v>119950857</v>
       </c>
       <c r="B65" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7309,34 +7309,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503283</v>
+        <v>503168</v>
       </c>
       <c r="R65" t="n">
-        <v>7135226</v>
+        <v>7134856</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7395,10 +7395,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119966735</v>
+        <v>119949016</v>
       </c>
       <c r="B66" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7407,41 +7407,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503371</v>
+        <v>503196</v>
       </c>
       <c r="R66" t="n">
-        <v>7134532</v>
+        <v>7134584</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119948976</v>
+        <v>119947420</v>
       </c>
       <c r="B67" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7509,25 +7509,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503222</v>
+        <v>503213</v>
       </c>
       <c r="R67" t="n">
-        <v>7134576</v>
+        <v>7134622</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7599,10 +7599,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966722</v>
+        <v>119948911</v>
       </c>
       <c r="B68" t="n">
-        <v>89650</v>
+        <v>79131</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7615,37 +7615,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503218</v>
+        <v>503190</v>
       </c>
       <c r="R68" t="n">
-        <v>7134517</v>
+        <v>7134550</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7701,10 +7701,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119953308</v>
+        <v>119966742</v>
       </c>
       <c r="B69" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7713,41 +7713,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503244</v>
+        <v>503371</v>
       </c>
       <c r="R69" t="n">
-        <v>7135195</v>
+        <v>7134522</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119944976</v>
+        <v>119966729</v>
       </c>
       <c r="B70" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7819,37 +7819,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503197</v>
+        <v>503291</v>
       </c>
       <c r="R70" t="n">
-        <v>7134856</v>
+        <v>7135241</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119948911</v>
+        <v>119966733</v>
       </c>
       <c r="B71" t="n">
-        <v>79131</v>
+        <v>79659</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7917,41 +7917,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503190</v>
+        <v>503392</v>
       </c>
       <c r="R71" t="n">
-        <v>7134550</v>
+        <v>7134464</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8007,10 +8007,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119953277</v>
+        <v>119948845</v>
       </c>
       <c r="B72" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8023,37 +8023,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503236</v>
+        <v>503204</v>
       </c>
       <c r="R72" t="n">
-        <v>7135178</v>
+        <v>7134543</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119966724</v>
+        <v>119949136</v>
       </c>
       <c r="B73" t="n">
         <v>57473</v>
@@ -8143,16 +8143,21 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503195</v>
+        <v>503213</v>
       </c>
       <c r="R73" t="n">
-        <v>7134698</v>
+        <v>7134603</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8185,11 +8190,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8216,10 +8216,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119966731</v>
+        <v>119953208</v>
       </c>
       <c r="B74" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8232,37 +8232,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503310</v>
+        <v>503164</v>
       </c>
       <c r="R74" t="n">
-        <v>7134560</v>
+        <v>7135128</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8318,10 +8318,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119966740</v>
+        <v>119953290</v>
       </c>
       <c r="B75" t="n">
-        <v>78187</v>
+        <v>79658</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8330,41 +8330,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503194</v>
+        <v>503235</v>
       </c>
       <c r="R75" t="n">
-        <v>7134678</v>
+        <v>7135189</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8420,10 +8420,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119953375</v>
+        <v>119950926</v>
       </c>
       <c r="B76" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8436,37 +8436,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503279</v>
+        <v>503153</v>
       </c>
       <c r="R76" t="n">
-        <v>7135237</v>
+        <v>7134897</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8522,10 +8522,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966748</v>
+        <v>119950704</v>
       </c>
       <c r="B77" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8538,37 +8538,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503392</v>
+        <v>503155</v>
       </c>
       <c r="R77" t="n">
-        <v>7134464</v>
+        <v>7134772</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8624,10 +8624,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119966739</v>
+        <v>119966747</v>
       </c>
       <c r="B78" t="n">
-        <v>78187</v>
+        <v>12337</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8636,25 +8636,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>101283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503196</v>
+        <v>503341</v>
       </c>
       <c r="R78" t="n">
-        <v>7134493</v>
+        <v>7134550</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8700,6 +8700,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8726,10 +8731,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119966719</v>
+        <v>119945215</v>
       </c>
       <c r="B79" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8742,37 +8747,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503312</v>
+        <v>503171</v>
       </c>
       <c r="R79" t="n">
-        <v>7134559</v>
+        <v>7134729</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8828,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119945198</v>
+        <v>119948853</v>
       </c>
       <c r="B80" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8840,25 +8845,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8868,10 +8873,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503176</v>
+        <v>503204</v>
       </c>
       <c r="R80" t="n">
-        <v>7134750</v>
+        <v>7134538</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8930,10 +8935,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119966720</v>
+        <v>119966737</v>
       </c>
       <c r="B81" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8946,21 +8951,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8970,10 +8975,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503241</v>
+        <v>503354</v>
       </c>
       <c r="R81" t="n">
-        <v>7134650</v>
+        <v>7134564</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9032,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119966749</v>
+        <v>119944976</v>
       </c>
       <c r="B82" t="n">
-        <v>4915</v>
+        <v>78278</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9048,37 +9053,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101994</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503364</v>
+        <v>503197</v>
       </c>
       <c r="R82" t="n">
-        <v>7134522</v>
+        <v>7134856</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9108,11 +9113,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119953313</v>
+        <v>119966722</v>
       </c>
       <c r="B15" t="n">
-        <v>79624</v>
+        <v>89650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,37 +2199,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503239</v>
+        <v>503218</v>
       </c>
       <c r="R15" t="n">
-        <v>7135198</v>
+        <v>7134517</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119966726</v>
+        <v>119950802</v>
       </c>
       <c r="B16" t="n">
-        <v>79652</v>
+        <v>89650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,41 +2297,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503285</v>
+        <v>503165</v>
       </c>
       <c r="R16" t="n">
-        <v>7134565</v>
+        <v>7134812</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119966735</v>
+        <v>119953313</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,37 +2403,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503371</v>
+        <v>503239</v>
       </c>
       <c r="R17" t="n">
-        <v>7134532</v>
+        <v>7135198</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119948938</v>
+        <v>119966726</v>
       </c>
       <c r="B18" t="n">
-        <v>89650</v>
+        <v>79652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,41 +2501,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503207</v>
+        <v>503285</v>
       </c>
       <c r="R18" t="n">
-        <v>7134561</v>
+        <v>7134565</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119966722</v>
+        <v>119966735</v>
       </c>
       <c r="B19" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503218</v>
+        <v>503371</v>
       </c>
       <c r="R19" t="n">
-        <v>7134517</v>
+        <v>7134532</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,7 +2693,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119950802</v>
+        <v>119948938</v>
       </c>
       <c r="B20" t="n">
         <v>89650</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503165</v>
+        <v>503207</v>
       </c>
       <c r="R20" t="n">
-        <v>7134812</v>
+        <v>7134561</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119945075</v>
+        <v>119966720</v>
       </c>
       <c r="B33" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4035,37 +4035,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503170</v>
+        <v>503241</v>
       </c>
       <c r="R33" t="n">
-        <v>7134825</v>
+        <v>7134650</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119966748</v>
+        <v>119945075</v>
       </c>
       <c r="B35" t="n">
-        <v>79658</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4235,41 +4235,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503392</v>
+        <v>503170</v>
       </c>
       <c r="R35" t="n">
-        <v>7134464</v>
+        <v>7134825</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4325,10 +4325,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119953361</v>
+        <v>119966748</v>
       </c>
       <c r="B36" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4337,41 +4337,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503283</v>
+        <v>503392</v>
       </c>
       <c r="R36" t="n">
-        <v>7135226</v>
+        <v>7134464</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119966720</v>
+        <v>119953361</v>
       </c>
       <c r="B37" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4443,37 +4443,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503241</v>
+        <v>503283</v>
       </c>
       <c r="R37" t="n">
-        <v>7134650</v>
+        <v>7135226</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966724</v>
+        <v>119966740</v>
       </c>
       <c r="B47" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5463,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503195</v>
+        <v>503194</v>
       </c>
       <c r="R47" t="n">
-        <v>7134698</v>
+        <v>7134678</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5523,11 +5523,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5758,10 +5753,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119966740</v>
+        <v>119966724</v>
       </c>
       <c r="B50" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5774,21 +5769,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5793,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503194</v>
+        <v>503195</v>
       </c>
       <c r="R50" t="n">
-        <v>7134678</v>
+        <v>7134698</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5834,6 +5829,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6477,10 +6477,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119950727</v>
+        <v>119944974</v>
       </c>
       <c r="B57" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6493,21 +6493,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503147</v>
+        <v>503197</v>
       </c>
       <c r="R57" t="n">
-        <v>7134810</v>
+        <v>7134847</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6579,10 +6579,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119944974</v>
+        <v>119950727</v>
       </c>
       <c r="B58" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6595,21 +6595,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6619,13 +6619,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503197</v>
+        <v>503147</v>
       </c>
       <c r="R58" t="n">
-        <v>7134847</v>
+        <v>7134810</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119966722</v>
+        <v>119950926</v>
       </c>
       <c r="B15" t="n">
-        <v>89650</v>
+        <v>79131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,37 +2199,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503218</v>
+        <v>503153</v>
       </c>
       <c r="R15" t="n">
-        <v>7134517</v>
+        <v>7134897</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119950802</v>
+        <v>119966722</v>
       </c>
       <c r="B16" t="n">
         <v>89650</v>
@@ -2321,17 +2321,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503165</v>
+        <v>503218</v>
       </c>
       <c r="R16" t="n">
-        <v>7134812</v>
+        <v>7134517</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119953313</v>
+        <v>119947114</v>
       </c>
       <c r="B17" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,34 +2403,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503239</v>
+        <v>503256</v>
       </c>
       <c r="R17" t="n">
-        <v>7135198</v>
+        <v>7134674</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119966726</v>
+        <v>119944974</v>
       </c>
       <c r="B18" t="n">
-        <v>79652</v>
+        <v>78187</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,41 +2501,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503285</v>
+        <v>503197</v>
       </c>
       <c r="R18" t="n">
-        <v>7134565</v>
+        <v>7134847</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119966735</v>
+        <v>119953290</v>
       </c>
       <c r="B19" t="n">
-        <v>78278</v>
+        <v>79658</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,41 +2603,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503371</v>
+        <v>503235</v>
       </c>
       <c r="R19" t="n">
-        <v>7134532</v>
+        <v>7135189</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119948938</v>
+        <v>119947043</v>
       </c>
       <c r="B20" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503207</v>
+        <v>503245</v>
       </c>
       <c r="R20" t="n">
-        <v>7134561</v>
+        <v>7134683</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119947043</v>
+        <v>119966724</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,41 +2807,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503245</v>
+        <v>503195</v>
       </c>
       <c r="R21" t="n">
-        <v>7134683</v>
+        <v>7134698</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2871,6 +2871,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119947013</v>
+        <v>119947420</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,25 +2914,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,13 +2942,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503258</v>
+        <v>503213</v>
       </c>
       <c r="R22" t="n">
-        <v>7134669</v>
+        <v>7134622</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2999,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119951025</v>
+        <v>119953208</v>
       </c>
       <c r="B23" t="n">
-        <v>92048</v>
+        <v>79624</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,37 +3020,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503166</v>
+        <v>503164</v>
       </c>
       <c r="R23" t="n">
-        <v>7134990</v>
+        <v>7135128</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119966734</v>
+        <v>119947387</v>
       </c>
       <c r="B24" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3117,37 +3122,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503386</v>
+        <v>503210</v>
       </c>
       <c r="R24" t="n">
-        <v>7134487</v>
+        <v>7134632</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,10 +3208,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119948976</v>
+        <v>119953375</v>
       </c>
       <c r="B25" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,34 +3224,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503222</v>
+        <v>503279</v>
       </c>
       <c r="R25" t="n">
-        <v>7134576</v>
+        <v>7135237</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3305,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119953375</v>
+        <v>119953313</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3321,21 +3326,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503279</v>
+        <v>503239</v>
       </c>
       <c r="R26" t="n">
-        <v>7135237</v>
+        <v>7135198</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3407,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119966732</v>
+        <v>119945075</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3423,37 +3428,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503285</v>
+        <v>503170</v>
       </c>
       <c r="R27" t="n">
-        <v>7135231</v>
+        <v>7134825</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3509,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950521</v>
+        <v>119945243</v>
       </c>
       <c r="B28" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3525,21 +3530,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503238</v>
+        <v>503165</v>
       </c>
       <c r="R28" t="n">
-        <v>7134692</v>
+        <v>7134719</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3611,7 +3616,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119966744</v>
+        <v>119945215</v>
       </c>
       <c r="B29" t="n">
         <v>91858</v>
@@ -3647,17 +3652,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503354</v>
+        <v>503171</v>
       </c>
       <c r="R29" t="n">
-        <v>7134553</v>
+        <v>7134729</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3713,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119966731</v>
+        <v>119953308</v>
       </c>
       <c r="B30" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3729,37 +3734,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503310</v>
+        <v>503244</v>
       </c>
       <c r="R30" t="n">
-        <v>7134560</v>
+        <v>7135195</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3815,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119945252</v>
+        <v>119949136</v>
       </c>
       <c r="B31" t="n">
-        <v>79131</v>
+        <v>57473</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,37 +3836,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503166</v>
+        <v>503213</v>
       </c>
       <c r="R31" t="n">
-        <v>7134711</v>
+        <v>7134603</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3917,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950732</v>
+        <v>119948976</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>89650</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3933,21 +3943,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3957,13 +3967,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503146</v>
+        <v>503222</v>
       </c>
       <c r="R32" t="n">
-        <v>7134809</v>
+        <v>7134576</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4019,7 +4029,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119966720</v>
+        <v>119946999</v>
       </c>
       <c r="B33" t="n">
         <v>79131</v>
@@ -4055,17 +4065,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503241</v>
+        <v>503249</v>
       </c>
       <c r="R33" t="n">
-        <v>7134650</v>
+        <v>7134683</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4121,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119949113</v>
+        <v>119966740</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4133,41 +4143,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503213</v>
+        <v>503194</v>
       </c>
       <c r="R34" t="n">
-        <v>7134599</v>
+        <v>7134678</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119945075</v>
+        <v>119950802</v>
       </c>
       <c r="B35" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4239,21 +4249,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4263,13 +4273,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503170</v>
+        <v>503165</v>
       </c>
       <c r="R35" t="n">
-        <v>7134825</v>
+        <v>7134812</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4325,10 +4335,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119966748</v>
+        <v>119966744</v>
       </c>
       <c r="B36" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4341,21 +4351,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4365,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503392</v>
+        <v>503354</v>
       </c>
       <c r="R36" t="n">
-        <v>7134464</v>
+        <v>7134553</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4427,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119953361</v>
+        <v>119950727</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4443,34 +4453,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503283</v>
+        <v>503147</v>
       </c>
       <c r="R37" t="n">
-        <v>7135226</v>
+        <v>7134810</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4529,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119953308</v>
+        <v>119966749</v>
       </c>
       <c r="B38" t="n">
-        <v>79623</v>
+        <v>4915</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4545,37 +4555,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>101994</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503244</v>
+        <v>503364</v>
       </c>
       <c r="R38" t="n">
-        <v>7135195</v>
+        <v>7134522</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4605,6 +4615,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4631,7 +4646,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119944992</v>
+        <v>119950732</v>
       </c>
       <c r="B39" t="n">
         <v>79131</v>
@@ -4671,13 +4686,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503182</v>
+        <v>503146</v>
       </c>
       <c r="R39" t="n">
-        <v>7134856</v>
+        <v>7134809</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4733,10 +4748,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119947387</v>
+        <v>119953277</v>
       </c>
       <c r="B40" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4749,37 +4764,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503210</v>
+        <v>503236</v>
       </c>
       <c r="R40" t="n">
-        <v>7134632</v>
+        <v>7135178</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4835,10 +4850,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119953316</v>
+        <v>119947013</v>
       </c>
       <c r="B41" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4847,41 +4862,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503249</v>
+        <v>503258</v>
       </c>
       <c r="R41" t="n">
-        <v>7135183</v>
+        <v>7134669</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4937,10 +4952,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119946999</v>
+        <v>119966733</v>
       </c>
       <c r="B42" t="n">
-        <v>79131</v>
+        <v>79659</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4949,41 +4964,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503249</v>
+        <v>503392</v>
       </c>
       <c r="R42" t="n">
-        <v>7134683</v>
+        <v>7134464</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5039,7 +5054,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119950932</v>
+        <v>119950975</v>
       </c>
       <c r="B43" t="n">
         <v>91858</v>
@@ -5079,10 +5094,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503151</v>
+        <v>503152</v>
       </c>
       <c r="R43" t="n">
-        <v>7134896</v>
+        <v>7134944</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5141,7 +5156,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966728</v>
+        <v>119966729</v>
       </c>
       <c r="B44" t="n">
         <v>79624</v>
@@ -5181,10 +5196,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503285</v>
+        <v>503291</v>
       </c>
       <c r="R44" t="n">
-        <v>7134565</v>
+        <v>7135241</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5243,10 +5258,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119953353</v>
+        <v>119953361</v>
       </c>
       <c r="B45" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,25 +5270,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5283,10 +5298,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503265</v>
+        <v>503283</v>
       </c>
       <c r="R45" t="n">
-        <v>7135233</v>
+        <v>7135226</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5345,10 +5360,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966739</v>
+        <v>119949113</v>
       </c>
       <c r="B46" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,41 +5372,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503196</v>
+        <v>503213</v>
       </c>
       <c r="R46" t="n">
-        <v>7134493</v>
+        <v>7134599</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5447,10 +5462,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966740</v>
+        <v>119950877</v>
       </c>
       <c r="B47" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,41 +5474,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503194</v>
+        <v>503166</v>
       </c>
       <c r="R47" t="n">
-        <v>7134678</v>
+        <v>7134864</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5549,10 +5564,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119950877</v>
+        <v>119966719</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,37 +5580,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503166</v>
+        <v>503312</v>
       </c>
       <c r="R48" t="n">
-        <v>7134864</v>
+        <v>7134559</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5651,10 +5666,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119953277</v>
+        <v>119944998</v>
       </c>
       <c r="B49" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5667,37 +5682,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503236</v>
+        <v>503182</v>
       </c>
       <c r="R49" t="n">
-        <v>7135178</v>
+        <v>7134859</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5753,10 +5768,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119966724</v>
+        <v>119953316</v>
       </c>
       <c r="B50" t="n">
-        <v>57473</v>
+        <v>79652</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5765,41 +5780,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503195</v>
+        <v>503249</v>
       </c>
       <c r="R50" t="n">
-        <v>7134698</v>
+        <v>7135183</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5829,11 +5844,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5860,10 +5870,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119947114</v>
+        <v>119966735</v>
       </c>
       <c r="B51" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5876,37 +5886,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503256</v>
+        <v>503371</v>
       </c>
       <c r="R51" t="n">
-        <v>7134674</v>
+        <v>7134532</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5962,10 +5972,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119945243</v>
+        <v>119949016</v>
       </c>
       <c r="B52" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5974,25 +5984,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6002,10 +6012,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503165</v>
+        <v>503196</v>
       </c>
       <c r="R52" t="n">
-        <v>7134719</v>
+        <v>7134584</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6064,10 +6074,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119945198</v>
+        <v>119950521</v>
       </c>
       <c r="B53" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6080,21 +6090,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6104,10 +6114,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503176</v>
+        <v>503238</v>
       </c>
       <c r="R53" t="n">
-        <v>7134750</v>
+        <v>7134692</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6166,10 +6176,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119966719</v>
+        <v>119966746</v>
       </c>
       <c r="B54" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6182,21 +6192,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6206,10 +6216,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503312</v>
+        <v>503256</v>
       </c>
       <c r="R54" t="n">
-        <v>7134559</v>
+        <v>7134674</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6268,10 +6278,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119950972</v>
+        <v>119945137</v>
       </c>
       <c r="B55" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6280,25 +6290,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6308,10 +6318,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503157</v>
+        <v>503172</v>
       </c>
       <c r="R55" t="n">
-        <v>7134940</v>
+        <v>7134763</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6370,10 +6380,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119966749</v>
+        <v>119951025</v>
       </c>
       <c r="B56" t="n">
-        <v>4915</v>
+        <v>92048</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6386,37 +6396,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>101994</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503364</v>
+        <v>503166</v>
       </c>
       <c r="R56" t="n">
-        <v>7134522</v>
+        <v>7134990</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6446,11 +6456,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6477,10 +6482,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119944974</v>
+        <v>119966728</v>
       </c>
       <c r="B57" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6493,37 +6498,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503197</v>
+        <v>503285</v>
       </c>
       <c r="R57" t="n">
-        <v>7134847</v>
+        <v>7134565</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6579,10 +6584,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119950727</v>
+        <v>119966720</v>
       </c>
       <c r="B58" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6595,37 +6600,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503147</v>
+        <v>503241</v>
       </c>
       <c r="R58" t="n">
-        <v>7134810</v>
+        <v>7134650</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6681,10 +6686,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119944998</v>
+        <v>119966739</v>
       </c>
       <c r="B59" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6697,37 +6702,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503182</v>
+        <v>503196</v>
       </c>
       <c r="R59" t="n">
-        <v>7134859</v>
+        <v>7134493</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6783,10 +6788,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119945137</v>
+        <v>119966737</v>
       </c>
       <c r="B60" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6795,41 +6800,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503172</v>
+        <v>503354</v>
       </c>
       <c r="R60" t="n">
-        <v>7134763</v>
+        <v>7134564</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6885,10 +6890,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119966741</v>
+        <v>119966743</v>
       </c>
       <c r="B61" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6897,25 +6902,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6925,10 +6930,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503195</v>
+        <v>503321</v>
       </c>
       <c r="R61" t="n">
-        <v>7134698</v>
+        <v>7134576</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6987,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119966743</v>
+        <v>119945198</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6999,41 +7004,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503321</v>
+        <v>503176</v>
       </c>
       <c r="R62" t="n">
-        <v>7134576</v>
+        <v>7134750</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7089,10 +7094,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119950975</v>
+        <v>119966731</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7101,41 +7106,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503152</v>
+        <v>503310</v>
       </c>
       <c r="R63" t="n">
-        <v>7134944</v>
+        <v>7134560</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7191,10 +7196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119966746</v>
+        <v>119966748</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>79658</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7207,21 +7212,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7231,10 +7236,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503256</v>
+        <v>503392</v>
       </c>
       <c r="R64" t="n">
-        <v>7134674</v>
+        <v>7134464</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7293,10 +7298,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119950857</v>
+        <v>119953353</v>
       </c>
       <c r="B65" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7305,38 +7310,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503168</v>
+        <v>503265</v>
       </c>
       <c r="R65" t="n">
-        <v>7134856</v>
+        <v>7135233</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7395,10 +7400,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119949016</v>
+        <v>119966734</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7407,41 +7412,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503196</v>
+        <v>503386</v>
       </c>
       <c r="R66" t="n">
-        <v>7134584</v>
+        <v>7134487</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7497,10 +7502,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119947420</v>
+        <v>119966732</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7509,41 +7514,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503213</v>
+        <v>503285</v>
       </c>
       <c r="R67" t="n">
-        <v>7134622</v>
+        <v>7135231</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7599,10 +7604,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119948911</v>
+        <v>119950857</v>
       </c>
       <c r="B68" t="n">
-        <v>79131</v>
+        <v>78278</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7615,21 +7620,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7639,13 +7644,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503190</v>
+        <v>503168</v>
       </c>
       <c r="R68" t="n">
-        <v>7134550</v>
+        <v>7134856</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7701,10 +7706,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119966742</v>
+        <v>119966726</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7717,21 +7722,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7741,10 +7746,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503371</v>
+        <v>503285</v>
       </c>
       <c r="R69" t="n">
-        <v>7134522</v>
+        <v>7134565</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7803,10 +7808,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119966729</v>
+        <v>119966742</v>
       </c>
       <c r="B70" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7815,25 +7820,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7843,10 +7848,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503291</v>
+        <v>503371</v>
       </c>
       <c r="R70" t="n">
-        <v>7135241</v>
+        <v>7134522</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7905,10 +7910,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119966733</v>
+        <v>119950704</v>
       </c>
       <c r="B71" t="n">
-        <v>79659</v>
+        <v>91858</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7921,37 +7926,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503392</v>
+        <v>503155</v>
       </c>
       <c r="R71" t="n">
-        <v>7134464</v>
+        <v>7134772</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8007,10 +8012,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119948845</v>
+        <v>119945252</v>
       </c>
       <c r="B72" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8023,21 +8028,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8047,10 +8052,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503204</v>
+        <v>503166</v>
       </c>
       <c r="R72" t="n">
-        <v>7134543</v>
+        <v>7134711</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8109,10 +8114,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119949136</v>
+        <v>119944992</v>
       </c>
       <c r="B73" t="n">
-        <v>57473</v>
+        <v>79131</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8125,42 +8130,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503213</v>
+        <v>503182</v>
       </c>
       <c r="R73" t="n">
-        <v>7134603</v>
+        <v>7134856</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8216,10 +8216,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119953208</v>
+        <v>119944976</v>
       </c>
       <c r="B74" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8232,34 +8232,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503164</v>
+        <v>503197</v>
       </c>
       <c r="R74" t="n">
-        <v>7135128</v>
+        <v>7134856</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8318,10 +8318,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119953290</v>
+        <v>119950972</v>
       </c>
       <c r="B75" t="n">
-        <v>79658</v>
+        <v>91901</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8330,41 +8330,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6463</v>
+        <v>5448</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503235</v>
+        <v>503157</v>
       </c>
       <c r="R75" t="n">
-        <v>7135189</v>
+        <v>7134940</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8420,10 +8420,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119950926</v>
+        <v>119950932</v>
       </c>
       <c r="B76" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8432,25 +8432,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8460,13 +8460,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503153</v>
+        <v>503151</v>
       </c>
       <c r="R76" t="n">
-        <v>7134897</v>
+        <v>7134896</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119950704</v>
+        <v>119948853</v>
       </c>
       <c r="B77" t="n">
         <v>91858</v>
@@ -8562,10 +8562,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503155</v>
+        <v>503204</v>
       </c>
       <c r="R77" t="n">
-        <v>7134772</v>
+        <v>7134538</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119945215</v>
+        <v>119948911</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8743,25 +8743,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8771,13 +8771,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503171</v>
+        <v>503190</v>
       </c>
       <c r="R79" t="n">
-        <v>7134729</v>
+        <v>7134550</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119948853</v>
+        <v>119948845</v>
       </c>
       <c r="B80" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8845,25 +8845,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8876,7 +8876,7 @@
         <v>503204</v>
       </c>
       <c r="R80" t="n">
-        <v>7134538</v>
+        <v>7134543</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119966737</v>
+        <v>119966741</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8951,21 +8951,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503354</v>
+        <v>503195</v>
       </c>
       <c r="R81" t="n">
-        <v>7134564</v>
+        <v>7134698</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119944976</v>
+        <v>119948938</v>
       </c>
       <c r="B82" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,21 +9053,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9077,13 +9077,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503197</v>
+        <v>503207</v>
       </c>
       <c r="R82" t="n">
-        <v>7134856</v>
+        <v>7134561</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -5054,10 +5054,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119950975</v>
+        <v>119966729</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5066,41 +5066,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503152</v>
+        <v>503291</v>
       </c>
       <c r="R43" t="n">
-        <v>7134944</v>
+        <v>7135241</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966729</v>
+        <v>119950975</v>
       </c>
       <c r="B44" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5168,41 +5168,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503291</v>
+        <v>503152</v>
       </c>
       <c r="R44" t="n">
-        <v>7135241</v>
+        <v>7134944</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119966746</v>
+        <v>119945137</v>
       </c>
       <c r="B54" t="n">
         <v>91858</v>
@@ -6212,17 +6212,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503256</v>
+        <v>503172</v>
       </c>
       <c r="R54" t="n">
-        <v>7134674</v>
+        <v>7134763</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6278,10 +6278,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119945137</v>
+        <v>119951025</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6290,25 +6290,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6318,13 +6318,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503172</v>
+        <v>503166</v>
       </c>
       <c r="R55" t="n">
-        <v>7134763</v>
+        <v>7134990</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6380,10 +6380,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119951025</v>
+        <v>119966728</v>
       </c>
       <c r="B56" t="n">
-        <v>92048</v>
+        <v>79624</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6396,37 +6396,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503166</v>
+        <v>503285</v>
       </c>
       <c r="R56" t="n">
-        <v>7134990</v>
+        <v>7134565</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119966728</v>
+        <v>119966746</v>
       </c>
       <c r="B57" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6494,25 +6494,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503285</v>
+        <v>503256</v>
       </c>
       <c r="R57" t="n">
-        <v>7134565</v>
+        <v>7134674</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7094,10 +7094,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119966731</v>
+        <v>119966748</v>
       </c>
       <c r="B63" t="n">
-        <v>78279</v>
+        <v>79658</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7106,25 +7106,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503310</v>
+        <v>503392</v>
       </c>
       <c r="R63" t="n">
-        <v>7134560</v>
+        <v>7134464</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7196,10 +7196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119966748</v>
+        <v>119966731</v>
       </c>
       <c r="B64" t="n">
-        <v>79658</v>
+        <v>78279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7208,25 +7208,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503392</v>
+        <v>503310</v>
       </c>
       <c r="R64" t="n">
-        <v>7134464</v>
+        <v>7134560</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119950926</v>
+        <v>119966734</v>
       </c>
       <c r="B15" t="n">
-        <v>79131</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,37 +2199,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503153</v>
+        <v>503386</v>
       </c>
       <c r="R15" t="n">
-        <v>7134897</v>
+        <v>7134487</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119966722</v>
+        <v>119953361</v>
       </c>
       <c r="B16" t="n">
-        <v>89650</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,37 +2301,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503218</v>
+        <v>503283</v>
       </c>
       <c r="R16" t="n">
-        <v>7134517</v>
+        <v>7135226</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119947114</v>
+        <v>119947013</v>
       </c>
       <c r="B17" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503256</v>
+        <v>503258</v>
       </c>
       <c r="R17" t="n">
-        <v>7134674</v>
+        <v>7134669</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119944974</v>
+        <v>119953308</v>
       </c>
       <c r="B18" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,34 +2505,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503197</v>
+        <v>503244</v>
       </c>
       <c r="R18" t="n">
-        <v>7134847</v>
+        <v>7135195</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119953290</v>
+        <v>119950975</v>
       </c>
       <c r="B19" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,37 +2607,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503235</v>
+        <v>503152</v>
       </c>
       <c r="R19" t="n">
-        <v>7135189</v>
+        <v>7134944</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119947043</v>
+        <v>119950972</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503245</v>
+        <v>503157</v>
       </c>
       <c r="R20" t="n">
-        <v>7134683</v>
+        <v>7134940</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966724</v>
+        <v>119947420</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,41 +2807,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503195</v>
+        <v>503213</v>
       </c>
       <c r="R21" t="n">
-        <v>7134698</v>
+        <v>7134622</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2871,11 +2871,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119947420</v>
+        <v>119947387</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,25 +2909,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503213</v>
+        <v>503210</v>
       </c>
       <c r="R22" t="n">
-        <v>7134622</v>
+        <v>7134632</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3004,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119953208</v>
+        <v>119950857</v>
       </c>
       <c r="B23" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,37 +3015,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503164</v>
+        <v>503168</v>
       </c>
       <c r="R23" t="n">
-        <v>7135128</v>
+        <v>7134856</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3106,10 +3101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119947387</v>
+        <v>119946999</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3122,21 +3117,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503210</v>
+        <v>503249</v>
       </c>
       <c r="R24" t="n">
-        <v>7134632</v>
+        <v>7134683</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3208,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119953375</v>
+        <v>119949136</v>
       </c>
       <c r="B25" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3224,37 +3219,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503279</v>
+        <v>503213</v>
       </c>
       <c r="R25" t="n">
-        <v>7135237</v>
+        <v>7134603</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119953313</v>
+        <v>119966737</v>
       </c>
       <c r="B26" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503239</v>
+        <v>503354</v>
       </c>
       <c r="R26" t="n">
-        <v>7135198</v>
+        <v>7134564</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119945075</v>
+        <v>119953277</v>
       </c>
       <c r="B27" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3428,37 +3428,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503170</v>
+        <v>503236</v>
       </c>
       <c r="R27" t="n">
-        <v>7134825</v>
+        <v>7135178</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119945243</v>
+        <v>119966742</v>
       </c>
       <c r="B28" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,41 +3526,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503165</v>
+        <v>503371</v>
       </c>
       <c r="R28" t="n">
-        <v>7134719</v>
+        <v>7134522</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119945215</v>
+        <v>119948976</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3628,25 +3628,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503171</v>
+        <v>503222</v>
       </c>
       <c r="R29" t="n">
-        <v>7134729</v>
+        <v>7134576</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3718,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119953308</v>
+        <v>119945243</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3734,34 +3734,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503244</v>
+        <v>503165</v>
       </c>
       <c r="R30" t="n">
-        <v>7135195</v>
+        <v>7134719</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119949136</v>
+        <v>119953290</v>
       </c>
       <c r="B31" t="n">
-        <v>57473</v>
+        <v>79658</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,46 +3832,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503213</v>
+        <v>503235</v>
       </c>
       <c r="R31" t="n">
-        <v>7134603</v>
+        <v>7135189</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3927,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119948976</v>
+        <v>119948911</v>
       </c>
       <c r="B32" t="n">
-        <v>89650</v>
+        <v>79131</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,21 +3938,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503222</v>
+        <v>503190</v>
       </c>
       <c r="R32" t="n">
-        <v>7134576</v>
+        <v>7134550</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4029,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119946999</v>
+        <v>119945137</v>
       </c>
       <c r="B33" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4041,25 +4036,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4069,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503249</v>
+        <v>503172</v>
       </c>
       <c r="R33" t="n">
-        <v>7134683</v>
+        <v>7134763</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4131,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119966740</v>
+        <v>119944976</v>
       </c>
       <c r="B34" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4147,37 +4142,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503194</v>
+        <v>503197</v>
       </c>
       <c r="R34" t="n">
-        <v>7134678</v>
+        <v>7134856</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4233,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950802</v>
+        <v>119947114</v>
       </c>
       <c r="B35" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4249,21 +4244,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4273,13 +4268,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503165</v>
+        <v>503256</v>
       </c>
       <c r="R35" t="n">
-        <v>7134812</v>
+        <v>7134674</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4335,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119966744</v>
+        <v>119945252</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4347,41 +4342,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503354</v>
+        <v>503166</v>
       </c>
       <c r="R36" t="n">
-        <v>7134553</v>
+        <v>7134711</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4437,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950727</v>
+        <v>119944992</v>
       </c>
       <c r="B37" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4453,21 +4448,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4477,13 +4472,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503147</v>
+        <v>503182</v>
       </c>
       <c r="R37" t="n">
-        <v>7134810</v>
+        <v>7134856</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4539,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119966749</v>
+        <v>119966729</v>
       </c>
       <c r="B38" t="n">
-        <v>4915</v>
+        <v>79624</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4555,21 +4550,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101994</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4579,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503364</v>
+        <v>503291</v>
       </c>
       <c r="R38" t="n">
-        <v>7134522</v>
+        <v>7135241</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4615,11 +4610,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119950732</v>
+        <v>119950802</v>
       </c>
       <c r="B39" t="n">
-        <v>79131</v>
+        <v>89650</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4662,21 +4652,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4686,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503146</v>
+        <v>503165</v>
       </c>
       <c r="R39" t="n">
-        <v>7134809</v>
+        <v>7134812</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4748,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119953277</v>
+        <v>119966746</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4760,41 +4750,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503236</v>
+        <v>503256</v>
       </c>
       <c r="R40" t="n">
-        <v>7135178</v>
+        <v>7134674</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4850,10 +4840,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119947013</v>
+        <v>119966747</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>12337</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4862,41 +4852,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>101283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503258</v>
+        <v>503341</v>
       </c>
       <c r="R41" t="n">
-        <v>7134669</v>
+        <v>7134550</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4926,6 +4916,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4952,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119966733</v>
+        <v>119945215</v>
       </c>
       <c r="B42" t="n">
-        <v>79659</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4968,37 +4963,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503392</v>
+        <v>503171</v>
       </c>
       <c r="R42" t="n">
-        <v>7134464</v>
+        <v>7134729</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5054,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119966729</v>
+        <v>119945198</v>
       </c>
       <c r="B43" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5070,37 +5065,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503291</v>
+        <v>503176</v>
       </c>
       <c r="R43" t="n">
-        <v>7135241</v>
+        <v>7134750</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5156,10 +5151,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119950975</v>
+        <v>119953313</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5168,38 +5163,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503152</v>
+        <v>503239</v>
       </c>
       <c r="R44" t="n">
-        <v>7134944</v>
+        <v>7135198</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5258,10 +5253,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119953361</v>
+        <v>119950877</v>
       </c>
       <c r="B45" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5270,41 +5265,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503283</v>
+        <v>503166</v>
       </c>
       <c r="R45" t="n">
-        <v>7135226</v>
+        <v>7134864</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5360,10 +5355,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119949113</v>
+        <v>119944974</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5372,25 +5367,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5400,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503213</v>
+        <v>503197</v>
       </c>
       <c r="R46" t="n">
-        <v>7134599</v>
+        <v>7134847</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5462,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119950877</v>
+        <v>119966724</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5474,41 +5469,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503166</v>
+        <v>503195</v>
       </c>
       <c r="R47" t="n">
-        <v>7134864</v>
+        <v>7134698</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5538,6 +5533,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5564,10 +5564,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119966719</v>
+        <v>119948853</v>
       </c>
       <c r="B48" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5580,37 +5580,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503312</v>
+        <v>503204</v>
       </c>
       <c r="R48" t="n">
-        <v>7134559</v>
+        <v>7134538</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5666,10 +5666,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119944998</v>
+        <v>119949016</v>
       </c>
       <c r="B49" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5678,25 +5678,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5706,13 +5706,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503182</v>
+        <v>503196</v>
       </c>
       <c r="R49" t="n">
-        <v>7134859</v>
+        <v>7134584</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119953316</v>
+        <v>119953208</v>
       </c>
       <c r="B50" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5780,25 +5780,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503249</v>
+        <v>503164</v>
       </c>
       <c r="R50" t="n">
-        <v>7135183</v>
+        <v>7135128</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5870,10 +5870,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119966735</v>
+        <v>119966719</v>
       </c>
       <c r="B51" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5882,25 +5882,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5910,10 +5910,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503371</v>
+        <v>503312</v>
       </c>
       <c r="R51" t="n">
-        <v>7134532</v>
+        <v>7134559</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5972,7 +5972,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119949016</v>
+        <v>119947043</v>
       </c>
       <c r="B52" t="n">
         <v>91858</v>
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503196</v>
+        <v>503245</v>
       </c>
       <c r="R52" t="n">
-        <v>7134584</v>
+        <v>7134683</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6074,10 +6074,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119950521</v>
+        <v>119953316</v>
       </c>
       <c r="B53" t="n">
-        <v>79131</v>
+        <v>79652</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6086,38 +6086,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503238</v>
+        <v>503249</v>
       </c>
       <c r="R53" t="n">
-        <v>7134692</v>
+        <v>7135183</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6176,7 +6176,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119945137</v>
+        <v>119950932</v>
       </c>
       <c r="B54" t="n">
         <v>91858</v>
@@ -6216,10 +6216,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503172</v>
+        <v>503151</v>
       </c>
       <c r="R54" t="n">
-        <v>7134763</v>
+        <v>7134896</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6278,10 +6278,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119951025</v>
+        <v>119966740</v>
       </c>
       <c r="B55" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6294,37 +6294,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503166</v>
+        <v>503194</v>
       </c>
       <c r="R55" t="n">
-        <v>7134990</v>
+        <v>7134678</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6380,10 +6380,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119966728</v>
+        <v>119966720</v>
       </c>
       <c r="B56" t="n">
-        <v>79624</v>
+        <v>79131</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503285</v>
+        <v>503241</v>
       </c>
       <c r="R56" t="n">
-        <v>7134565</v>
+        <v>7134650</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119966746</v>
+        <v>119951025</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6494,41 +6494,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503256</v>
+        <v>503166</v>
       </c>
       <c r="R57" t="n">
-        <v>7134674</v>
+        <v>7134990</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119966720</v>
+        <v>119966744</v>
       </c>
       <c r="B58" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6596,25 +6596,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6624,10 +6624,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503241</v>
+        <v>503354</v>
       </c>
       <c r="R58" t="n">
-        <v>7134650</v>
+        <v>7134553</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119966739</v>
+        <v>119966748</v>
       </c>
       <c r="B59" t="n">
-        <v>78187</v>
+        <v>79658</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6698,25 +6698,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503196</v>
+        <v>503392</v>
       </c>
       <c r="R59" t="n">
-        <v>7134493</v>
+        <v>7134464</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6788,10 +6788,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119966737</v>
+        <v>119966739</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6804,21 +6804,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6828,10 +6828,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503354</v>
+        <v>503196</v>
       </c>
       <c r="R60" t="n">
-        <v>7134564</v>
+        <v>7134493</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6890,10 +6890,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119966743</v>
+        <v>119966741</v>
       </c>
       <c r="B61" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6902,25 +6902,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6930,10 +6930,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503321</v>
+        <v>503195</v>
       </c>
       <c r="R61" t="n">
-        <v>7134576</v>
+        <v>7134698</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119945198</v>
+        <v>119949113</v>
       </c>
       <c r="B62" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7004,25 +7004,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7032,10 +7032,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503176</v>
+        <v>503213</v>
       </c>
       <c r="R62" t="n">
-        <v>7134750</v>
+        <v>7134599</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7094,10 +7094,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119966748</v>
+        <v>119950704</v>
       </c>
       <c r="B63" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7110,37 +7110,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503392</v>
+        <v>503155</v>
       </c>
       <c r="R63" t="n">
-        <v>7134464</v>
+        <v>7134772</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7196,10 +7196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119966731</v>
+        <v>119966743</v>
       </c>
       <c r="B64" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7208,25 +7208,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503310</v>
+        <v>503321</v>
       </c>
       <c r="R64" t="n">
-        <v>7134560</v>
+        <v>7134576</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7298,10 +7298,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119953353</v>
+        <v>119966732</v>
       </c>
       <c r="B65" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7310,41 +7310,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503265</v>
+        <v>503285</v>
       </c>
       <c r="R65" t="n">
-        <v>7135233</v>
+        <v>7135231</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7400,10 +7400,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119966734</v>
+        <v>119950732</v>
       </c>
       <c r="B66" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7416,37 +7416,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503386</v>
+        <v>503146</v>
       </c>
       <c r="R66" t="n">
-        <v>7134487</v>
+        <v>7134809</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119966732</v>
+        <v>119948845</v>
       </c>
       <c r="B67" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7518,37 +7518,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503285</v>
+        <v>503204</v>
       </c>
       <c r="R67" t="n">
-        <v>7135231</v>
+        <v>7134543</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119950857</v>
+        <v>119966735</v>
       </c>
       <c r="B68" t="n">
         <v>78278</v>
@@ -7640,17 +7640,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503168</v>
+        <v>503371</v>
       </c>
       <c r="R68" t="n">
-        <v>7134856</v>
+        <v>7134532</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119966726</v>
+        <v>119953353</v>
       </c>
       <c r="B69" t="n">
-        <v>79652</v>
+        <v>90545</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7722,37 +7722,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503285</v>
+        <v>503265</v>
       </c>
       <c r="R69" t="n">
-        <v>7134565</v>
+        <v>7135233</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119966742</v>
+        <v>119950521</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7820,41 +7820,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503371</v>
+        <v>503238</v>
       </c>
       <c r="R70" t="n">
-        <v>7134522</v>
+        <v>7134692</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7910,10 +7910,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119950704</v>
+        <v>119966731</v>
       </c>
       <c r="B71" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7922,41 +7922,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503155</v>
+        <v>503310</v>
       </c>
       <c r="R71" t="n">
-        <v>7134772</v>
+        <v>7134560</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8012,10 +8012,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119945252</v>
+        <v>119966733</v>
       </c>
       <c r="B72" t="n">
-        <v>79131</v>
+        <v>79659</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8024,41 +8024,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503166</v>
+        <v>503392</v>
       </c>
       <c r="R72" t="n">
-        <v>7134711</v>
+        <v>7134464</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119944992</v>
+        <v>119948938</v>
       </c>
       <c r="B73" t="n">
-        <v>79131</v>
+        <v>89650</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8130,21 +8130,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8154,13 +8154,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503182</v>
+        <v>503207</v>
       </c>
       <c r="R73" t="n">
-        <v>7134856</v>
+        <v>7134561</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8216,10 +8216,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119944976</v>
+        <v>119966726</v>
       </c>
       <c r="B74" t="n">
-        <v>78278</v>
+        <v>79652</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8228,41 +8228,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503197</v>
+        <v>503285</v>
       </c>
       <c r="R74" t="n">
-        <v>7134856</v>
+        <v>7134565</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8318,10 +8318,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119950972</v>
+        <v>119953375</v>
       </c>
       <c r="B75" t="n">
-        <v>91901</v>
+        <v>78187</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8334,34 +8334,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503157</v>
+        <v>503279</v>
       </c>
       <c r="R75" t="n">
-        <v>7134940</v>
+        <v>7135237</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8420,10 +8420,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119950932</v>
+        <v>119966749</v>
       </c>
       <c r="B76" t="n">
-        <v>91858</v>
+        <v>4915</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8432,41 +8432,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>101994</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503151</v>
+        <v>503364</v>
       </c>
       <c r="R76" t="n">
-        <v>7134896</v>
+        <v>7134522</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8496,6 +8496,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8522,10 +8527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119948853</v>
+        <v>119950926</v>
       </c>
       <c r="B77" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8534,25 +8539,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8562,13 +8567,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503204</v>
+        <v>503153</v>
       </c>
       <c r="R77" t="n">
-        <v>7134538</v>
+        <v>7134897</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8624,10 +8629,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119966747</v>
+        <v>119966722</v>
       </c>
       <c r="B78" t="n">
-        <v>12337</v>
+        <v>89650</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8636,25 +8641,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>101283</v>
+        <v>1962</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8664,10 +8669,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503341</v>
+        <v>503218</v>
       </c>
       <c r="R78" t="n">
-        <v>7134550</v>
+        <v>7134517</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8700,11 +8705,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8731,10 +8731,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119948911</v>
+        <v>119950727</v>
       </c>
       <c r="B79" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8747,21 +8747,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8771,13 +8771,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503190</v>
+        <v>503147</v>
       </c>
       <c r="R79" t="n">
-        <v>7134550</v>
+        <v>7134810</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119948845</v>
+        <v>119944998</v>
       </c>
       <c r="B80" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8849,21 +8849,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8873,13 +8873,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503204</v>
+        <v>503182</v>
       </c>
       <c r="R80" t="n">
-        <v>7134543</v>
+        <v>7134859</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119966741</v>
+        <v>119945075</v>
       </c>
       <c r="B81" t="n">
         <v>78187</v>
@@ -8971,17 +8971,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503195</v>
+        <v>503170</v>
       </c>
       <c r="R81" t="n">
-        <v>7134698</v>
+        <v>7134825</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119948938</v>
+        <v>119966728</v>
       </c>
       <c r="B82" t="n">
-        <v>89650</v>
+        <v>79624</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,37 +9053,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503207</v>
+        <v>503285</v>
       </c>
       <c r="R82" t="n">
-        <v>7134561</v>
+        <v>7134565</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119966734</v>
+        <v>119953353</v>
       </c>
       <c r="B15" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,41 +2195,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503386</v>
+        <v>503265</v>
       </c>
       <c r="R15" t="n">
-        <v>7134487</v>
+        <v>7135233</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119953361</v>
+        <v>119966740</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,37 +2301,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503283</v>
+        <v>503194</v>
       </c>
       <c r="R16" t="n">
-        <v>7135226</v>
+        <v>7134678</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119947013</v>
+        <v>119953308</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,37 +2403,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503258</v>
+        <v>503244</v>
       </c>
       <c r="R17" t="n">
-        <v>7134669</v>
+        <v>7135195</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119953308</v>
+        <v>119966748</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,41 +2501,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503244</v>
+        <v>503392</v>
       </c>
       <c r="R18" t="n">
-        <v>7135195</v>
+        <v>7134464</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119950975</v>
+        <v>119966732</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,41 +2603,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503152</v>
+        <v>503285</v>
       </c>
       <c r="R19" t="n">
-        <v>7134944</v>
+        <v>7135231</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119950972</v>
+        <v>119966733</v>
       </c>
       <c r="B20" t="n">
-        <v>91901</v>
+        <v>79659</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,41 +2705,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5448</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503157</v>
+        <v>503392</v>
       </c>
       <c r="R20" t="n">
-        <v>7134940</v>
+        <v>7134464</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119947420</v>
+        <v>119966720</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,41 +2807,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503213</v>
+        <v>503241</v>
       </c>
       <c r="R21" t="n">
-        <v>7134622</v>
+        <v>7134650</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119947387</v>
+        <v>119945252</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503210</v>
+        <v>503166</v>
       </c>
       <c r="R22" t="n">
-        <v>7134632</v>
+        <v>7134711</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950857</v>
+        <v>119944992</v>
       </c>
       <c r="B23" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,21 +3015,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503168</v>
+        <v>503182</v>
       </c>
       <c r="R23" t="n">
         <v>7134856</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119946999</v>
+        <v>119945215</v>
       </c>
       <c r="B24" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,25 +3113,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503249</v>
+        <v>503171</v>
       </c>
       <c r="R24" t="n">
-        <v>7134683</v>
+        <v>7134729</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119949136</v>
+        <v>119948845</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,42 +3219,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503213</v>
+        <v>503204</v>
       </c>
       <c r="R25" t="n">
-        <v>7134603</v>
+        <v>7134543</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3310,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966737</v>
+        <v>119944976</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,37 +3321,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503354</v>
+        <v>503197</v>
       </c>
       <c r="R26" t="n">
-        <v>7134564</v>
+        <v>7134856</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3412,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119953277</v>
+        <v>119953375</v>
       </c>
       <c r="B27" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3428,21 +3423,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,13 +3447,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503236</v>
+        <v>503279</v>
       </c>
       <c r="R27" t="n">
-        <v>7135178</v>
+        <v>7135237</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119966742</v>
+        <v>119953361</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,41 +3521,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503371</v>
+        <v>503283</v>
       </c>
       <c r="R28" t="n">
-        <v>7134522</v>
+        <v>7135226</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3616,10 +3611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119948976</v>
+        <v>119949136</v>
       </c>
       <c r="B29" t="n">
-        <v>89650</v>
+        <v>57473</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3632,37 +3627,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503222</v>
+        <v>503213</v>
       </c>
       <c r="R29" t="n">
-        <v>7134576</v>
+        <v>7134603</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3718,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119945243</v>
+        <v>119966744</v>
       </c>
       <c r="B30" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3730,41 +3730,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503165</v>
+        <v>503354</v>
       </c>
       <c r="R30" t="n">
-        <v>7134719</v>
+        <v>7134553</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119953290</v>
+        <v>119946999</v>
       </c>
       <c r="B31" t="n">
-        <v>79658</v>
+        <v>79131</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,41 +3832,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503235</v>
+        <v>503249</v>
       </c>
       <c r="R31" t="n">
-        <v>7135189</v>
+        <v>7134683</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119948911</v>
+        <v>119951025</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>92048</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,21 +3938,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3962,13 +3962,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503190</v>
+        <v>503166</v>
       </c>
       <c r="R32" t="n">
-        <v>7134550</v>
+        <v>7134990</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119945137</v>
+        <v>119966734</v>
       </c>
       <c r="B33" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,41 +4036,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503172</v>
+        <v>503386</v>
       </c>
       <c r="R33" t="n">
-        <v>7134763</v>
+        <v>7134487</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119944976</v>
+        <v>119950727</v>
       </c>
       <c r="B34" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4142,21 +4142,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4166,13 +4166,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503197</v>
+        <v>503147</v>
       </c>
       <c r="R34" t="n">
-        <v>7134856</v>
+        <v>7134810</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119947114</v>
+        <v>119953290</v>
       </c>
       <c r="B35" t="n">
-        <v>78187</v>
+        <v>79658</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,41 +4240,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503256</v>
+        <v>503235</v>
       </c>
       <c r="R35" t="n">
-        <v>7134674</v>
+        <v>7135189</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119945252</v>
+        <v>119945243</v>
       </c>
       <c r="B36" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503166</v>
+        <v>503165</v>
       </c>
       <c r="R36" t="n">
-        <v>7134711</v>
+        <v>7134719</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119944992</v>
+        <v>119966729</v>
       </c>
       <c r="B37" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4448,37 +4448,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503182</v>
+        <v>503291</v>
       </c>
       <c r="R37" t="n">
-        <v>7134856</v>
+        <v>7135241</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119966729</v>
+        <v>119966719</v>
       </c>
       <c r="B38" t="n">
-        <v>79624</v>
+        <v>90545</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503291</v>
+        <v>503312</v>
       </c>
       <c r="R38" t="n">
-        <v>7135241</v>
+        <v>7134559</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119950802</v>
+        <v>119966728</v>
       </c>
       <c r="B39" t="n">
-        <v>89650</v>
+        <v>79624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,37 +4652,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503165</v>
+        <v>503285</v>
       </c>
       <c r="R39" t="n">
-        <v>7134812</v>
+        <v>7134565</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119966746</v>
+        <v>119966731</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4750,25 +4750,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503256</v>
+        <v>503310</v>
       </c>
       <c r="R40" t="n">
-        <v>7134674</v>
+        <v>7134560</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119966747</v>
+        <v>119945137</v>
       </c>
       <c r="B41" t="n">
-        <v>12337</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4852,41 +4852,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101283</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503341</v>
+        <v>503172</v>
       </c>
       <c r="R41" t="n">
-        <v>7134550</v>
+        <v>7134763</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4916,11 +4916,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4947,10 +4942,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119945215</v>
+        <v>119947013</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,25 +4954,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4987,13 +4982,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503171</v>
+        <v>503258</v>
       </c>
       <c r="R42" t="n">
-        <v>7134729</v>
+        <v>7134669</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5049,10 +5044,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119945198</v>
+        <v>119966722</v>
       </c>
       <c r="B43" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,37 +5060,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503176</v>
+        <v>503218</v>
       </c>
       <c r="R43" t="n">
-        <v>7134750</v>
+        <v>7134517</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5151,10 +5146,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119953313</v>
+        <v>119966735</v>
       </c>
       <c r="B44" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5167,37 +5162,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503239</v>
+        <v>503371</v>
       </c>
       <c r="R44" t="n">
-        <v>7135198</v>
+        <v>7134532</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5253,7 +5248,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119950877</v>
+        <v>119949016</v>
       </c>
       <c r="B45" t="n">
         <v>91858</v>
@@ -5293,10 +5288,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503166</v>
+        <v>503196</v>
       </c>
       <c r="R45" t="n">
-        <v>7134864</v>
+        <v>7134584</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5355,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119944974</v>
+        <v>119966749</v>
       </c>
       <c r="B46" t="n">
-        <v>78187</v>
+        <v>4915</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5371,37 +5366,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>101994</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503197</v>
+        <v>503364</v>
       </c>
       <c r="R46" t="n">
-        <v>7134847</v>
+        <v>7134522</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5431,6 +5426,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5457,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966724</v>
+        <v>119945075</v>
       </c>
       <c r="B47" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5473,37 +5473,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503195</v>
+        <v>503170</v>
       </c>
       <c r="R47" t="n">
-        <v>7134698</v>
+        <v>7134825</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5533,11 +5533,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5564,7 +5559,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119948853</v>
+        <v>119966742</v>
       </c>
       <c r="B48" t="n">
         <v>91858</v>
@@ -5600,17 +5595,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503204</v>
+        <v>503371</v>
       </c>
       <c r="R48" t="n">
-        <v>7134538</v>
+        <v>7134522</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5666,7 +5661,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119949016</v>
+        <v>119948853</v>
       </c>
       <c r="B49" t="n">
         <v>91858</v>
@@ -5706,10 +5701,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503196</v>
+        <v>503204</v>
       </c>
       <c r="R49" t="n">
-        <v>7134584</v>
+        <v>7134538</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5768,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119953208</v>
+        <v>119950975</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5780,38 +5775,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503164</v>
+        <v>503152</v>
       </c>
       <c r="R50" t="n">
-        <v>7135128</v>
+        <v>7134944</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5870,10 +5865,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119966719</v>
+        <v>119966726</v>
       </c>
       <c r="B51" t="n">
-        <v>90545</v>
+        <v>79652</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5886,21 +5881,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5910,10 +5905,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503312</v>
+        <v>503285</v>
       </c>
       <c r="R51" t="n">
-        <v>7134559</v>
+        <v>7134565</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5972,10 +5967,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119947043</v>
+        <v>119966747</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>12337</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5984,41 +5979,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>101283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503245</v>
+        <v>503341</v>
       </c>
       <c r="R52" t="n">
-        <v>7134683</v>
+        <v>7134550</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6048,6 +6043,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6074,10 +6074,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119953316</v>
+        <v>119948938</v>
       </c>
       <c r="B53" t="n">
-        <v>79652</v>
+        <v>89650</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6086,41 +6086,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503249</v>
+        <v>503207</v>
       </c>
       <c r="R53" t="n">
-        <v>7135183</v>
+        <v>7134561</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6176,10 +6176,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119950932</v>
+        <v>119950926</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6188,25 +6188,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503151</v>
+        <v>503153</v>
       </c>
       <c r="R54" t="n">
-        <v>7134896</v>
+        <v>7134897</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6278,10 +6278,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119966740</v>
+        <v>119950521</v>
       </c>
       <c r="B55" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6294,37 +6294,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503194</v>
+        <v>503238</v>
       </c>
       <c r="R55" t="n">
-        <v>7134678</v>
+        <v>7134692</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6380,10 +6380,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119966720</v>
+        <v>119966739</v>
       </c>
       <c r="B56" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503241</v>
+        <v>503196</v>
       </c>
       <c r="R56" t="n">
-        <v>7134650</v>
+        <v>7134493</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119951025</v>
+        <v>119944998</v>
       </c>
       <c r="B57" t="n">
-        <v>92048</v>
+        <v>78278</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6498,21 +6498,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6522,13 +6522,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503166</v>
+        <v>503182</v>
       </c>
       <c r="R57" t="n">
-        <v>7134990</v>
+        <v>7134859</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119966744</v>
+        <v>119966737</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6596,25 +6596,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6627,7 +6627,7 @@
         <v>503354</v>
       </c>
       <c r="R58" t="n">
-        <v>7134553</v>
+        <v>7134564</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119966748</v>
+        <v>119966724</v>
       </c>
       <c r="B59" t="n">
-        <v>79658</v>
+        <v>57473</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6698,25 +6698,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503392</v>
+        <v>503195</v>
       </c>
       <c r="R59" t="n">
-        <v>7134464</v>
+        <v>7134698</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6762,6 +6762,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6788,10 +6793,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119966739</v>
+        <v>119953277</v>
       </c>
       <c r="B60" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6804,37 +6809,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503196</v>
+        <v>503236</v>
       </c>
       <c r="R60" t="n">
-        <v>7134493</v>
+        <v>7135178</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6992,10 +6997,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119949113</v>
+        <v>119948911</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7004,25 +7009,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7032,10 +7037,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503213</v>
+        <v>503190</v>
       </c>
       <c r="R62" t="n">
-        <v>7134599</v>
+        <v>7134550</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7094,7 +7099,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119950704</v>
+        <v>119966746</v>
       </c>
       <c r="B63" t="n">
         <v>91858</v>
@@ -7130,17 +7135,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503155</v>
+        <v>503256</v>
       </c>
       <c r="R63" t="n">
-        <v>7134772</v>
+        <v>7134674</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7196,7 +7201,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119966743</v>
+        <v>119947420</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7232,17 +7237,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503321</v>
+        <v>503213</v>
       </c>
       <c r="R64" t="n">
-        <v>7134576</v>
+        <v>7134622</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7298,10 +7303,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119966732</v>
+        <v>119944974</v>
       </c>
       <c r="B65" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7314,37 +7319,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503285</v>
+        <v>503197</v>
       </c>
       <c r="R65" t="n">
-        <v>7135231</v>
+        <v>7134847</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7400,10 +7405,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119950732</v>
+        <v>119953313</v>
       </c>
       <c r="B66" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7416,37 +7421,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503146</v>
+        <v>503239</v>
       </c>
       <c r="R66" t="n">
-        <v>7134809</v>
+        <v>7135198</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7502,10 +7507,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119948845</v>
+        <v>119950802</v>
       </c>
       <c r="B67" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7518,21 +7523,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7542,13 +7547,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503204</v>
+        <v>503165</v>
       </c>
       <c r="R67" t="n">
-        <v>7134543</v>
+        <v>7134812</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7604,10 +7609,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966735</v>
+        <v>119948976</v>
       </c>
       <c r="B68" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7620,37 +7625,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503371</v>
+        <v>503222</v>
       </c>
       <c r="R68" t="n">
-        <v>7134532</v>
+        <v>7134576</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7706,10 +7711,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119953353</v>
+        <v>119947114</v>
       </c>
       <c r="B69" t="n">
-        <v>90545</v>
+        <v>78187</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7718,41 +7723,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503265</v>
+        <v>503256</v>
       </c>
       <c r="R69" t="n">
-        <v>7135233</v>
+        <v>7134674</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7808,10 +7813,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119950521</v>
+        <v>119950877</v>
       </c>
       <c r="B70" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7820,25 +7825,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7848,10 +7853,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503238</v>
+        <v>503166</v>
       </c>
       <c r="R70" t="n">
-        <v>7134692</v>
+        <v>7134864</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7910,10 +7915,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119966731</v>
+        <v>119950704</v>
       </c>
       <c r="B71" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7922,41 +7927,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503310</v>
+        <v>503155</v>
       </c>
       <c r="R71" t="n">
-        <v>7134560</v>
+        <v>7134772</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8012,10 +8017,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119966733</v>
+        <v>119950932</v>
       </c>
       <c r="B72" t="n">
-        <v>79659</v>
+        <v>91858</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8028,37 +8033,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503392</v>
+        <v>503151</v>
       </c>
       <c r="R72" t="n">
-        <v>7134464</v>
+        <v>7134896</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8114,10 +8119,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119948938</v>
+        <v>119953208</v>
       </c>
       <c r="B73" t="n">
-        <v>89650</v>
+        <v>79624</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8130,37 +8135,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503207</v>
+        <v>503164</v>
       </c>
       <c r="R73" t="n">
-        <v>7134561</v>
+        <v>7135128</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8216,10 +8221,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119966726</v>
+        <v>119950732</v>
       </c>
       <c r="B74" t="n">
-        <v>79652</v>
+        <v>79131</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8228,41 +8233,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503285</v>
+        <v>503146</v>
       </c>
       <c r="R74" t="n">
-        <v>7134565</v>
+        <v>7134809</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8318,10 +8323,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119953375</v>
+        <v>119953316</v>
       </c>
       <c r="B75" t="n">
-        <v>78187</v>
+        <v>79652</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8330,25 +8335,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8358,10 +8363,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503279</v>
+        <v>503249</v>
       </c>
       <c r="R75" t="n">
-        <v>7135237</v>
+        <v>7135183</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8420,10 +8425,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966749</v>
+        <v>119966743</v>
       </c>
       <c r="B76" t="n">
-        <v>4915</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8432,25 +8437,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>101994</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8460,10 +8465,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503364</v>
+        <v>503321</v>
       </c>
       <c r="R76" t="n">
-        <v>7134522</v>
+        <v>7134576</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8496,11 +8501,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8527,10 +8527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119950926</v>
+        <v>119950972</v>
       </c>
       <c r="B77" t="n">
-        <v>79131</v>
+        <v>91901</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>5448</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8567,13 +8567,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503153</v>
+        <v>503157</v>
       </c>
       <c r="R77" t="n">
-        <v>7134897</v>
+        <v>7134940</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119966722</v>
+        <v>119947043</v>
       </c>
       <c r="B78" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8641,41 +8641,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503218</v>
+        <v>503245</v>
       </c>
       <c r="R78" t="n">
-        <v>7134517</v>
+        <v>7134683</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119950727</v>
+        <v>119950857</v>
       </c>
       <c r="B79" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8747,21 +8747,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503147</v>
+        <v>503168</v>
       </c>
       <c r="R79" t="n">
-        <v>7134810</v>
+        <v>7134856</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119944998</v>
+        <v>119947387</v>
       </c>
       <c r="B80" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8849,21 +8849,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8873,13 +8873,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503182</v>
+        <v>503210</v>
       </c>
       <c r="R80" t="n">
-        <v>7134859</v>
+        <v>7134632</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119945075</v>
+        <v>119949113</v>
       </c>
       <c r="B81" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8947,25 +8947,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503170</v>
+        <v>503213</v>
       </c>
       <c r="R81" t="n">
-        <v>7134825</v>
+        <v>7134599</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119966728</v>
+        <v>119945198</v>
       </c>
       <c r="B82" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,37 +9053,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503285</v>
+        <v>503176</v>
       </c>
       <c r="R82" t="n">
-        <v>7134565</v>
+        <v>7134750</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -3611,10 +3611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119949136</v>
+        <v>119950727</v>
       </c>
       <c r="B29" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3627,42 +3627,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503213</v>
+        <v>503147</v>
       </c>
       <c r="R29" t="n">
-        <v>7134603</v>
+        <v>7134810</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3718,10 +3713,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119966744</v>
+        <v>119949136</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3730,38 +3725,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503354</v>
+        <v>503213</v>
       </c>
       <c r="R30" t="n">
-        <v>7134553</v>
+        <v>7134603</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119946999</v>
+        <v>119966744</v>
       </c>
       <c r="B31" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,41 +3832,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503249</v>
+        <v>503354</v>
       </c>
       <c r="R31" t="n">
-        <v>7134683</v>
+        <v>7134553</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119951025</v>
+        <v>119946999</v>
       </c>
       <c r="B32" t="n">
-        <v>92048</v>
+        <v>79131</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,21 +3938,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3962,13 +3962,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503166</v>
+        <v>503249</v>
       </c>
       <c r="R32" t="n">
-        <v>7134990</v>
+        <v>7134683</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119966734</v>
+        <v>119951025</v>
       </c>
       <c r="B33" t="n">
-        <v>78278</v>
+        <v>92048</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4040,37 +4040,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503386</v>
+        <v>503166</v>
       </c>
       <c r="R33" t="n">
-        <v>7134487</v>
+        <v>7134990</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950727</v>
+        <v>119966734</v>
       </c>
       <c r="B34" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4142,37 +4142,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503147</v>
+        <v>503386</v>
       </c>
       <c r="R34" t="n">
-        <v>7134810</v>
+        <v>7134487</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6997,10 +6997,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119948911</v>
+        <v>119947420</v>
       </c>
       <c r="B62" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7009,25 +7009,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503190</v>
+        <v>503213</v>
       </c>
       <c r="R62" t="n">
-        <v>7134550</v>
+        <v>7134622</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7099,10 +7099,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119966746</v>
+        <v>119944974</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7111,41 +7111,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503256</v>
+        <v>503197</v>
       </c>
       <c r="R63" t="n">
-        <v>7134674</v>
+        <v>7134847</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119947420</v>
+        <v>119966746</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7237,17 +7237,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503213</v>
+        <v>503256</v>
       </c>
       <c r="R64" t="n">
-        <v>7134622</v>
+        <v>7134674</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119944974</v>
+        <v>119948911</v>
       </c>
       <c r="B65" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7319,21 +7319,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503197</v>
+        <v>503190</v>
       </c>
       <c r="R65" t="n">
-        <v>7134847</v>
+        <v>7134550</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7405,10 +7405,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119953313</v>
+        <v>119948976</v>
       </c>
       <c r="B66" t="n">
-        <v>79624</v>
+        <v>89650</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7421,34 +7421,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503239</v>
+        <v>503222</v>
       </c>
       <c r="R66" t="n">
-        <v>7135198</v>
+        <v>7134576</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7507,10 +7507,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119950802</v>
+        <v>119947114</v>
       </c>
       <c r="B67" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7547,13 +7547,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503165</v>
+        <v>503256</v>
       </c>
       <c r="R67" t="n">
-        <v>7134812</v>
+        <v>7134674</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7609,10 +7609,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119948976</v>
+        <v>119953313</v>
       </c>
       <c r="B68" t="n">
-        <v>89650</v>
+        <v>79624</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7625,34 +7625,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503222</v>
+        <v>503239</v>
       </c>
       <c r="R68" t="n">
-        <v>7134576</v>
+        <v>7135198</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119947114</v>
+        <v>119950802</v>
       </c>
       <c r="B69" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7727,21 +7727,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7751,13 +7751,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503256</v>
+        <v>503165</v>
       </c>
       <c r="R69" t="n">
-        <v>7134674</v>
+        <v>7134812</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966743</v>
+        <v>119947043</v>
       </c>
       <c r="B76" t="n">
         <v>91858</v>
@@ -8461,17 +8461,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503321</v>
+        <v>503245</v>
       </c>
       <c r="R76" t="n">
-        <v>7134576</v>
+        <v>7134683</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8527,10 +8527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119950972</v>
+        <v>119966743</v>
       </c>
       <c r="B77" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8539,41 +8539,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503157</v>
+        <v>503321</v>
       </c>
       <c r="R77" t="n">
-        <v>7134940</v>
+        <v>7134576</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119947043</v>
+        <v>119950972</v>
       </c>
       <c r="B78" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8641,25 +8641,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503245</v>
+        <v>503157</v>
       </c>
       <c r="R78" t="n">
-        <v>7134683</v>
+        <v>7134940</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119953353</v>
+        <v>119945075</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,41 +2195,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503265</v>
+        <v>503170</v>
       </c>
       <c r="R15" t="n">
-        <v>7135233</v>
+        <v>7134825</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119966740</v>
+        <v>119944998</v>
       </c>
       <c r="B16" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,37 +2301,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503194</v>
+        <v>503182</v>
       </c>
       <c r="R16" t="n">
-        <v>7134678</v>
+        <v>7134859</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119953308</v>
+        <v>119950975</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,38 +2399,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503244</v>
+        <v>503152</v>
       </c>
       <c r="R17" t="n">
-        <v>7135195</v>
+        <v>7134944</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119966748</v>
+        <v>119950932</v>
       </c>
       <c r="B18" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,37 +2505,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503392</v>
+        <v>503151</v>
       </c>
       <c r="R18" t="n">
-        <v>7134464</v>
+        <v>7134896</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119966732</v>
+        <v>119966734</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503285</v>
+        <v>503386</v>
       </c>
       <c r="R19" t="n">
-        <v>7135231</v>
+        <v>7134487</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119966733</v>
+        <v>119966735</v>
       </c>
       <c r="B20" t="n">
-        <v>79659</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503392</v>
+        <v>503371</v>
       </c>
       <c r="R20" t="n">
-        <v>7134464</v>
+        <v>7134532</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966720</v>
+        <v>119950732</v>
       </c>
       <c r="B21" t="n">
         <v>79131</v>
@@ -2831,17 +2831,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503241</v>
+        <v>503146</v>
       </c>
       <c r="R21" t="n">
-        <v>7134650</v>
+        <v>7134809</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119945252</v>
+        <v>119950521</v>
       </c>
       <c r="B22" t="n">
         <v>79131</v>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503166</v>
+        <v>503238</v>
       </c>
       <c r="R22" t="n">
-        <v>7134711</v>
+        <v>7134692</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119944992</v>
+        <v>119966729</v>
       </c>
       <c r="B23" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,37 +3015,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503182</v>
+        <v>503291</v>
       </c>
       <c r="R23" t="n">
-        <v>7134856</v>
+        <v>7135241</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119945215</v>
+        <v>119966728</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,41 +3113,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503171</v>
+        <v>503285</v>
       </c>
       <c r="R24" t="n">
-        <v>7134729</v>
+        <v>7134565</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119948845</v>
+        <v>119945215</v>
       </c>
       <c r="B25" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503204</v>
+        <v>503171</v>
       </c>
       <c r="R25" t="n">
-        <v>7134543</v>
+        <v>7134729</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119944976</v>
+        <v>119966737</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3321,37 +3321,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503197</v>
+        <v>503354</v>
       </c>
       <c r="R26" t="n">
-        <v>7134856</v>
+        <v>7134564</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119953375</v>
+        <v>119948976</v>
       </c>
       <c r="B27" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3423,34 +3423,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503279</v>
+        <v>503222</v>
       </c>
       <c r="R27" t="n">
-        <v>7135237</v>
+        <v>7134576</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119953361</v>
+        <v>119950877</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,41 +3521,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503283</v>
+        <v>503166</v>
       </c>
       <c r="R28" t="n">
-        <v>7135226</v>
+        <v>7134864</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3611,10 +3611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950727</v>
+        <v>119948911</v>
       </c>
       <c r="B29" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503147</v>
+        <v>503190</v>
       </c>
       <c r="R29" t="n">
-        <v>7134810</v>
+        <v>7134550</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119949136</v>
+        <v>119947013</v>
       </c>
       <c r="B30" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3729,42 +3729,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503213</v>
+        <v>503258</v>
       </c>
       <c r="R30" t="n">
-        <v>7134603</v>
+        <v>7134669</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3820,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119966744</v>
+        <v>119953208</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,41 +3827,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503354</v>
+        <v>503164</v>
       </c>
       <c r="R31" t="n">
-        <v>7134553</v>
+        <v>7135128</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119946999</v>
+        <v>119949016</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,25 +3929,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3962,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503249</v>
+        <v>503196</v>
       </c>
       <c r="R32" t="n">
-        <v>7134683</v>
+        <v>7134584</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4024,10 +4019,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119951025</v>
+        <v>119953353</v>
       </c>
       <c r="B33" t="n">
-        <v>92048</v>
+        <v>90545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,38 +4031,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503166</v>
+        <v>503265</v>
       </c>
       <c r="R33" t="n">
-        <v>7134990</v>
+        <v>7135233</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,10 +4121,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119966734</v>
+        <v>119950727</v>
       </c>
       <c r="B34" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4142,37 +4137,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503386</v>
+        <v>503147</v>
       </c>
       <c r="R34" t="n">
-        <v>7134487</v>
+        <v>7134810</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,10 +4223,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119953290</v>
+        <v>119966749</v>
       </c>
       <c r="B35" t="n">
-        <v>79658</v>
+        <v>4915</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,41 +4235,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>101994</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503235</v>
+        <v>503364</v>
       </c>
       <c r="R35" t="n">
-        <v>7135189</v>
+        <v>7134522</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4304,6 +4299,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119945243</v>
+        <v>119946999</v>
       </c>
       <c r="B36" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503165</v>
+        <v>503249</v>
       </c>
       <c r="R36" t="n">
-        <v>7134719</v>
+        <v>7134683</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119966729</v>
+        <v>119966719</v>
       </c>
       <c r="B37" t="n">
-        <v>79624</v>
+        <v>90545</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,25 +4444,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503291</v>
+        <v>503312</v>
       </c>
       <c r="R37" t="n">
-        <v>7135241</v>
+        <v>7134559</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119966719</v>
+        <v>119966746</v>
       </c>
       <c r="B38" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4550,21 +4550,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503312</v>
+        <v>503256</v>
       </c>
       <c r="R38" t="n">
-        <v>7134559</v>
+        <v>7134674</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119966728</v>
+        <v>119953316</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,41 +4648,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503285</v>
+        <v>503249</v>
       </c>
       <c r="R39" t="n">
-        <v>7134565</v>
+        <v>7135183</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119966731</v>
+        <v>119966726</v>
       </c>
       <c r="B40" t="n">
-        <v>78279</v>
+        <v>79652</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4750,25 +4750,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503310</v>
+        <v>503285</v>
       </c>
       <c r="R40" t="n">
-        <v>7134560</v>
+        <v>7134565</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119945137</v>
+        <v>119966741</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4852,41 +4852,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503172</v>
+        <v>503195</v>
       </c>
       <c r="R41" t="n">
-        <v>7134763</v>
+        <v>7134698</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119947013</v>
+        <v>119947387</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4958,21 +4958,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4982,13 +4982,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503258</v>
+        <v>503210</v>
       </c>
       <c r="R42" t="n">
-        <v>7134669</v>
+        <v>7134632</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119966722</v>
+        <v>119948845</v>
       </c>
       <c r="B43" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5060,37 +5060,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503218</v>
+        <v>503204</v>
       </c>
       <c r="R43" t="n">
-        <v>7134517</v>
+        <v>7134543</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119966735</v>
+        <v>119950704</v>
       </c>
       <c r="B44" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5158,41 +5158,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503371</v>
+        <v>503155</v>
       </c>
       <c r="R44" t="n">
-        <v>7134532</v>
+        <v>7134772</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119949016</v>
+        <v>119951025</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5260,25 +5260,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5288,13 +5288,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503196</v>
+        <v>503166</v>
       </c>
       <c r="R45" t="n">
-        <v>7134584</v>
+        <v>7134990</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966749</v>
+        <v>119966722</v>
       </c>
       <c r="B46" t="n">
-        <v>4915</v>
+        <v>89650</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5366,21 +5366,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101994</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503364</v>
+        <v>503218</v>
       </c>
       <c r="R46" t="n">
-        <v>7134522</v>
+        <v>7134517</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5426,11 +5426,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5457,7 +5452,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119945075</v>
+        <v>119953375</v>
       </c>
       <c r="B47" t="n">
         <v>78187</v>
@@ -5493,14 +5488,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503170</v>
+        <v>503279</v>
       </c>
       <c r="R47" t="n">
-        <v>7134825</v>
+        <v>7135237</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5559,10 +5554,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119966742</v>
+        <v>119966724</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5571,25 +5566,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5599,10 +5594,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503371</v>
+        <v>503195</v>
       </c>
       <c r="R48" t="n">
-        <v>7134522</v>
+        <v>7134698</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5635,6 +5630,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5661,10 +5661,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119948853</v>
+        <v>119966739</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5673,41 +5673,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503204</v>
+        <v>503196</v>
       </c>
       <c r="R49" t="n">
-        <v>7134538</v>
+        <v>7134493</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119950975</v>
+        <v>119950802</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5775,25 +5775,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5803,13 +5803,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503152</v>
+        <v>503165</v>
       </c>
       <c r="R50" t="n">
-        <v>7134944</v>
+        <v>7134812</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119966726</v>
+        <v>119945198</v>
       </c>
       <c r="B51" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5877,41 +5877,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503285</v>
+        <v>503176</v>
       </c>
       <c r="R51" t="n">
-        <v>7134565</v>
+        <v>7134750</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5967,10 +5967,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119966747</v>
+        <v>119950926</v>
       </c>
       <c r="B52" t="n">
-        <v>12337</v>
+        <v>79131</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5979,41 +5979,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101283</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503341</v>
+        <v>503153</v>
       </c>
       <c r="R52" t="n">
-        <v>7134550</v>
+        <v>7134897</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6043,11 +6043,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6074,10 +6069,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119948938</v>
+        <v>119949113</v>
       </c>
       <c r="B53" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6086,25 +6081,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6114,13 +6109,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503207</v>
+        <v>503213</v>
       </c>
       <c r="R53" t="n">
-        <v>7134561</v>
+        <v>7134599</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6176,10 +6171,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119950926</v>
+        <v>119950857</v>
       </c>
       <c r="B54" t="n">
-        <v>79131</v>
+        <v>78278</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6192,21 +6187,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6216,10 +6211,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503153</v>
+        <v>503168</v>
       </c>
       <c r="R54" t="n">
-        <v>7134897</v>
+        <v>7134856</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6278,10 +6273,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119950521</v>
+        <v>119953361</v>
       </c>
       <c r="B55" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6294,37 +6289,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503238</v>
+        <v>503283</v>
       </c>
       <c r="R55" t="n">
-        <v>7134692</v>
+        <v>7135226</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6380,10 +6375,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119966739</v>
+        <v>119966747</v>
       </c>
       <c r="B56" t="n">
-        <v>78187</v>
+        <v>12337</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6392,25 +6387,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>101283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6420,10 +6415,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503196</v>
+        <v>503341</v>
       </c>
       <c r="R56" t="n">
-        <v>7134493</v>
+        <v>7134550</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6456,6 +6451,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6482,10 +6482,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119944998</v>
+        <v>119945137</v>
       </c>
       <c r="B57" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6494,25 +6494,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6522,13 +6522,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503182</v>
+        <v>503172</v>
       </c>
       <c r="R57" t="n">
-        <v>7134859</v>
+        <v>7134763</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119966737</v>
+        <v>119953308</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6600,37 +6600,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503354</v>
+        <v>503244</v>
       </c>
       <c r="R58" t="n">
-        <v>7134564</v>
+        <v>7135195</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119966724</v>
+        <v>119944992</v>
       </c>
       <c r="B59" t="n">
-        <v>57473</v>
+        <v>79131</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6702,37 +6702,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503195</v>
+        <v>503182</v>
       </c>
       <c r="R59" t="n">
-        <v>7134698</v>
+        <v>7134856</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6762,11 +6762,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6793,10 +6788,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119953277</v>
+        <v>119945243</v>
       </c>
       <c r="B60" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6809,37 +6804,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503236</v>
+        <v>503165</v>
       </c>
       <c r="R60" t="n">
-        <v>7135178</v>
+        <v>7134719</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6895,10 +6890,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119966741</v>
+        <v>119953277</v>
       </c>
       <c r="B61" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6911,37 +6906,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503195</v>
+        <v>503236</v>
       </c>
       <c r="R61" t="n">
-        <v>7134698</v>
+        <v>7135178</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6997,7 +6992,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119947420</v>
+        <v>119966742</v>
       </c>
       <c r="B62" t="n">
         <v>91858</v>
@@ -7033,17 +7028,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503213</v>
+        <v>503371</v>
       </c>
       <c r="R62" t="n">
-        <v>7134622</v>
+        <v>7134522</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7099,10 +7094,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119944974</v>
+        <v>119966744</v>
       </c>
       <c r="B63" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7111,41 +7106,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503197</v>
+        <v>503354</v>
       </c>
       <c r="R63" t="n">
-        <v>7134847</v>
+        <v>7134553</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7201,10 +7196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119966746</v>
+        <v>119966740</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7213,25 +7208,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7241,10 +7236,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503256</v>
+        <v>503194</v>
       </c>
       <c r="R64" t="n">
-        <v>7134674</v>
+        <v>7134678</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7303,10 +7298,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119948911</v>
+        <v>119966732</v>
       </c>
       <c r="B65" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7319,37 +7314,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503190</v>
+        <v>503285</v>
       </c>
       <c r="R65" t="n">
-        <v>7134550</v>
+        <v>7135231</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7405,7 +7400,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119948976</v>
+        <v>119948938</v>
       </c>
       <c r="B66" t="n">
         <v>89650</v>
@@ -7445,13 +7440,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503222</v>
+        <v>503207</v>
       </c>
       <c r="R66" t="n">
-        <v>7134576</v>
+        <v>7134561</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7609,10 +7604,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119953313</v>
+        <v>119950972</v>
       </c>
       <c r="B68" t="n">
-        <v>79624</v>
+        <v>91901</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7625,34 +7620,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>5448</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503239</v>
+        <v>503157</v>
       </c>
       <c r="R68" t="n">
-        <v>7135198</v>
+        <v>7134940</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7711,10 +7706,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119950802</v>
+        <v>119953290</v>
       </c>
       <c r="B69" t="n">
-        <v>89650</v>
+        <v>79658</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7723,38 +7718,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1962</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503165</v>
+        <v>503235</v>
       </c>
       <c r="R69" t="n">
-        <v>7134812</v>
+        <v>7135189</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7813,10 +7808,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119950877</v>
+        <v>119966720</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7825,41 +7820,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503166</v>
+        <v>503241</v>
       </c>
       <c r="R70" t="n">
-        <v>7134864</v>
+        <v>7134650</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7915,10 +7910,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119950704</v>
+        <v>119953313</v>
       </c>
       <c r="B71" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7927,38 +7922,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503155</v>
+        <v>503239</v>
       </c>
       <c r="R71" t="n">
-        <v>7134772</v>
+        <v>7135198</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8017,7 +8012,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119950932</v>
+        <v>119948853</v>
       </c>
       <c r="B72" t="n">
         <v>91858</v>
@@ -8057,10 +8052,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503151</v>
+        <v>503204</v>
       </c>
       <c r="R72" t="n">
-        <v>7134896</v>
+        <v>7134538</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8119,10 +8114,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119953208</v>
+        <v>119947420</v>
       </c>
       <c r="B73" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8131,38 +8126,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503164</v>
+        <v>503213</v>
       </c>
       <c r="R73" t="n">
-        <v>7135128</v>
+        <v>7134622</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8221,10 +8216,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119950732</v>
+        <v>119966748</v>
       </c>
       <c r="B74" t="n">
-        <v>79131</v>
+        <v>79658</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8233,41 +8228,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503146</v>
+        <v>503392</v>
       </c>
       <c r="R74" t="n">
-        <v>7134809</v>
+        <v>7134464</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8323,10 +8318,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119953316</v>
+        <v>119949136</v>
       </c>
       <c r="B75" t="n">
-        <v>79652</v>
+        <v>57473</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8335,41 +8330,46 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503249</v>
+        <v>503213</v>
       </c>
       <c r="R75" t="n">
-        <v>7135183</v>
+        <v>7134603</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8527,10 +8527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966743</v>
+        <v>119966733</v>
       </c>
       <c r="B77" t="n">
-        <v>91858</v>
+        <v>79659</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503321</v>
+        <v>503392</v>
       </c>
       <c r="R77" t="n">
-        <v>7134576</v>
+        <v>7134464</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119950972</v>
+        <v>119944974</v>
       </c>
       <c r="B78" t="n">
-        <v>91901</v>
+        <v>78187</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8645,21 +8645,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503157</v>
+        <v>503197</v>
       </c>
       <c r="R78" t="n">
-        <v>7134940</v>
+        <v>7134847</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119950857</v>
+        <v>119966743</v>
       </c>
       <c r="B79" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8743,41 +8743,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503168</v>
+        <v>503321</v>
       </c>
       <c r="R79" t="n">
-        <v>7134856</v>
+        <v>7134576</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119947387</v>
+        <v>119966731</v>
       </c>
       <c r="B80" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8849,37 +8849,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503210</v>
+        <v>503310</v>
       </c>
       <c r="R80" t="n">
-        <v>7134632</v>
+        <v>7134560</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119949113</v>
+        <v>119944976</v>
       </c>
       <c r="B81" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8947,25 +8947,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503213</v>
+        <v>503197</v>
       </c>
       <c r="R81" t="n">
-        <v>7134599</v>
+        <v>7134856</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119945198</v>
+        <v>119945252</v>
       </c>
       <c r="B82" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,21 +9053,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503176</v>
+        <v>503166</v>
       </c>
       <c r="R82" t="n">
-        <v>7134750</v>
+        <v>7134711</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119945075</v>
+        <v>119950704</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,25 +2195,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503170</v>
+        <v>503155</v>
       </c>
       <c r="R15" t="n">
-        <v>7134825</v>
+        <v>7134772</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119944998</v>
+        <v>119966742</v>
       </c>
       <c r="B16" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,41 +2297,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503182</v>
+        <v>503371</v>
       </c>
       <c r="R16" t="n">
-        <v>7134859</v>
+        <v>7134522</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119950975</v>
+        <v>119947043</v>
       </c>
       <c r="B17" t="n">
         <v>91858</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503152</v>
+        <v>503245</v>
       </c>
       <c r="R17" t="n">
-        <v>7134944</v>
+        <v>7134683</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2489,7 +2489,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119950932</v>
+        <v>119947420</v>
       </c>
       <c r="B18" t="n">
         <v>91858</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503151</v>
+        <v>503213</v>
       </c>
       <c r="R18" t="n">
-        <v>7134896</v>
+        <v>7134622</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119966734</v>
+        <v>119950521</v>
       </c>
       <c r="B19" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,37 +2607,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503386</v>
+        <v>503238</v>
       </c>
       <c r="R19" t="n">
-        <v>7134487</v>
+        <v>7134692</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119966735</v>
+        <v>119953316</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>79652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,41 +2705,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503371</v>
+        <v>503249</v>
       </c>
       <c r="R20" t="n">
-        <v>7134532</v>
+        <v>7135183</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119950732</v>
+        <v>119966737</v>
       </c>
       <c r="B21" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503146</v>
+        <v>503354</v>
       </c>
       <c r="R21" t="n">
-        <v>7134809</v>
+        <v>7134564</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950521</v>
+        <v>119953208</v>
       </c>
       <c r="B22" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,34 +2913,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503238</v>
+        <v>503164</v>
       </c>
       <c r="R22" t="n">
-        <v>7134692</v>
+        <v>7135128</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119966729</v>
+        <v>119947114</v>
       </c>
       <c r="B23" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,37 +3015,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503291</v>
+        <v>503256</v>
       </c>
       <c r="R23" t="n">
-        <v>7135241</v>
+        <v>7134674</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119966728</v>
+        <v>119949113</v>
       </c>
       <c r="B24" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,41 +3113,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503285</v>
+        <v>503213</v>
       </c>
       <c r="R24" t="n">
-        <v>7134565</v>
+        <v>7134599</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119945215</v>
+        <v>119966729</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,41 +3215,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503171</v>
+        <v>503291</v>
       </c>
       <c r="R25" t="n">
-        <v>7134729</v>
+        <v>7135241</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966737</v>
+        <v>119966735</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503354</v>
+        <v>503371</v>
       </c>
       <c r="R26" t="n">
-        <v>7134564</v>
+        <v>7134532</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119948976</v>
+        <v>119945215</v>
       </c>
       <c r="B27" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,25 +3419,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503222</v>
+        <v>503171</v>
       </c>
       <c r="R27" t="n">
-        <v>7134576</v>
+        <v>7134729</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950877</v>
+        <v>119950732</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,25 +3521,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,13 +3549,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503166</v>
+        <v>503146</v>
       </c>
       <c r="R28" t="n">
-        <v>7134864</v>
+        <v>7134809</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119947013</v>
+        <v>119950802</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3729,21 +3729,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503258</v>
+        <v>503165</v>
       </c>
       <c r="R30" t="n">
-        <v>7134669</v>
+        <v>7134812</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119953208</v>
+        <v>119950926</v>
       </c>
       <c r="B31" t="n">
-        <v>79624</v>
+        <v>79131</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,37 +3831,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503164</v>
+        <v>503153</v>
       </c>
       <c r="R31" t="n">
-        <v>7135128</v>
+        <v>7134897</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119949016</v>
+        <v>119948853</v>
       </c>
       <c r="B32" t="n">
         <v>91858</v>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503196</v>
+        <v>503204</v>
       </c>
       <c r="R32" t="n">
-        <v>7134584</v>
+        <v>7134538</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119953353</v>
+        <v>119966749</v>
       </c>
       <c r="B33" t="n">
-        <v>90545</v>
+        <v>4915</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4031,41 +4031,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>101994</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503265</v>
+        <v>503364</v>
       </c>
       <c r="R33" t="n">
-        <v>7135233</v>
+        <v>7134522</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4095,6 +4095,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4121,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950727</v>
+        <v>119944976</v>
       </c>
       <c r="B34" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4137,21 +4142,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4161,13 +4166,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503147</v>
+        <v>503197</v>
       </c>
       <c r="R34" t="n">
-        <v>7134810</v>
+        <v>7134856</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119966749</v>
+        <v>119966719</v>
       </c>
       <c r="B35" t="n">
-        <v>4915</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4235,25 +4240,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101994</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4263,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503364</v>
+        <v>503312</v>
       </c>
       <c r="R35" t="n">
-        <v>7134522</v>
+        <v>7134559</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4299,11 +4304,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119946999</v>
+        <v>119953313</v>
       </c>
       <c r="B36" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,34 +4346,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503249</v>
+        <v>503239</v>
       </c>
       <c r="R36" t="n">
-        <v>7134683</v>
+        <v>7135198</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119966719</v>
+        <v>119950727</v>
       </c>
       <c r="B37" t="n">
-        <v>90545</v>
+        <v>78279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,41 +4444,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503312</v>
+        <v>503147</v>
       </c>
       <c r="R37" t="n">
-        <v>7134559</v>
+        <v>7134810</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119966746</v>
+        <v>119966731</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503256</v>
+        <v>503310</v>
       </c>
       <c r="R38" t="n">
-        <v>7134674</v>
+        <v>7134560</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119953316</v>
+        <v>119947387</v>
       </c>
       <c r="B39" t="n">
-        <v>79652</v>
+        <v>78187</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,38 +4648,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503249</v>
+        <v>503210</v>
       </c>
       <c r="R39" t="n">
-        <v>7135183</v>
+        <v>7134632</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119966726</v>
+        <v>119966746</v>
       </c>
       <c r="B40" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503285</v>
+        <v>503256</v>
       </c>
       <c r="R40" t="n">
-        <v>7134565</v>
+        <v>7134674</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119966741</v>
+        <v>119966739</v>
       </c>
       <c r="B41" t="n">
         <v>78187</v>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503195</v>
+        <v>503196</v>
       </c>
       <c r="R41" t="n">
-        <v>7134698</v>
+        <v>7134493</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119947387</v>
+        <v>119966733</v>
       </c>
       <c r="B42" t="n">
-        <v>78187</v>
+        <v>79659</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4954,41 +4954,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503210</v>
+        <v>503392</v>
       </c>
       <c r="R42" t="n">
-        <v>7134632</v>
+        <v>7134464</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119948845</v>
+        <v>119946999</v>
       </c>
       <c r="B43" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5060,21 +5060,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5084,10 +5084,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503204</v>
+        <v>503249</v>
       </c>
       <c r="R43" t="n">
-        <v>7134543</v>
+        <v>7134683</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119950704</v>
+        <v>119945252</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5158,25 +5158,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5186,10 +5186,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503155</v>
+        <v>503166</v>
       </c>
       <c r="R44" t="n">
-        <v>7134772</v>
+        <v>7134711</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119951025</v>
+        <v>119950975</v>
       </c>
       <c r="B45" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5260,25 +5260,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5288,13 +5288,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503166</v>
+        <v>503152</v>
       </c>
       <c r="R45" t="n">
-        <v>7134990</v>
+        <v>7134944</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119966722</v>
+        <v>119953353</v>
       </c>
       <c r="B46" t="n">
-        <v>89650</v>
+        <v>90545</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,41 +5362,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503218</v>
+        <v>503265</v>
       </c>
       <c r="R46" t="n">
-        <v>7134517</v>
+        <v>7135233</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119953375</v>
+        <v>119966741</v>
       </c>
       <c r="B47" t="n">
         <v>78187</v>
@@ -5488,17 +5488,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503279</v>
+        <v>503195</v>
       </c>
       <c r="R47" t="n">
-        <v>7135237</v>
+        <v>7134698</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119966724</v>
+        <v>119945198</v>
       </c>
       <c r="B48" t="n">
-        <v>57473</v>
+        <v>78278</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5570,37 +5570,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503195</v>
+        <v>503176</v>
       </c>
       <c r="R48" t="n">
-        <v>7134698</v>
+        <v>7134750</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5630,11 +5630,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5661,7 +5656,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119966739</v>
+        <v>119948845</v>
       </c>
       <c r="B49" t="n">
         <v>78187</v>
@@ -5697,17 +5692,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503196</v>
+        <v>503204</v>
       </c>
       <c r="R49" t="n">
-        <v>7134493</v>
+        <v>7134543</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,10 +5758,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119950802</v>
+        <v>119949016</v>
       </c>
       <c r="B50" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5775,25 +5770,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5803,13 +5798,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503165</v>
+        <v>503196</v>
       </c>
       <c r="R50" t="n">
-        <v>7134812</v>
+        <v>7134584</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5865,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119945198</v>
+        <v>119949136</v>
       </c>
       <c r="B51" t="n">
-        <v>78278</v>
+        <v>57473</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5881,37 +5876,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503176</v>
+        <v>503213</v>
       </c>
       <c r="R51" t="n">
-        <v>7134750</v>
+        <v>7134603</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5967,10 +5967,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119950926</v>
+        <v>119945075</v>
       </c>
       <c r="B52" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5983,21 +5983,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503153</v>
+        <v>503170</v>
       </c>
       <c r="R52" t="n">
-        <v>7134897</v>
+        <v>7134825</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119949113</v>
+        <v>119950877</v>
       </c>
       <c r="B53" t="n">
         <v>91858</v>
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503213</v>
+        <v>503166</v>
       </c>
       <c r="R53" t="n">
-        <v>7134599</v>
+        <v>7134864</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119950857</v>
+        <v>119966722</v>
       </c>
       <c r="B54" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6187,37 +6187,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503168</v>
+        <v>503218</v>
       </c>
       <c r="R54" t="n">
-        <v>7134856</v>
+        <v>7134517</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119953361</v>
+        <v>119950857</v>
       </c>
       <c r="B55" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6289,34 +6289,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503283</v>
+        <v>503168</v>
       </c>
       <c r="R55" t="n">
-        <v>7135226</v>
+        <v>7134856</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6375,10 +6375,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119966747</v>
+        <v>119966720</v>
       </c>
       <c r="B56" t="n">
-        <v>12337</v>
+        <v>79131</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6387,25 +6387,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>101283</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6415,10 +6415,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503341</v>
+        <v>503241</v>
       </c>
       <c r="R56" t="n">
-        <v>7134550</v>
+        <v>7134650</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6451,11 +6451,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6482,10 +6477,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119945137</v>
+        <v>119945243</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6494,25 +6489,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6522,10 +6517,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503172</v>
+        <v>503165</v>
       </c>
       <c r="R57" t="n">
-        <v>7134763</v>
+        <v>7134719</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6584,10 +6579,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119953308</v>
+        <v>119947013</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6600,37 +6595,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503244</v>
+        <v>503258</v>
       </c>
       <c r="R58" t="n">
-        <v>7135195</v>
+        <v>7134669</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6686,10 +6681,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119944992</v>
+        <v>119966726</v>
       </c>
       <c r="B59" t="n">
-        <v>79131</v>
+        <v>79652</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6698,41 +6693,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503182</v>
+        <v>503285</v>
       </c>
       <c r="R59" t="n">
-        <v>7134856</v>
+        <v>7134565</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6788,10 +6783,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119945243</v>
+        <v>119953277</v>
       </c>
       <c r="B60" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6804,37 +6799,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503165</v>
+        <v>503236</v>
       </c>
       <c r="R60" t="n">
-        <v>7134719</v>
+        <v>7135178</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6890,10 +6885,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119953277</v>
+        <v>119966744</v>
       </c>
       <c r="B61" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6902,41 +6897,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503236</v>
+        <v>503354</v>
       </c>
       <c r="R61" t="n">
-        <v>7135178</v>
+        <v>7134553</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6992,10 +6987,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119966742</v>
+        <v>119944974</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7004,41 +6999,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503371</v>
+        <v>503197</v>
       </c>
       <c r="R62" t="n">
-        <v>7134522</v>
+        <v>7134847</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7094,10 +7089,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119966744</v>
+        <v>119948976</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7106,41 +7101,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503354</v>
+        <v>503222</v>
       </c>
       <c r="R63" t="n">
-        <v>7134553</v>
+        <v>7134576</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7196,10 +7191,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119966740</v>
+        <v>119948938</v>
       </c>
       <c r="B64" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7212,37 +7207,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503194</v>
+        <v>503207</v>
       </c>
       <c r="R64" t="n">
-        <v>7134678</v>
+        <v>7134561</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7298,10 +7293,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119966732</v>
+        <v>119944998</v>
       </c>
       <c r="B65" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7314,37 +7309,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503285</v>
+        <v>503182</v>
       </c>
       <c r="R65" t="n">
-        <v>7135231</v>
+        <v>7134859</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7400,10 +7395,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119948938</v>
+        <v>119950932</v>
       </c>
       <c r="B66" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7412,25 +7407,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7440,13 +7435,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503207</v>
+        <v>503151</v>
       </c>
       <c r="R66" t="n">
-        <v>7134561</v>
+        <v>7134896</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7502,7 +7497,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119947114</v>
+        <v>119966740</v>
       </c>
       <c r="B67" t="n">
         <v>78187</v>
@@ -7538,17 +7533,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503256</v>
+        <v>503194</v>
       </c>
       <c r="R67" t="n">
-        <v>7134674</v>
+        <v>7134678</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7604,10 +7599,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119950972</v>
+        <v>119966748</v>
       </c>
       <c r="B68" t="n">
-        <v>91901</v>
+        <v>79658</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7616,41 +7611,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5448</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503157</v>
+        <v>503392</v>
       </c>
       <c r="R68" t="n">
-        <v>7134940</v>
+        <v>7134464</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7706,10 +7701,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119953290</v>
+        <v>119966734</v>
       </c>
       <c r="B69" t="n">
-        <v>79658</v>
+        <v>78278</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7718,41 +7713,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503235</v>
+        <v>503386</v>
       </c>
       <c r="R69" t="n">
-        <v>7135189</v>
+        <v>7134487</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7808,10 +7803,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119966720</v>
+        <v>119966724</v>
       </c>
       <c r="B70" t="n">
-        <v>79131</v>
+        <v>57473</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7824,21 +7819,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7848,10 +7843,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503241</v>
+        <v>503195</v>
       </c>
       <c r="R70" t="n">
-        <v>7134650</v>
+        <v>7134698</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7884,6 +7879,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7910,10 +7910,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119953313</v>
+        <v>119951025</v>
       </c>
       <c r="B71" t="n">
-        <v>79624</v>
+        <v>92048</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7926,37 +7926,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503239</v>
+        <v>503166</v>
       </c>
       <c r="R71" t="n">
-        <v>7135198</v>
+        <v>7134990</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8012,10 +8012,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119948853</v>
+        <v>119966747</v>
       </c>
       <c r="B72" t="n">
-        <v>91858</v>
+        <v>12337</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8024,41 +8024,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>101283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503204</v>
+        <v>503341</v>
       </c>
       <c r="R72" t="n">
-        <v>7134538</v>
+        <v>7134550</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8088,6 +8088,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8114,10 +8119,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119947420</v>
+        <v>119953308</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8126,38 +8131,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503213</v>
+        <v>503244</v>
       </c>
       <c r="R73" t="n">
-        <v>7134622</v>
+        <v>7135195</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8216,10 +8221,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119966748</v>
+        <v>119966728</v>
       </c>
       <c r="B74" t="n">
-        <v>79658</v>
+        <v>79624</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8228,25 +8233,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8256,10 +8261,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503392</v>
+        <v>503285</v>
       </c>
       <c r="R74" t="n">
-        <v>7134464</v>
+        <v>7134565</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8318,10 +8323,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119949136</v>
+        <v>119966732</v>
       </c>
       <c r="B75" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8334,39 +8339,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503213</v>
+        <v>503285</v>
       </c>
       <c r="R75" t="n">
-        <v>7134603</v>
+        <v>7135231</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119947043</v>
+        <v>119944992</v>
       </c>
       <c r="B76" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8437,25 +8437,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8465,13 +8465,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503245</v>
+        <v>503182</v>
       </c>
       <c r="R76" t="n">
-        <v>7134683</v>
+        <v>7134856</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8527,10 +8527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966733</v>
+        <v>119950972</v>
       </c>
       <c r="B77" t="n">
-        <v>79659</v>
+        <v>91901</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8539,41 +8539,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>5448</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503392</v>
+        <v>503157</v>
       </c>
       <c r="R77" t="n">
-        <v>7134464</v>
+        <v>7134940</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119944974</v>
+        <v>119945137</v>
       </c>
       <c r="B78" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8641,25 +8641,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503197</v>
+        <v>503172</v>
       </c>
       <c r="R78" t="n">
-        <v>7134847</v>
+        <v>7134763</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119966731</v>
+        <v>119953290</v>
       </c>
       <c r="B80" t="n">
-        <v>78279</v>
+        <v>79658</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8845,41 +8845,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503310</v>
+        <v>503235</v>
       </c>
       <c r="R80" t="n">
-        <v>7134560</v>
+        <v>7135189</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119944976</v>
+        <v>119953375</v>
       </c>
       <c r="B81" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8951,34 +8951,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503197</v>
+        <v>503279</v>
       </c>
       <c r="R81" t="n">
-        <v>7134856</v>
+        <v>7135237</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119945252</v>
+        <v>119953361</v>
       </c>
       <c r="B82" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9053,37 +9053,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503166</v>
+        <v>503283</v>
       </c>
       <c r="R82" t="n">
-        <v>7134711</v>
+        <v>7135226</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119947420</v>
+        <v>119950521</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,25 +2501,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503213</v>
+        <v>503238</v>
       </c>
       <c r="R18" t="n">
-        <v>7134622</v>
+        <v>7134692</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119950521</v>
+        <v>119947420</v>
       </c>
       <c r="B19" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503238</v>
+        <v>503213</v>
       </c>
       <c r="R19" t="n">
-        <v>7134692</v>
+        <v>7134622</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119945215</v>
+        <v>119948911</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,25 +3419,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503171</v>
+        <v>503190</v>
       </c>
       <c r="R27" t="n">
-        <v>7134729</v>
+        <v>7134550</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950732</v>
+        <v>119945215</v>
       </c>
       <c r="B28" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,25 +3521,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,13 +3549,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503146</v>
+        <v>503171</v>
       </c>
       <c r="R28" t="n">
-        <v>7134809</v>
+        <v>7134729</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119948911</v>
+        <v>119950732</v>
       </c>
       <c r="B29" t="n">
         <v>79131</v>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503190</v>
+        <v>503146</v>
       </c>
       <c r="R29" t="n">
-        <v>7134550</v>
+        <v>7134809</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119948853</v>
+        <v>119966749</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>4915</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3929,41 +3929,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>101994</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503204</v>
+        <v>503364</v>
       </c>
       <c r="R32" t="n">
-        <v>7134538</v>
+        <v>7134522</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,6 +3993,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4019,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119966749</v>
+        <v>119948853</v>
       </c>
       <c r="B33" t="n">
-        <v>4915</v>
+        <v>91858</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4031,41 +4036,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101994</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503364</v>
+        <v>503204</v>
       </c>
       <c r="R33" t="n">
-        <v>7134522</v>
+        <v>7134538</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4095,11 +4100,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119966719</v>
+        <v>119950727</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>78279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,41 +4240,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503312</v>
+        <v>503147</v>
       </c>
       <c r="R35" t="n">
-        <v>7134559</v>
+        <v>7134810</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119953313</v>
+        <v>119966731</v>
       </c>
       <c r="B36" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,37 +4346,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503239</v>
+        <v>503310</v>
       </c>
       <c r="R36" t="n">
-        <v>7135198</v>
+        <v>7134560</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950727</v>
+        <v>119966719</v>
       </c>
       <c r="B37" t="n">
-        <v>78279</v>
+        <v>90545</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,41 +4444,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503147</v>
+        <v>503312</v>
       </c>
       <c r="R37" t="n">
-        <v>7134810</v>
+        <v>7134559</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119966731</v>
+        <v>119953313</v>
       </c>
       <c r="B38" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4550,37 +4550,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503310</v>
+        <v>503239</v>
       </c>
       <c r="R38" t="n">
-        <v>7134560</v>
+        <v>7135198</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119950975</v>
+        <v>119953353</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5264,37 +5264,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503152</v>
+        <v>503265</v>
       </c>
       <c r="R45" t="n">
-        <v>7134944</v>
+        <v>7135233</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119953353</v>
+        <v>119945198</v>
       </c>
       <c r="B46" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,41 +5362,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503265</v>
+        <v>503176</v>
       </c>
       <c r="R46" t="n">
-        <v>7135233</v>
+        <v>7134750</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119966741</v>
+        <v>119950975</v>
       </c>
       <c r="B47" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5464,41 +5464,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503195</v>
+        <v>503152</v>
       </c>
       <c r="R47" t="n">
-        <v>7134698</v>
+        <v>7134944</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119945198</v>
+        <v>119966741</v>
       </c>
       <c r="B48" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5570,37 +5570,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503176</v>
+        <v>503195</v>
       </c>
       <c r="R48" t="n">
-        <v>7134750</v>
+        <v>7134698</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6069,10 +6069,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119950877</v>
+        <v>119966722</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6081,41 +6081,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503166</v>
+        <v>503218</v>
       </c>
       <c r="R53" t="n">
-        <v>7134864</v>
+        <v>7134517</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119966722</v>
+        <v>119950877</v>
       </c>
       <c r="B54" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6183,41 +6183,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503218</v>
+        <v>503166</v>
       </c>
       <c r="R54" t="n">
-        <v>7134517</v>
+        <v>7134864</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6579,10 +6579,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119947013</v>
+        <v>119966726</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6591,41 +6591,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503258</v>
+        <v>503285</v>
       </c>
       <c r="R58" t="n">
-        <v>7134669</v>
+        <v>7134565</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119966726</v>
+        <v>119947013</v>
       </c>
       <c r="B59" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6693,41 +6693,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503285</v>
+        <v>503258</v>
       </c>
       <c r="R59" t="n">
-        <v>7134565</v>
+        <v>7134669</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -9142,7 +9142,7 @@
         <v>119966727</v>
       </c>
       <c r="B83" t="n">
-        <v>92273</v>
+        <v>92290</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -9142,7 +9142,7 @@
         <v>119966727</v>
       </c>
       <c r="B83" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 47027-2020 artfynd.xlsx
+++ b/artfynd/A 47027-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88782047</v>
+        <v>89602989</v>
       </c>
       <c r="B2" t="n">
         <v>78596</v>
@@ -709,22 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503286.3053328037</v>
+        <v>503285.8717110572</v>
       </c>
       <c r="R2" t="n">
-        <v>7134571.249362721</v>
+        <v>7134570.815360786</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,14 +780,18 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88782032</v>
+        <v>89602990</v>
       </c>
       <c r="B3" t="n">
         <v>78570</v>
@@ -825,22 +825,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503263.3213690317</v>
+        <v>503262.8872805079</v>
       </c>
       <c r="R3" t="n">
-        <v>7134549.981423025</v>
+        <v>7134549.980961885</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,14 +896,18 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88782018</v>
+        <v>89602997</v>
       </c>
       <c r="B4" t="n">
         <v>77258</v>
@@ -941,22 +941,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503179.7640824763</v>
+        <v>503180.1981420306</v>
       </c>
       <c r="R4" t="n">
-        <v>7134754.95184574</v>
+        <v>7134754.952295142</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1001,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1012,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88782044</v>
+        <v>89602994</v>
       </c>
       <c r="B7" t="n">
         <v>78570</v>
@@ -1289,22 +1289,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503286.3053328037</v>
+        <v>503285.8717110572</v>
       </c>
       <c r="R7" t="n">
-        <v>7134571.249362721</v>
+        <v>7134570.815360786</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1349,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1364,17 +1360,21 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89602997</v>
+        <v>89602973</v>
       </c>
       <c r="B8" t="n">
-        <v>77258</v>
+        <v>78596</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,25 +1383,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503180.1981420306</v>
+        <v>503275.8812696152</v>
       </c>
       <c r="R8" t="n">
-        <v>7134754.952295142</v>
+        <v>7134576.874216847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89602973</v>
+        <v>89603004</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
+        <v>78072</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,25 +1499,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503275.8812696152</v>
+        <v>503177.1628641962</v>
       </c>
       <c r="R9" t="n">
-        <v>7134576.874216847</v>
+        <v>7134751.914567594</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89602989</v>
+        <v>89602992</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
+        <v>77259</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503285.8717110572</v>
+        <v>503175.8593394911</v>
       </c>
       <c r="R10" t="n">
-        <v>7134570.815360786</v>
+        <v>7134753.213756816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89602994</v>
+        <v>119950704</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,41 +1731,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503285.8717110572</v>
+        <v>503155</v>
       </c>
       <c r="R11" t="n">
-        <v>7134570.815360786</v>
+        <v>7134772</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1789,22 +1789,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,21 +1814,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89603004</v>
+        <v>119966742</v>
       </c>
       <c r="B12" t="n">
-        <v>78072</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,25 +1833,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,13 +1861,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503177.1628641962</v>
+        <v>503371</v>
       </c>
       <c r="R12" t="n">
-        <v>7134751.914567594</v>
+        <v>7134522</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,22 +1891,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,21 +1916,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89602990</v>
+        <v>119947043</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,41 +1935,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503262.8872805079</v>
+        <v>503245</v>
       </c>
       <c r="R13" t="n">
-        <v>7134549.980961885</v>
+        <v>7134683</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2021,22 +1993,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,21 +2018,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89602992</v>
+        <v>119950521</v>
       </c>
       <c r="B14" t="n">
-        <v>77259</v>
+        <v>79131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,37 +2041,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503175.8593394911</v>
+        <v>503238</v>
       </c>
       <c r="R14" t="n">
-        <v>7134753.213756816</v>
+        <v>7134692</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2137,22 +2095,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,18 +2120,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119950704</v>
+        <v>119947420</v>
       </c>
       <c r="B15" t="n">
         <v>91858</v>
@@ -2223,10 +2167,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503155</v>
+        <v>503213</v>
       </c>
       <c r="R15" t="n">
-        <v>7134772</v>
+        <v>7134622</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2285,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119966742</v>
+        <v>119953316</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,37 +2245,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503371</v>
+        <v>503249</v>
       </c>
       <c r="R16" t="n">
-        <v>7134522</v>
+        <v>7135183</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,10 +2331,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119947043</v>
+        <v>119966737</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,41 +2343,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503245</v>
+        <v>503354</v>
       </c>
       <c r="R17" t="n">
-        <v>7134683</v>
+        <v>7134564</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119950521</v>
+        <v>119953208</v>
       </c>
       <c r="B18" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,34 +2449,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503238</v>
+        <v>503164</v>
       </c>
       <c r="R18" t="n">
-        <v>7134692</v>
+        <v>7135128</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2591,10 +2535,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119947420</v>
+        <v>119947114</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2547,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2575,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503213</v>
+        <v>503256</v>
       </c>
       <c r="R19" t="n">
-        <v>7134622</v>
+        <v>7134674</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2693,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119953316</v>
+        <v>119949113</v>
       </c>
       <c r="B20" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,34 +2653,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503249</v>
+        <v>503213</v>
       </c>
       <c r="R20" t="n">
-        <v>7135183</v>
+        <v>7134599</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2795,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119966737</v>
+        <v>119966729</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2811,21 +2755,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503354</v>
+        <v>503291</v>
       </c>
       <c r="R21" t="n">
-        <v>7134564</v>
+        <v>7135241</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119953208</v>
+        <v>119966735</v>
       </c>
       <c r="B22" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,37 +2857,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503164</v>
+        <v>503371</v>
       </c>
       <c r="R22" t="n">
-        <v>7135128</v>
+        <v>7134532</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2999,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119947114</v>
+        <v>119948911</v>
       </c>
       <c r="B23" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,21 +2959,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3039,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503256</v>
+        <v>503190</v>
       </c>
       <c r="R23" t="n">
-        <v>7134674</v>
+        <v>7134550</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3101,7 +3045,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119949113</v>
+        <v>119945215</v>
       </c>
       <c r="B24" t="n">
         <v>91858</v>
@@ -3141,13 +3085,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503213</v>
+        <v>503171</v>
       </c>
       <c r="R24" t="n">
-        <v>7134599</v>
+        <v>7134729</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119966729</v>
+        <v>119950732</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>79131</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,37 +3163,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503291</v>
+        <v>503146</v>
       </c>
       <c r="R25" t="n">
-        <v>7135241</v>
+        <v>7134809</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3305,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119966735</v>
+        <v>119950802</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3321,37 +3265,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503371</v>
+        <v>503165</v>
       </c>
       <c r="R26" t="n">
-        <v>7134532</v>
+        <v>7134812</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3407,7 +3351,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119948911</v>
+        <v>119950926</v>
       </c>
       <c r="B27" t="n">
         <v>79131</v>
@@ -3447,13 +3391,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503190</v>
+        <v>503153</v>
       </c>
       <c r="R27" t="n">
-        <v>7134550</v>
+        <v>7134897</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3509,10 +3453,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119945215</v>
+        <v>119966749</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>4915</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,41 +3465,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>101994</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503171</v>
+        <v>503364</v>
       </c>
       <c r="R28" t="n">
-        <v>7134729</v>
+        <v>7134522</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3585,6 +3529,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3611,10 +3560,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950732</v>
+        <v>119948853</v>
       </c>
       <c r="B29" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3623,25 +3572,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3651,13 +3600,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503146</v>
+        <v>503204</v>
       </c>
       <c r="R29" t="n">
-        <v>7134809</v>
+        <v>7134538</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3713,10 +3662,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950802</v>
+        <v>119944976</v>
       </c>
       <c r="B30" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3729,21 +3678,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3753,13 +3702,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503165</v>
+        <v>503197</v>
       </c>
       <c r="R30" t="n">
-        <v>7134812</v>
+        <v>7134856</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3815,10 +3764,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950926</v>
+        <v>119950727</v>
       </c>
       <c r="B31" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,21 +3780,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3855,10 +3804,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503153</v>
+        <v>503147</v>
       </c>
       <c r="R31" t="n">
-        <v>7134897</v>
+        <v>7134810</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3917,10 +3866,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119966749</v>
+        <v>119966731</v>
       </c>
       <c r="B32" t="n">
-        <v>4915</v>
+        <v>78279</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3933,21 +3882,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101994</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3957,10 +3906,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503364</v>
+        <v>503310</v>
       </c>
       <c r="R32" t="n">
-        <v>7134522</v>
+        <v>7134560</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3993,11 +3942,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. 2 mm runda kläckhål i barken på nedfallen topp till gammal asphögstubbe.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4024,10 +3968,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119948853</v>
+        <v>119966719</v>
       </c>
       <c r="B33" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4040,37 +3984,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503204</v>
+        <v>503312</v>
       </c>
       <c r="R33" t="n">
-        <v>7134538</v>
+        <v>7134559</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4126,10 +4070,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119944976</v>
+        <v>119953313</v>
       </c>
       <c r="B34" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4142,34 +4086,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503197</v>
+        <v>503239</v>
       </c>
       <c r="R34" t="n">
-        <v>7134856</v>
+        <v>7135198</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4228,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950727</v>
+        <v>119947387</v>
       </c>
       <c r="B35" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4244,21 +4188,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,13 +4212,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503147</v>
+        <v>503210</v>
       </c>
       <c r="R35" t="n">
-        <v>7134810</v>
+        <v>7134632</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4330,10 +4274,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119966731</v>
+        <v>119966746</v>
       </c>
       <c r="B36" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,25 +4286,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503310</v>
+        <v>503256</v>
       </c>
       <c r="R36" t="n">
-        <v>7134560</v>
+        <v>7134674</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4432,10 +4376,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119966719</v>
+        <v>119966739</v>
       </c>
       <c r="B37" t="n">
-        <v>90545</v>
+        <v>78187</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,25 +4388,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4472,10 +4416,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503312</v>
+        <v>503196</v>
       </c>
       <c r="R37" t="n">
-        <v>7134559</v>
+        <v>7134493</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4534,10 +4478,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119953313</v>
+        <v>119966733</v>
       </c>
       <c r="B38" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,41 +4490,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503239</v>
+        <v>503392</v>
       </c>
       <c r="R38" t="n">
-        <v>7135198</v>
+        <v>7134464</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4636,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119947387</v>
+        <v>119946999</v>
       </c>
       <c r="B39" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,21 +4596,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503210</v>
+        <v>503249</v>
       </c>
       <c r="R39" t="n">
-        <v>7134632</v>
+        <v>7134683</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4738,10 +4682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119966746</v>
+        <v>119945252</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4750,41 +4694,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503256</v>
+        <v>503166</v>
       </c>
       <c r="R40" t="n">
-        <v>7134674</v>
+        <v>7134711</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4840,10 +4784,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119966739</v>
+        <v>119953353</v>
       </c>
       <c r="B41" t="n">
-        <v>78187</v>
+        <v>90545</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4852,41 +4796,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503196</v>
+        <v>503265</v>
       </c>
       <c r="R41" t="n">
-        <v>7134493</v>
+        <v>7135233</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4942,10 +4886,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119966733</v>
+        <v>119945198</v>
       </c>
       <c r="B42" t="n">
-        <v>79659</v>
+        <v>78278</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4954,41 +4898,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503392</v>
+        <v>503176</v>
       </c>
       <c r="R42" t="n">
-        <v>7134464</v>
+        <v>7134750</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5044,10 +4988,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119946999</v>
+        <v>119950975</v>
       </c>
       <c r="B43" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5056,25 +5000,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5084,10 +5028,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503249</v>
+        <v>503152</v>
       </c>
       <c r="R43" t="n">
-        <v>7134683</v>
+        <v>7134944</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5146,10 +5090,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119945252</v>
+        <v>119966741</v>
       </c>
       <c r="B44" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5162,37 +5106,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503166</v>
+        <v>503195</v>
       </c>
       <c r="R44" t="n">
-        <v>7134711</v>
+        <v>7134698</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5248,10 +5192,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119953353</v>
+        <v>119948845</v>
       </c>
       <c r="B45" t="n">
-        <v>90545</v>
+        <v>78187</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5260,41 +5204,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503265</v>
+        <v>503204</v>
       </c>
       <c r="R45" t="n">
-        <v>7135233</v>
+        <v>7134543</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5350,10 +5294,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119945198</v>
+        <v>119949016</v>
       </c>
       <c r="B46" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,25 +5306,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5390,10 +5334,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503176</v>
+        <v>503196</v>
       </c>
       <c r="R46" t="n">
-        <v>7134750</v>
+        <v>7134584</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5452,10 +5396,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119950975</v>
+        <v>119949136</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5464,41 +5408,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503152</v>
+        <v>503213</v>
       </c>
       <c r="R47" t="n">
-        <v>7134944</v>
+        <v>7134603</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5554,7 +5503,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119966741</v>
+        <v>119945075</v>
       </c>
       <c r="B48" t="n">
         <v>78187</v>
@@ -5590,17 +5539,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503195</v>
+        <v>503170</v>
       </c>
       <c r="R48" t="n">
-        <v>7134698</v>
+        <v>7134825</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5656,10 +5605,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119948845</v>
+        <v>119966722</v>
       </c>
       <c r="B49" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5672,37 +5621,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503204</v>
+        <v>503218</v>
       </c>
       <c r="R49" t="n">
-        <v>7134543</v>
+        <v>7134517</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5758,7 +5707,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119949016</v>
+        <v>119950877</v>
       </c>
       <c r="B50" t="n">
         <v>91858</v>
@@ -5798,10 +5747,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503196</v>
+        <v>503166</v>
       </c>
       <c r="R50" t="n">
-        <v>7134584</v>
+        <v>7134864</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5860,10 +5809,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119949136</v>
+        <v>119950857</v>
       </c>
       <c r="B51" t="n">
-        <v>57473</v>
+        <v>78278</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5876,42 +5825,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503213</v>
+        <v>503168</v>
       </c>
       <c r="R51" t="n">
-        <v>7134603</v>
+        <v>7134856</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5967,10 +5911,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119945075</v>
+        <v>119966720</v>
       </c>
       <c r="B52" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5983,37 +5927,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503170</v>
+        <v>503241</v>
       </c>
       <c r="R52" t="n">
-        <v>7134825</v>
+        <v>7134650</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6069,10 +6013,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119966722</v>
+        <v>119945243</v>
       </c>
       <c r="B53" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6085,37 +6029,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503218</v>
+        <v>503165</v>
       </c>
       <c r="R53" t="n">
-        <v>7134517</v>
+        <v>7134719</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6171,10 +6115,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119950877</v>
+        <v>119966726</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6187,37 +6131,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503166</v>
+        <v>503285</v>
       </c>
       <c r="R54" t="n">
-        <v>7134864</v>
+        <v>7134565</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6273,10 +6217,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119950857</v>
+        <v>119947013</v>
       </c>
       <c r="B55" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6289,21 +6233,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6313,10 +6257,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503168</v>
+        <v>503258</v>
       </c>
       <c r="R55" t="n">
-        <v>7134856</v>
+        <v>7134669</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6375,10 +6319,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119966720</v>
+        <v>119953277</v>
       </c>
       <c r="B56" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6391,37 +6335,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503241</v>
+        <v>503236</v>
       </c>
       <c r="R56" t="n">
-        <v>7134650</v>
+        <v>7135178</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6477,10 +6421,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119945243</v>
+        <v>119966744</v>
       </c>
       <c r="B57" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6489,41 +6433,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503165</v>
+        <v>503354</v>
       </c>
       <c r="R57" t="n">
-        <v>7134719</v>
+        <v>7134553</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6579,10 +6523,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119966726</v>
+        <v>119944974</v>
       </c>
       <c r="B58" t="n">
-        <v>79652</v>
+        <v>78187</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6591,41 +6535,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503285</v>
+        <v>503197</v>
       </c>
       <c r="R58" t="n">
-        <v>7134565</v>
+        <v>7134847</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6681,10 +6625,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119947013</v>
+        <v>119948976</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6697,21 +6641,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6721,13 +6665,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503258</v>
+        <v>503222</v>
       </c>
       <c r="R59" t="n">
-        <v>7134669</v>
+        <v>7134576</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6783,10 +6727,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119953277</v>
+        <v>119948938</v>
       </c>
       <c r="B60" t="n">
-        <v>79624</v>
+        <v>89650</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6799,34 +6743,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503236</v>
+        <v>503207</v>
       </c>
       <c r="R60" t="n">
-        <v>7135178</v>
+        <v>7134561</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6885,10 +6829,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119966744</v>
+        <v>119944998</v>
       </c>
       <c r="B61" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6897,41 +6841,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503354</v>
+        <v>503182</v>
       </c>
       <c r="R61" t="n">
-        <v>7134553</v>
+        <v>7134859</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6987,10 +6931,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119944974</v>
+        <v>119950932</v>
       </c>
       <c r="B62" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6999,25 +6943,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7027,10 +6971,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503197</v>
+        <v>503151</v>
       </c>
       <c r="R62" t="n">
-        <v>7134847</v>
+        <v>7134896</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7089,10 +7033,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119948976</v>
+        <v>119966740</v>
       </c>
       <c r="B63" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7105,37 +7049,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503222</v>
+        <v>503194</v>
       </c>
       <c r="R63" t="n">
-        <v>7134576</v>
+        <v>7134678</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7191,10 +7135,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119948938</v>
+        <v>119966748</v>
       </c>
       <c r="B64" t="n">
-        <v>89650</v>
+        <v>79658</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7203,41 +7147,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503207</v>
+        <v>503392</v>
       </c>
       <c r="R64" t="n">
-        <v>7134561</v>
+        <v>7134464</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7293,7 +7237,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119944998</v>
+        <v>119966734</v>
       </c>
       <c r="B65" t="n">
         <v>78278</v>
@@ -7329,17 +7273,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503182</v>
+        <v>503386</v>
       </c>
       <c r="R65" t="n">
-        <v>7134859</v>
+        <v>7134487</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7395,10 +7339,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119950932</v>
+        <v>119966724</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7407,41 +7351,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503151</v>
+        <v>503195</v>
       </c>
       <c r="R66" t="n">
-        <v>7134896</v>
+        <v>7134698</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7471,6 +7415,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7497,10 +7446,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119966740</v>
+        <v>119951025</v>
       </c>
       <c r="B67" t="n">
-        <v>78187</v>
+        <v>92048</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7513,37 +7462,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503194</v>
+        <v>503166</v>
       </c>
       <c r="R67" t="n">
-        <v>7134678</v>
+        <v>7134990</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7599,10 +7548,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119966748</v>
+        <v>119966747</v>
       </c>
       <c r="B68" t="n">
-        <v>79658</v>
+        <v>12337</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7611,25 +7560,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>101283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7639,10 +7588,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503392</v>
+        <v>503341</v>
       </c>
       <c r="R68" t="n">
-        <v>7134464</v>
+        <v>7134550</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7675,6 +7624,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7701,10 +7655,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119966734</v>
+        <v>119953308</v>
       </c>
       <c r="B69" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7717,37 +7671,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503386</v>
+        <v>503244</v>
       </c>
       <c r="R69" t="n">
-        <v>7134487</v>
+        <v>7135195</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7803,10 +7757,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119966724</v>
+        <v>119966728</v>
       </c>
       <c r="B70" t="n">
-        <v>57473</v>
+        <v>79624</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7819,21 +7773,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7843,10 +7797,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503195</v>
+        <v>503285</v>
       </c>
       <c r="R70" t="n">
-        <v>7134698</v>
+        <v>7134565</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7879,11 +7833,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7910,10 +7859,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119951025</v>
+        <v>119966732</v>
       </c>
       <c r="B71" t="n">
-        <v>92048</v>
+        <v>79623</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7926,37 +7875,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503166</v>
+        <v>503285</v>
       </c>
       <c r="R71" t="n">
-        <v>7134990</v>
+        <v>7135231</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8012,10 +7961,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119966747</v>
+        <v>119944992</v>
       </c>
       <c r="B72" t="n">
-        <v>12337</v>
+        <v>79131</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8024,41 +7973,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>101283</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503341</v>
+        <v>503182</v>
       </c>
       <c r="R72" t="n">
-        <v>7134550</v>
+        <v>7134856</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8088,11 +8037,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8119,10 +8063,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119953308</v>
+        <v>119950972</v>
       </c>
       <c r="B73" t="n">
-        <v>79623</v>
+        <v>91901</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8135,34 +8079,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5448</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503244</v>
+        <v>503157</v>
       </c>
       <c r="R73" t="n">
-        <v>7135195</v>
+        <v>7134940</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8221,10 +8165,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119966728</v>
+        <v>119945137</v>
       </c>
       <c r="B74" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8233,41 +8177,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503285</v>
+        <v>503172</v>
       </c>
       <c r="R74" t="n">
-        <v>7134565</v>
+        <v>7134763</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8323,10 +8267,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119966732</v>
+        <v>119966743</v>
       </c>
       <c r="B75" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8335,25 +8279,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8363,10 +8307,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503285</v>
+        <v>503321</v>
       </c>
       <c r="R75" t="n">
-        <v>7135231</v>
+        <v>7134576</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8425,10 +8369,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119944992</v>
+        <v>119953290</v>
       </c>
       <c r="B76" t="n">
-        <v>79131</v>
+        <v>79658</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8437,41 +8381,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503182</v>
+        <v>503235</v>
       </c>
       <c r="R76" t="n">
-        <v>7134856</v>
+        <v>7135189</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8527,10 +8471,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119950972</v>
+        <v>119953375</v>
       </c>
       <c r="B77" t="n">
-        <v>91901</v>
+        <v>78187</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8543,34 +8487,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503157</v>
+        <v>503279</v>
       </c>
       <c r="R77" t="n">
-        <v>7134940</v>
+        <v>7135237</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8629,10 +8573,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119945137</v>
+        <v>119953361</v>
       </c>
       <c r="B78" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8641,41 +8585,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503172</v>
+        <v>503283</v>
       </c>
       <c r="R78" t="n">
-        <v>7134763</v>
+        <v>7135226</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8731,10 +8675,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119966743</v>
+        <v>119966727</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
+        <v>92297</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8743,38 +8687,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503321</v>
+        <v>503216</v>
       </c>
       <c r="R79" t="n">
-        <v>7134576</v>
+        <v>7134515</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8809,12 +8756,18 @@
           <t>2024-09-24</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under bränd tallåga.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8830,423 +8783,6 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>119953290</v>
-      </c>
-      <c r="B80" t="n">
-        <v>79658</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Strömsund, Strömsund, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>503235</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7135189</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>119953375</v>
-      </c>
-      <c r="B81" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>353</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Strömsund, Strömsund, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>503279</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7135237</v>
-      </c>
-      <c r="S81" t="n">
-        <v>15</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>119953361</v>
-      </c>
-      <c r="B82" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Strömsund, Strömsund, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>503283</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7135226</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>119966727</v>
-      </c>
-      <c r="B83" t="n">
-        <v>92295</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Phellodon melaleucus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>503216</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7134515</v>
-      </c>
-      <c r="S83" t="n">
-        <v>25</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under bränd tallåga.</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="inlineStr"/>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
